--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -467,7 +467,7 @@
         <v>64.5</v>
       </c>
       <c r="C2">
-        <v>64.5</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -478,7 +478,7 @@
         <v>63.56005859375</v>
       </c>
       <c r="C3">
-        <v>63.56005859375</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -489,7 +489,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C4">
-        <v>47.860107421875</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -500,7 +500,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="C5">
-        <v>66.3701171875</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -511,7 +511,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="C6">
-        <v>83.2001953125</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -522,7 +522,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>53.659912109375</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -533,7 +533,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>71.9599609375</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -544,7 +544,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>56.050048828125</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -555,7 +555,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>61.56005859375</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -566,7 +566,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>54.050048828125</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -577,7 +577,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>47.860107421875</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -588,7 +588,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>55.659912109375</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -599,7 +599,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>62.56005859375</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -610,7 +610,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>55.659912109375</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -632,7 +632,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>60.60009765625</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -643,7 +643,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>61.159912109375</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -654,7 +654,7 @@
         <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>67.16015625</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -665,7 +665,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>54.89990234375</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -676,7 +676,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>68.06005859375</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1175,55 +1175,55 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>83.2001953125</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>71.9599609375</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>68.06005859375</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>67.16015625</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>66.3701171875</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>64.5</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>63.56005859375</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1231,103 +1231,103 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>62.56005859375</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>61.56005859375</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>61.159912109375</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>60.60009765625</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13">
-        <v>56.050048828125</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>55.659912109375</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>55.659912109375</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B16">
-        <v>54.89990234375</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>54.050048828125</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B18">
-        <v>53.659912109375</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B19">
-        <v>47.860107421875</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B20">
-        <v>47.860107421875</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>18.8</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -577,7 +577,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1228,26 +1228,26 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B10">
-        <v>53.6</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B11">
-        <v>52.8</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -467,7 +467,7 @@
         <v>64.5</v>
       </c>
       <c r="C2">
-        <v>42.8</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -478,7 +478,7 @@
         <v>63.56005859375</v>
       </c>
       <c r="C3">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -489,7 +489,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C4">
-        <v>67.25</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -500,7 +500,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="C5">
-        <v>28.7</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -511,7 +511,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="C6">
-        <v>83.5</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -522,7 +522,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>49.8</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -533,7 +533,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>53.6</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -544,7 +544,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>57.25</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -555,7 +555,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>41.7</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -566,7 +566,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>51.15</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -577,7 +577,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>56.2</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -588,7 +588,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>38.9</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -599,7 +599,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>55.9</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -610,7 +610,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>18.8</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>63.85</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -632,7 +632,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>48.95</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -643,7 +643,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>57.65</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -654,7 +654,7 @@
         <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>62.35</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -665,7 +665,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>47.35</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -676,7 +676,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1172,146 +1172,146 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>83.5</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>82.5</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>67.25</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>63.85</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>62.35</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>57.65</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>57.25</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>56.2</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>55.9</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>53.6</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12">
-        <v>51.15</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>49.8</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B14">
-        <v>48.95</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>47.35</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>42.8</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17">
-        <v>41.7</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>41.7</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B19">
-        <v>38.9</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>5</v>
       </c>
       <c r="B20">
-        <v>28.7</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>15</v>
       </c>
       <c r="B21">
-        <v>18.8</v>
+        <v>29.81</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -467,7 +467,7 @@
         <v>64.5</v>
       </c>
       <c r="C2">
-        <v>61.71</v>
+        <v>75.68000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -478,7 +478,7 @@
         <v>63.56005859375</v>
       </c>
       <c r="C3">
-        <v>85.90000000000001</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -489,7 +489,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C4">
-        <v>71.55</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -500,7 +500,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="C5">
-        <v>34.41</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -511,7 +511,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="C6">
-        <v>86.90000000000001</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -522,7 +522,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>61.41</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -533,7 +533,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>58.41</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -544,7 +544,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>66.25</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -555,7 +555,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>50.81</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -566,7 +566,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>68.84999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -577,7 +577,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>61.91</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -588,7 +588,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>59.6</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -599,7 +599,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>74.01000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -610,7 +610,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>29.81</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>94.47</v>
+        <v>95.41</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -632,7 +632,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>74.16</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -643,7 +643,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>63.36</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -654,7 +654,7 @@
         <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>82.55</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -665,7 +665,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>51.65</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -676,7 +676,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>94.47</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1183,151 +1183,151 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>86.90000000000001</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>85.90000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>82.55</v>
+        <v>95.41</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>74.16</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B7">
-        <v>74.01000000000001</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>71.55</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>68.84999999999999</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>66.25</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>63.36</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B12">
-        <v>61.91</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B13">
-        <v>61.71</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B14">
-        <v>61.41</v>
+        <v>75.68000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>59.81</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16">
-        <v>59.6</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B17">
-        <v>58.41</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B18">
-        <v>51.65</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B19">
-        <v>50.81</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B20">
-        <v>34.41</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B21">
-        <v>29.81</v>
+        <v>44.68</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="24">
   <si>
     <t>Rodada 1</t>
   </si>
   <si>
     <t>Rodada 2</t>
+  </si>
+  <si>
+    <t>Rodada 3</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -448,31 +451,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>64.5</v>
       </c>
       <c r="C2">
-        <v>75.68000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>75.68017578125</v>
+      </c>
+      <c r="D2">
+        <v>75.68017578125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -480,213 +489,273 @@
       <c r="C3">
         <v>100.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
       </c>
       <c r="C4">
-        <v>90.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>90.60009765625</v>
+      </c>
+      <c r="D4">
+        <v>90.60009765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
       </c>
       <c r="C5">
-        <v>44.68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>44.679931640625</v>
+      </c>
+      <c r="D5">
+        <v>44.679931640625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
       </c>
       <c r="C6">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>98.7001953125</v>
+      </c>
+      <c r="D6">
+        <v>98.7001953125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>81.48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>81.47998046875</v>
+      </c>
+      <c r="D7">
+        <v>81.47998046875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>66.68000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>66.68017578125</v>
+      </c>
+      <c r="D8">
+        <v>66.68017578125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>70.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>70.43994140625</v>
+      </c>
+      <c r="D9">
+        <v>70.43994140625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>83.48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>83.47998046875</v>
+      </c>
+      <c r="D10">
+        <v>83.47998046875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>85.7001953125</v>
+      </c>
+      <c r="D11">
+        <v>85.7001953125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>72.18000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>72.18017578125</v>
+      </c>
+      <c r="D12">
+        <v>72.18017578125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>73.59999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>73.60009765625</v>
+      </c>
+      <c r="D13">
+        <v>73.60009765625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>96.48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>96.47998046875</v>
+      </c>
+      <c r="D14">
+        <v>96.47998046875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>55.78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>55.780029296875</v>
+      </c>
+      <c r="D15">
+        <v>55.780029296875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>95.41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>95.41015625</v>
+      </c>
+      <c r="D16">
+        <v>95.41015625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>75.88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>75.8798828125</v>
+      </c>
+      <c r="D17">
+        <v>75.8798828125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>71.18000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>71.18017578125</v>
+      </c>
+      <c r="D18">
+        <v>71.18017578125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>86.45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>86.4501953125</v>
+      </c>
+      <c r="D19">
+        <v>86.4501953125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>77.59999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>77.60009765625</v>
+      </c>
+      <c r="D20">
+        <v>77.60009765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>82.18000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>82.18017578125</v>
+      </c>
+      <c r="D21">
+        <v>82.18017578125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
         <v>0</v>
       </c>
     </row>
@@ -702,107 +771,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +891,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -830,7 +899,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -838,7 +907,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -846,7 +915,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -854,7 +923,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -862,7 +931,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -870,7 +939,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -878,7 +947,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -886,7 +955,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -894,7 +963,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -902,7 +971,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -910,7 +979,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -918,7 +987,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -926,7 +995,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -934,7 +1003,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -942,7 +1011,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -950,7 +1019,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -958,7 +1027,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -966,7 +1035,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -974,7 +1043,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -997,7 +1066,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1005,7 +1074,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1013,7 +1082,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1021,7 +1090,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1029,7 +1098,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1037,7 +1106,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1045,7 +1114,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1053,7 +1122,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1061,7 +1130,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1069,7 +1138,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1077,7 +1146,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1085,7 +1154,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1093,7 +1162,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1101,7 +1170,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1109,7 +1178,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1117,7 +1186,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1125,7 +1194,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1133,7 +1202,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1141,7 +1210,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1149,7 +1218,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1172,162 +1241,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>100.5</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>98.7</v>
+        <v>197.400390625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>96.48</v>
+        <v>192.9599609375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5">
-        <v>95.41</v>
+        <v>190.8203125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>90.59999999999999</v>
+        <v>181.2001953125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
-        <v>86.45</v>
+        <v>172.900390625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
-        <v>85.7</v>
+        <v>171.400390625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>83.48</v>
+        <v>166.9599609375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
-        <v>82.18000000000001</v>
+        <v>164.3603515625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11">
-        <v>81.48</v>
+        <v>162.9599609375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>77.59999999999999</v>
+        <v>155.2001953125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>75.88</v>
+        <v>151.759765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14">
-        <v>75.68000000000001</v>
+        <v>151.3603515625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>73.59999999999999</v>
+        <v>147.2001953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>72.18000000000001</v>
+        <v>144.3603515625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
-        <v>71.18000000000001</v>
+        <v>142.3603515625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>70.3</v>
+        <v>140.8798828125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
-        <v>66.68000000000001</v>
+        <v>133.3603515625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20">
-        <v>55.78</v>
+        <v>111.56005859375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21">
-        <v>44.68</v>
+        <v>89.35986328125</v>
       </c>
     </row>
   </sheetData>
@@ -1347,7 +1416,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1355,7 +1424,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1363,7 +1432,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1371,7 +1440,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1379,7 +1448,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1387,7 +1456,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1395,7 +1464,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1403,7 +1472,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1411,7 +1480,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1419,7 +1488,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1427,7 +1496,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1435,7 +1504,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1443,7 +1512,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1451,7 +1520,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1459,7 +1528,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1467,7 +1536,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1475,7 +1544,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1483,7 +1552,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1491,7 +1560,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1499,7 +1568,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1522,7 +1591,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1530,7 +1599,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1538,7 +1607,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1546,7 +1615,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1554,7 +1623,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1562,7 +1631,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1570,7 +1639,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1578,7 +1647,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1586,7 +1655,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1594,7 +1663,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1602,7 +1671,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1610,7 +1679,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1618,7 +1687,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1626,7 +1695,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1634,7 +1703,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1642,7 +1711,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1650,7 +1719,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1658,7 +1727,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1666,7 +1735,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1674,7 +1743,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1697,7 +1766,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1705,7 +1774,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1713,7 +1782,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1721,7 +1790,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1729,7 +1798,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1737,7 +1806,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1745,7 +1814,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1753,7 +1822,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1761,7 +1830,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1769,7 +1838,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1777,7 +1846,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1785,7 +1854,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1793,7 +1862,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1801,7 +1870,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1809,7 +1878,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1817,7 +1886,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1825,7 +1894,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1833,7 +1902,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1841,7 +1910,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1849,7 +1918,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1872,7 +1941,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1880,7 +1949,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1888,7 +1957,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1896,7 +1965,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1904,7 +1973,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1912,7 +1981,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1920,7 +1989,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1928,7 +1997,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1936,7 +2005,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1944,7 +2013,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1952,7 +2021,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1960,7 +2029,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1968,7 +2037,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1976,7 +2045,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1984,7 +2053,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1992,7 +2061,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2000,7 +2069,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2008,7 +2077,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2016,7 +2085,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2024,7 +2093,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -476,7 +476,7 @@
         <v>75.68017578125</v>
       </c>
       <c r="D2">
-        <v>75.68017578125</v>
+        <v>38.37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -490,7 +490,7 @@
         <v>100.5</v>
       </c>
       <c r="D3">
-        <v>100.5</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -504,7 +504,7 @@
         <v>90.60009765625</v>
       </c>
       <c r="D4">
-        <v>90.60009765625</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -518,7 +518,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="D5">
-        <v>44.679931640625</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -532,7 +532,7 @@
         <v>98.7001953125</v>
       </c>
       <c r="D6">
-        <v>98.7001953125</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -546,7 +546,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D7">
-        <v>81.47998046875</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -560,7 +560,7 @@
         <v>66.68017578125</v>
       </c>
       <c r="D8">
-        <v>66.68017578125</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -574,7 +574,7 @@
         <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>70.43994140625</v>
+        <v>20.29</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -588,7 +588,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>83.47998046875</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -602,7 +602,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>85.7001953125</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -616,7 +616,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>72.18017578125</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -630,7 +630,7 @@
         <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>73.60009765625</v>
+        <v>41.97</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -644,7 +644,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>96.47998046875</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -658,7 +658,7 @@
         <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>55.780029296875</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -672,7 +672,7 @@
         <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>95.41015625</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -686,7 +686,7 @@
         <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>75.8798828125</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -700,7 +700,7 @@
         <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>71.18017578125</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -714,7 +714,7 @@
         <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>86.4501953125</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -728,7 +728,7 @@
         <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>77.60009765625</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -742,7 +742,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D21">
-        <v>82.18017578125</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1241,98 +1241,98 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B2">
-        <v>201</v>
+        <v>150.24998046875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B3">
-        <v>197.400390625</v>
+        <v>134.98017578125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>192.9599609375</v>
+        <v>132.57</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>190.8203125</v>
+        <v>131.4201953125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>181.2001953125</v>
+        <v>130.5001953125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B7">
-        <v>172.900390625</v>
+        <v>129.24998046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>171.400390625</v>
+        <v>128.20015625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B9">
-        <v>166.9599609375</v>
+        <v>127.35017578125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B10">
-        <v>164.3603515625</v>
+        <v>122.27009765625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>162.9599609375</v>
+        <v>121.1701953125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B12">
-        <v>155.2001953125</v>
+        <v>119.54998046875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>151.759765625</v>
+        <v>115.57009765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1340,55 +1340,55 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>151.3603515625</v>
+        <v>114.05017578125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>147.2001953125</v>
+        <v>113.05017578125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>144.3603515625</v>
+        <v>110.3698828125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>142.3603515625</v>
+        <v>110.27009765625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>140.8798828125</v>
+        <v>101.370029296875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19">
-        <v>133.3603515625</v>
+        <v>90.72994140624999</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B20">
-        <v>111.56005859375</v>
+        <v>83.98017578125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1396,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="B21">
-        <v>89.35986328125</v>
+        <v>75.869931640625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -476,7 +476,7 @@
         <v>75.68017578125</v>
       </c>
       <c r="D2">
-        <v>38.37</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -490,7 +490,7 @@
         <v>100.5</v>
       </c>
       <c r="D3">
-        <v>32.07</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -504,7 +504,7 @@
         <v>90.60009765625</v>
       </c>
       <c r="D4">
-        <v>31.67</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -518,7 +518,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="D5">
-        <v>31.19</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -532,7 +532,7 @@
         <v>98.7001953125</v>
       </c>
       <c r="D6">
-        <v>31.8</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -546,7 +546,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D7">
-        <v>38.07</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -560,7 +560,7 @@
         <v>66.68017578125</v>
       </c>
       <c r="D8">
-        <v>17.3</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -574,7 +574,7 @@
         <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>20.29</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -588,7 +588,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>45.77</v>
+        <v>90.45999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -602,7 +602,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>35.47</v>
+        <v>65.66</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -616,7 +616,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>62.8</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -630,7 +630,7 @@
         <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>41.97</v>
+        <v>99.26000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -644,7 +644,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>53.77</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -658,7 +658,7 @@
         <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>45.59</v>
+        <v>88.14</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -672,7 +672,7 @@
         <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>32.79</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -686,7 +686,7 @@
         <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>34.49</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -700,7 +700,7 @@
         <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>41.87</v>
+        <v>72.26000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -714,7 +714,7 @@
         <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>44.97</v>
+        <v>63.56</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -728,7 +728,7 @@
         <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>32.67</v>
+        <v>77.45999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -742,7 +742,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D21">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1241,42 +1241,42 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>150.24998046875</v>
+        <v>206.9001953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>134.98017578125</v>
+        <v>192.16</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>132.57</v>
+        <v>187.94017578125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>131.4201953125</v>
+        <v>183.93998046875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>130.5001953125</v>
+        <v>175.86009765625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1284,95 +1284,95 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>129.24998046875</v>
+        <v>173.93998046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>128.20015625</v>
+        <v>172.86009765625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B9">
-        <v>127.35017578125</v>
+        <v>169.58017578125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>122.27009765625</v>
+        <v>163.2698828125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B11">
-        <v>121.1701953125</v>
+        <v>159.93998046875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>119.54998046875</v>
+        <v>155.06009765625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13">
-        <v>115.57009765625</v>
+        <v>151.65015625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>114.05017578125</v>
+        <v>151.3601953125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>113.05017578125</v>
+        <v>150.0101953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B16">
-        <v>110.3698828125</v>
+        <v>148.94017578125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>110.27009765625</v>
+        <v>143.920029296875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>101.370029296875</v>
+        <v>143.44017578125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1380,23 +1380,23 @@
         <v>10</v>
       </c>
       <c r="B19">
-        <v>90.72994140624999</v>
+        <v>140.47994140625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B20">
-        <v>83.98017578125</v>
+        <v>125.719931640625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B21">
-        <v>75.869931640625</v>
+        <v>110.28017578125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="25">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -31,6 +31,9 @@
   </si>
   <si>
     <t>Rodada 3</t>
+  </si>
+  <si>
+    <t>Rodada 4</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -451,10 +454,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,10 +467,13 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -476,12 +482,15 @@
         <v>75.68017578125</v>
       </c>
       <c r="D2">
-        <v>73.26000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>73.259765625</v>
+      </c>
+      <c r="E2">
+        <v>73.259765625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -490,12 +499,15 @@
         <v>100.5</v>
       </c>
       <c r="D3">
-        <v>91.66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>91.66015625</v>
+      </c>
+      <c r="E3">
+        <v>91.66015625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -504,12 +516,15 @@
         <v>90.60009765625</v>
       </c>
       <c r="D4">
-        <v>85.26000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>84.56005859375</v>
+      </c>
+      <c r="E4">
+        <v>84.56005859375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -518,12 +533,15 @@
         <v>44.679931640625</v>
       </c>
       <c r="D5">
-        <v>81.04000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>79.740234375</v>
+      </c>
+      <c r="E5">
+        <v>79.740234375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -532,12 +550,15 @@
         <v>98.7001953125</v>
       </c>
       <c r="D6">
-        <v>108.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>109</v>
+      </c>
+      <c r="E6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -546,12 +567,15 @@
         <v>81.47998046875</v>
       </c>
       <c r="D7">
-        <v>78.45999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>79.259765625</v>
+      </c>
+      <c r="E7">
+        <v>79.259765625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -560,12 +584,15 @@
         <v>66.68017578125</v>
       </c>
       <c r="D8">
-        <v>43.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>42.14990234375</v>
+      </c>
+      <c r="E8">
+        <v>42.14990234375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -574,12 +601,15 @@
         <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>70.04000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>71.64013671875</v>
+      </c>
+      <c r="E9">
+        <v>71.64013671875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -588,12 +618,15 @@
         <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>90.45999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>90.4599609375</v>
+      </c>
+      <c r="E10">
+        <v>90.4599609375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -602,12 +635,15 @@
         <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>65.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>65.66015625</v>
+      </c>
+      <c r="E11">
+        <v>65.66015625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -616,12 +652,15 @@
         <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>97.40000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>97.39990234375</v>
+      </c>
+      <c r="E12">
+        <v>97.39990234375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -630,12 +669,15 @@
         <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>99.26000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>100.06005859375</v>
+      </c>
+      <c r="E13">
+        <v>100.06005859375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -644,12 +686,15 @@
         <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>87.45999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>87.4599609375</v>
+      </c>
+      <c r="E14">
+        <v>87.4599609375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -658,12 +703,15 @@
         <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>88.14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>88.93994140625</v>
+      </c>
+      <c r="E15">
+        <v>88.93994140625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -672,12 +720,15 @@
         <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>56.24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>57.0400390625</v>
+      </c>
+      <c r="E16">
+        <v>57.0400390625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -686,12 +737,15 @@
         <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>87.39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>87.39013671875</v>
+      </c>
+      <c r="E17">
+        <v>87.39013671875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -700,12 +754,15 @@
         <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>72.26000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>73.06005859375</v>
+      </c>
+      <c r="E18">
+        <v>73.06005859375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -714,12 +771,15 @@
         <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>63.56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>64.35986328125</v>
+      </c>
+      <c r="E19">
+        <v>64.35986328125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -728,12 +788,15 @@
         <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>77.45999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>78.259765625</v>
+      </c>
+      <c r="E20">
+        <v>78.259765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -742,12 +805,15 @@
         <v>82.18017578125</v>
       </c>
       <c r="D21">
-        <v>105.76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>105.759765625</v>
+      </c>
+      <c r="E21">
+        <v>105.759765625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -756,6 +822,9 @@
         <v>0</v>
       </c>
       <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>0</v>
       </c>
     </row>
@@ -771,107 +840,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -891,7 +960,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -899,7 +968,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -907,7 +976,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -915,7 +984,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -923,7 +992,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -931,7 +1000,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -939,7 +1008,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -947,7 +1016,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -955,7 +1024,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -963,7 +1032,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -971,7 +1040,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -979,7 +1048,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -987,7 +1056,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -995,7 +1064,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1003,7 +1072,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1011,7 +1080,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1019,7 +1088,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1027,7 +1096,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1035,7 +1104,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1043,7 +1112,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1066,7 +1135,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1074,7 +1143,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1082,7 +1151,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1090,7 +1159,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1098,7 +1167,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1106,7 +1175,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1114,7 +1183,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1122,7 +1191,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1130,7 +1199,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1138,7 +1207,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1146,7 +1215,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1154,7 +1223,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1162,7 +1231,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1170,7 +1239,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1178,7 +1247,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1186,7 +1255,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1194,7 +1263,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1202,7 +1271,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1210,7 +1279,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1218,7 +1287,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1241,26 +1310,26 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>206.9001953125</v>
+        <v>316.7001953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>192.16</v>
+        <v>293.69970703125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>187.94017578125</v>
+        <v>283.8203125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1268,63 +1337,63 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>183.93998046875</v>
+        <v>273.72021484375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B6">
-        <v>175.86009765625</v>
+        <v>271.39990234375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>173.93998046875</v>
+        <v>266.97998046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8">
-        <v>172.86009765625</v>
+        <v>264.39990234375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>169.58017578125</v>
+        <v>259.72021484375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>163.2698828125</v>
+        <v>250.66015625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>159.93998046875</v>
+        <v>239.99951171875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>155.06009765625</v>
+        <v>234.11962890625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1332,15 +1401,15 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>151.65015625</v>
+        <v>233.659912109375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B14">
-        <v>151.3601953125</v>
+        <v>222.19970703125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1348,55 +1417,55 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>150.0101953125</v>
+        <v>217.30029296875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>148.94017578125</v>
+        <v>217.0205078125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B17">
-        <v>143.920029296875</v>
+        <v>215.169921875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B18">
-        <v>143.44017578125</v>
+        <v>213.72021484375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>140.47994140625</v>
+        <v>209.490234375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20">
-        <v>125.719931640625</v>
+        <v>204.160400390625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21">
-        <v>110.28017578125</v>
+        <v>150.97998046875</v>
       </c>
     </row>
   </sheetData>
@@ -1416,7 +1485,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1424,7 +1493,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1432,7 +1501,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1440,7 +1509,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1448,7 +1517,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1456,7 +1525,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1464,7 +1533,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1472,7 +1541,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1480,7 +1549,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1488,7 +1557,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1496,7 +1565,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1504,7 +1573,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1512,7 +1581,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1520,7 +1589,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1528,7 +1597,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1536,7 +1605,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1544,7 +1613,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1552,7 +1621,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1560,7 +1629,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1568,7 +1637,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1591,7 +1660,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1599,7 +1668,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1607,7 +1676,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1615,7 +1684,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1623,7 +1692,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1631,7 +1700,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1639,7 +1708,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1647,7 +1716,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1655,7 +1724,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1663,7 +1732,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1671,7 +1740,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1679,7 +1748,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1687,7 +1756,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1695,7 +1764,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1703,7 +1772,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1711,7 +1780,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1719,7 +1788,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1727,7 +1796,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1735,7 +1804,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1743,7 +1812,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1766,7 +1835,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1774,7 +1843,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1782,7 +1851,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1790,7 +1859,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1798,7 +1867,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1806,7 +1875,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1814,7 +1883,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1822,7 +1891,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1830,7 +1899,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1838,7 +1907,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1846,7 +1915,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1854,7 +1923,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1862,7 +1931,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1870,7 +1939,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1878,7 +1947,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1886,7 +1955,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1894,7 +1963,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1902,7 +1971,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1910,7 +1979,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1918,7 +1987,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1941,7 +2010,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1949,7 +2018,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1957,7 +2026,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1965,7 +2034,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1973,7 +2042,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1981,7 +2050,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1989,7 +2058,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1997,7 +2066,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2005,7 +2074,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2013,7 +2082,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2021,7 +2090,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2029,7 +2098,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2037,7 +2106,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2045,7 +2114,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2053,7 +2122,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2061,7 +2130,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2069,7 +2138,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2077,7 +2146,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2085,7 +2154,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2093,7 +2162,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -485,7 +485,7 @@
         <v>73.259765625</v>
       </c>
       <c r="E2">
-        <v>73.259765625</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -502,7 +502,7 @@
         <v>91.66015625</v>
       </c>
       <c r="E3">
-        <v>91.66015625</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -519,7 +519,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="E4">
-        <v>84.56005859375</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -536,7 +536,7 @@
         <v>79.740234375</v>
       </c>
       <c r="E5">
-        <v>79.740234375</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -553,7 +553,7 @@
         <v>109</v>
       </c>
       <c r="E6">
-        <v>109</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -570,7 +570,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>79.259765625</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -587,7 +587,7 @@
         <v>42.14990234375</v>
       </c>
       <c r="E8">
-        <v>42.14990234375</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -604,7 +604,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>71.64013671875</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -621,7 +621,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>90.4599609375</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -638,7 +638,7 @@
         <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>65.66015625</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -655,7 +655,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>97.39990234375</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -672,7 +672,7 @@
         <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>100.06005859375</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -689,7 +689,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>87.4599609375</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -706,7 +706,7 @@
         <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>88.93994140625</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -723,7 +723,7 @@
         <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>57.0400390625</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -740,7 +740,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>87.39013671875</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -757,7 +757,7 @@
         <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>73.06005859375</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -774,7 +774,7 @@
         <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>64.35986328125</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -791,7 +791,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>78.259765625</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -808,7 +808,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>105.759765625</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1313,15 +1313,15 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>316.7001953125</v>
+        <v>269.1501953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>293.69970703125</v>
+        <v>235.130078125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1329,15 +1329,15 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>283.8203125</v>
+        <v>232.21015625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B5">
-        <v>273.72021484375</v>
+        <v>231.73994140625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1345,23 +1345,23 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>271.39990234375</v>
+        <v>228.53994140625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>266.97998046875</v>
+        <v>224.80994140625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>264.39990234375</v>
+        <v>220.26974609375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1369,55 +1369,55 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>259.72021484375</v>
+        <v>219.56015625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>250.66015625</v>
+        <v>214.36015625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>239.99951171875</v>
+        <v>205.24005859375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>234.11962890625</v>
+        <v>201.519970703125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>233.659912109375</v>
+        <v>201.3901953125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>222.19970703125</v>
+        <v>197.55986328125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>217.30029296875</v>
+        <v>193.11001953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1425,15 +1425,15 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>217.0205078125</v>
+        <v>190.7103515625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B17">
-        <v>215.169921875</v>
+        <v>189.08994140625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1441,15 +1441,15 @@
         <v>11</v>
       </c>
       <c r="B18">
-        <v>213.72021484375</v>
+        <v>187.380078125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>209.490234375</v>
+        <v>183.290234375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>204.160400390625</v>
+        <v>154.020166015625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1465,7 +1465,7 @@
         <v>10</v>
       </c>
       <c r="B21">
-        <v>150.97998046875</v>
+        <v>140.930078125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -485,7 +485,7 @@
         <v>73.259765625</v>
       </c>
       <c r="E2">
-        <v>40.15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -502,7 +502,7 @@
         <v>91.66015625</v>
       </c>
       <c r="E3">
-        <v>40.05</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -519,7 +519,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="E4">
-        <v>44.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -536,7 +536,7 @@
         <v>79.740234375</v>
       </c>
       <c r="E5">
-        <v>29.6</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -553,7 +553,7 @@
         <v>109</v>
       </c>
       <c r="E6">
-        <v>61.45</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -570,7 +570,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>59.53</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -587,7 +587,7 @@
         <v>42.14990234375</v>
       </c>
       <c r="E8">
-        <v>32.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -604,7 +604,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>45.3</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -621,7 +621,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>50.87</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -638,7 +638,7 @@
         <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>39.35</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -655,7 +655,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -672,7 +672,7 @@
         <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>40.7</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -689,7 +689,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>44.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -706,7 +706,7 @@
         <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>56.8</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -723,7 +723,7 @@
         <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>48.94</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -740,7 +740,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>29.84</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -757,7 +757,7 @@
         <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>39.05</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -774,7 +774,7 @@
         <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>54.43</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -791,7 +791,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>41.7</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -808,7 +808,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1313,7 +1313,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>269.1501953125</v>
+        <v>283.6601953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1321,7 +1321,7 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>235.130078125</v>
+        <v>251.230078125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1329,23 +1329,23 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>232.21015625</v>
+        <v>243.76015625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>231.73994140625</v>
+        <v>241.93994140625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B6">
-        <v>228.53994140625</v>
+        <v>234.58994140625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1353,7 +1353,7 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>224.80994140625</v>
+        <v>230.61994140625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>220.26974609375</v>
+        <v>229.46974609375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1369,7 +1369,7 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>219.56015625</v>
+        <v>222.66015625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1377,7 +1377,7 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>214.36015625</v>
+        <v>217.21015625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1385,7 +1385,7 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>205.24005859375</v>
+        <v>211.94005859375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1393,55 +1393,55 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>201.519970703125</v>
+        <v>204.129970703125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>201.3901953125</v>
+        <v>200.43001953125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>197.55986328125</v>
+        <v>200.2901953125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>193.11001953125</v>
+        <v>199.2603515625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B16">
-        <v>190.7103515625</v>
+        <v>199.20986328125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>189.08994140625</v>
+        <v>198.240078125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B18">
-        <v>187.380078125</v>
+        <v>191.93994140625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1449,7 +1449,7 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>183.290234375</v>
+        <v>186.800234375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>154.020166015625</v>
+        <v>168.770166015625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1465,7 +1465,7 @@
         <v>10</v>
       </c>
       <c r="B21">
-        <v>140.930078125</v>
+        <v>139.630078125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -485,7 +485,7 @@
         <v>73.259765625</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -502,7 +502,7 @@
         <v>91.66015625</v>
       </c>
       <c r="E3">
-        <v>51.6</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -519,7 +519,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="E4">
-        <v>47.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -536,7 +536,7 @@
         <v>79.740234375</v>
       </c>
       <c r="E5">
-        <v>44.35</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -553,7 +553,7 @@
         <v>109</v>
       </c>
       <c r="E6">
-        <v>75.95999999999999</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -570,7 +570,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>68.73</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -604,7 +604,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>56.16</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -621,7 +621,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>56.68</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -638,7 +638,7 @@
         <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>47.9</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -672,7 +672,7 @@
         <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>43.55</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -689,7 +689,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>58</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -723,7 +723,7 @@
         <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>47.84</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -740,7 +740,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>37.16</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -791,7 +791,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>43.35</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -808,7 +808,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1313,39 +1313,39 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>283.6601953125</v>
+        <v>329.4601953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>251.230078125</v>
+        <v>269.39015625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>243.76015625</v>
+        <v>265.36994140625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B5">
-        <v>241.93994140625</v>
+        <v>253.08994140625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>234.58994140625</v>
+        <v>251.230078125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1353,7 +1353,7 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>230.61994140625</v>
+        <v>249.99994140625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1361,39 +1361,39 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>229.46974609375</v>
+        <v>247.16974609375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>222.66015625</v>
+        <v>236.41015625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B10">
-        <v>217.21015625</v>
+        <v>230.16015625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>211.94005859375</v>
+        <v>224.6901953125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>204.129970703125</v>
+        <v>211.94005859375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1401,31 +1401,31 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>200.43001953125</v>
+        <v>205.83001953125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>200.2901953125</v>
+        <v>204.129970703125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>199.2603515625</v>
+        <v>201.40986328125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>199.20986328125</v>
+        <v>200.8103515625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1433,7 +1433,7 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>198.240078125</v>
+        <v>198.440078125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1441,7 +1441,7 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>191.93994140625</v>
+        <v>198.36994140625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1457,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>168.770166015625</v>
+        <v>185.770166015625</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="26">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>Rodada 4</t>
+  </si>
+  <si>
+    <t>Rodada 5</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -454,10 +457,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,10 +473,13 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -485,12 +491,15 @@
         <v>73.259765625</v>
       </c>
       <c r="E2">
-        <v>49.43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>49.429931640625</v>
+      </c>
+      <c r="F2">
+        <v>49.429931640625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -502,12 +511,15 @@
         <v>91.66015625</v>
       </c>
       <c r="E3">
-        <v>77.23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>77.22998046875</v>
+      </c>
+      <c r="F3">
+        <v>77.22998046875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -521,10 +533,13 @@
       <c r="E4">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -536,12 +551,15 @@
         <v>79.740234375</v>
       </c>
       <c r="E5">
-        <v>61.35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>61.35009765625</v>
+      </c>
+      <c r="F5">
+        <v>61.35009765625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -553,12 +571,15 @@
         <v>109</v>
       </c>
       <c r="E6">
-        <v>121.76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>121.759765625</v>
+      </c>
+      <c r="F6">
+        <v>121.759765625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -570,12 +591,15 @@
         <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>86.43000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>86.43017578125</v>
+      </c>
+      <c r="F7">
+        <v>86.43017578125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -587,12 +611,15 @@
         <v>42.14990234375</v>
       </c>
       <c r="E8">
-        <v>30.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>30.800048828125</v>
+      </c>
+      <c r="F8">
+        <v>30.800048828125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -604,12 +631,15 @@
         <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>56.36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>56.360107421875</v>
+      </c>
+      <c r="F9">
+        <v>56.360107421875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -621,12 +651,15 @@
         <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>76.06</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>76.06005859375</v>
+      </c>
+      <c r="F10">
+        <v>76.06005859375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -638,12 +671,15 @@
         <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>49.45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>49.449951171875</v>
+      </c>
+      <c r="F11">
+        <v>49.449951171875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -655,12 +691,15 @@
         <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>81.65000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>81.64990234375</v>
+      </c>
+      <c r="F12">
+        <v>81.64990234375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -674,10 +713,13 @@
       <c r="E13">
         <v>62.75</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>62.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -689,12 +731,15 @@
         <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>81.43000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>81.43017578125</v>
+      </c>
+      <c r="F14">
+        <v>81.43017578125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -706,12 +751,15 @@
         <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>59.41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>59.409912109375</v>
+      </c>
+      <c r="F15">
+        <v>59.409912109375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -723,12 +771,15 @@
         <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>72.23999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>72.240234375</v>
+      </c>
+      <c r="F16">
+        <v>72.240234375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -740,12 +791,15 @@
         <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>42.56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>42.56005859375</v>
+      </c>
+      <c r="F17">
+        <v>42.56005859375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -757,12 +811,15 @@
         <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>42.56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>42.56005859375</v>
+      </c>
+      <c r="F18">
+        <v>42.56005859375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -774,12 +831,15 @@
         <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>61.13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>61.1298828125</v>
+      </c>
+      <c r="F19">
+        <v>61.1298828125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -791,12 +851,15 @@
         <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>45.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>45.550048828125</v>
+      </c>
+      <c r="F20">
+        <v>45.550048828125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -808,12 +871,15 @@
         <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>65.15000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>65.14990234375</v>
+      </c>
+      <c r="F21">
+        <v>65.14990234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -825,6 +891,9 @@
         <v>0</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>0</v>
       </c>
     </row>
@@ -840,107 +909,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -960,7 +1029,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -968,7 +1037,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -976,7 +1045,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -984,7 +1053,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -992,7 +1061,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1000,7 +1069,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1008,7 +1077,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1016,7 +1085,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1024,7 +1093,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1032,7 +1101,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1040,7 +1109,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1048,7 +1117,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1056,7 +1125,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1064,7 +1133,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1072,7 +1141,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1080,7 +1149,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1088,7 +1157,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1096,7 +1165,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1104,7 +1173,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1112,7 +1181,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1135,7 +1204,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1143,7 +1212,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1151,7 +1220,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1159,7 +1228,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1167,7 +1236,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1175,7 +1244,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1183,7 +1252,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1191,7 +1260,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1199,7 +1268,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1207,7 +1276,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1215,7 +1284,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1223,7 +1292,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1231,7 +1300,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1239,7 +1308,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1247,7 +1316,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1255,7 +1324,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1263,7 +1332,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1271,7 +1340,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1279,7 +1348,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1287,7 +1356,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1310,63 +1379,63 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>329.4601953125</v>
+        <v>329.4599609375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>269.39015625</v>
+        <v>269.39013671875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4">
-        <v>265.36994140625</v>
+        <v>265.3701171875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>253.08994140625</v>
+        <v>253.08984375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>251.230078125</v>
+        <v>251.22998046875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>249.99994140625</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>247.16974609375</v>
+        <v>247.169921875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1374,7 +1443,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1382,90 +1451,90 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
-        <v>224.6901953125</v>
+        <v>224.6904296875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>211.94005859375</v>
+        <v>211.93994140625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
-        <v>205.83001953125</v>
+        <v>205.830078125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>204.129970703125</v>
+        <v>204.1298828125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>201.40986328125</v>
+        <v>201.409912109375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>200.8103515625</v>
+        <v>200.810302734375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17">
-        <v>198.440078125</v>
+        <v>198.440185546875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18">
-        <v>198.36994140625</v>
+        <v>198.369873046875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
-        <v>186.800234375</v>
+        <v>186.80029296875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20">
-        <v>185.770166015625</v>
+        <v>185.770263671875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21">
-        <v>139.630078125</v>
+        <v>139.630126953125</v>
       </c>
     </row>
   </sheetData>
@@ -1485,66 +1554,66 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>121.759765625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>86.43017578125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>81.43017578125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>77.22998046875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>76.06005859375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>72.240234375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1552,31 +1621,31 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>61.35009765625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>61.1298828125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>59.409912109375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1584,63 +1653,63 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>56.360107421875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>49.449951171875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>49.429931640625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>45.550048828125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>42.56005859375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>42.56005859375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>30.800048828125</v>
       </c>
     </row>
   </sheetData>
@@ -1660,7 +1729,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1668,7 +1737,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1676,7 +1745,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1684,7 +1753,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1692,7 +1761,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1700,7 +1769,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1708,7 +1777,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1716,7 +1785,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1724,7 +1793,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1732,7 +1801,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1740,7 +1809,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1748,7 +1817,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1756,7 +1825,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1764,7 +1833,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1772,7 +1841,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1780,7 +1849,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1788,7 +1857,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1796,7 +1865,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1804,7 +1873,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1812,7 +1881,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1835,7 +1904,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1843,7 +1912,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1851,7 +1920,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1859,7 +1928,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1867,7 +1936,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1875,7 +1944,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1883,7 +1952,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1891,7 +1960,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1899,7 +1968,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1907,7 +1976,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1915,7 +1984,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1923,7 +1992,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1931,7 +2000,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1939,7 +2008,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1947,7 +2016,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1955,7 +2024,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1963,7 +2032,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1971,7 +2040,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1979,7 +2048,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1987,7 +2056,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2010,7 +2079,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2018,7 +2087,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2026,7 +2095,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2034,7 +2103,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2042,7 +2111,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2050,7 +2119,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2058,7 +2127,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2066,7 +2135,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2074,7 +2143,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2082,7 +2151,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2090,7 +2159,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2098,7 +2167,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2106,7 +2175,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2114,7 +2183,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2122,7 +2191,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2130,7 +2199,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2138,7 +2207,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2146,7 +2215,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2154,7 +2223,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2162,7 +2231,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="25">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>GaúchoDaFronteira F.C</t>
-  </si>
-  <si>
-    <t>GE Bebum</t>
   </si>
   <si>
     <t>GrioTeam</t>
@@ -457,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -494,7 +491,7 @@
         <v>49.429931640625</v>
       </c>
       <c r="F2">
-        <v>49.429931640625</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -514,7 +511,7 @@
         <v>77.22998046875</v>
       </c>
       <c r="F3">
-        <v>77.22998046875</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -534,7 +531,7 @@
         <v>55</v>
       </c>
       <c r="F4">
-        <v>55</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -554,7 +551,7 @@
         <v>61.35009765625</v>
       </c>
       <c r="F5">
-        <v>61.35009765625</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -574,7 +571,7 @@
         <v>121.759765625</v>
       </c>
       <c r="F6">
-        <v>121.759765625</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -594,7 +591,7 @@
         <v>86.43017578125</v>
       </c>
       <c r="F7">
-        <v>86.43017578125</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -614,7 +611,7 @@
         <v>30.800048828125</v>
       </c>
       <c r="F8">
-        <v>30.800048828125</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -622,19 +619,19 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>56.050048828125</v>
+        <v>61.56005859375</v>
       </c>
       <c r="C9">
-        <v>70.43994140625</v>
+        <v>83.47998046875</v>
       </c>
       <c r="D9">
-        <v>71.64013671875</v>
+        <v>90.4599609375</v>
       </c>
       <c r="E9">
-        <v>56.360107421875</v>
+        <v>76.06005859375</v>
       </c>
       <c r="F9">
-        <v>56.360107421875</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -642,19 +639,19 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>61.56005859375</v>
+        <v>54.050048828125</v>
       </c>
       <c r="C10">
-        <v>83.47998046875</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D10">
-        <v>90.4599609375</v>
+        <v>65.66015625</v>
       </c>
       <c r="E10">
-        <v>76.06005859375</v>
+        <v>49.449951171875</v>
       </c>
       <c r="F10">
-        <v>76.06005859375</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -662,19 +659,19 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>54.050048828125</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C11">
-        <v>85.7001953125</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D11">
-        <v>65.66015625</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E11">
-        <v>49.449951171875</v>
+        <v>81.64990234375</v>
       </c>
       <c r="F11">
-        <v>49.449951171875</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -682,19 +679,19 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>47.860107421875</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C12">
-        <v>72.18017578125</v>
+        <v>73.60009765625</v>
       </c>
       <c r="D12">
-        <v>97.39990234375</v>
+        <v>100.06005859375</v>
       </c>
       <c r="E12">
-        <v>81.64990234375</v>
+        <v>62.75</v>
       </c>
       <c r="F12">
-        <v>81.64990234375</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -702,19 +699,19 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>55.659912109375</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C13">
-        <v>73.60009765625</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D13">
-        <v>100.06005859375</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E13">
-        <v>62.75</v>
+        <v>81.43017578125</v>
       </c>
       <c r="F13">
-        <v>62.75</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -722,19 +719,19 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>62.56005859375</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C14">
-        <v>96.47998046875</v>
+        <v>55.780029296875</v>
       </c>
       <c r="D14">
-        <v>87.4599609375</v>
+        <v>88.93994140625</v>
       </c>
       <c r="E14">
-        <v>81.43017578125</v>
+        <v>59.409912109375</v>
       </c>
       <c r="F14">
-        <v>81.43017578125</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -742,19 +739,19 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>55.659912109375</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>55.780029296875</v>
+        <v>95.41015625</v>
       </c>
       <c r="D15">
-        <v>88.93994140625</v>
+        <v>57.0400390625</v>
       </c>
       <c r="E15">
-        <v>59.409912109375</v>
+        <v>72.240234375</v>
       </c>
       <c r="F15">
-        <v>59.409912109375</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -762,19 +759,19 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>60.60009765625</v>
       </c>
       <c r="C16">
-        <v>95.41015625</v>
+        <v>75.8798828125</v>
       </c>
       <c r="D16">
-        <v>57.0400390625</v>
+        <v>87.39013671875</v>
       </c>
       <c r="E16">
-        <v>72.240234375</v>
+        <v>42.56005859375</v>
       </c>
       <c r="F16">
-        <v>72.240234375</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -782,19 +779,19 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>60.60009765625</v>
+        <v>61.159912109375</v>
       </c>
       <c r="C17">
-        <v>75.8798828125</v>
+        <v>71.18017578125</v>
       </c>
       <c r="D17">
-        <v>87.39013671875</v>
+        <v>73.06005859375</v>
       </c>
       <c r="E17">
         <v>42.56005859375</v>
       </c>
       <c r="F17">
-        <v>42.56005859375</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -802,19 +799,19 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>61.159912109375</v>
+        <v>67.16015625</v>
       </c>
       <c r="C18">
-        <v>71.18017578125</v>
+        <v>86.4501953125</v>
       </c>
       <c r="D18">
-        <v>73.06005859375</v>
+        <v>64.35986328125</v>
       </c>
       <c r="E18">
-        <v>42.56005859375</v>
+        <v>61.1298828125</v>
       </c>
       <c r="F18">
-        <v>42.56005859375</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -822,19 +819,19 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>67.16015625</v>
+        <v>54.89990234375</v>
       </c>
       <c r="C19">
-        <v>86.4501953125</v>
+        <v>77.60009765625</v>
       </c>
       <c r="D19">
-        <v>64.35986328125</v>
+        <v>78.259765625</v>
       </c>
       <c r="E19">
-        <v>61.1298828125</v>
+        <v>45.550048828125</v>
       </c>
       <c r="F19">
-        <v>61.1298828125</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -842,19 +839,19 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>54.89990234375</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C20">
-        <v>77.60009765625</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D20">
-        <v>78.259765625</v>
+        <v>105.759765625</v>
       </c>
       <c r="E20">
-        <v>45.550048828125</v>
+        <v>65.14990234375</v>
       </c>
       <c r="F20">
-        <v>45.550048828125</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -862,38 +859,18 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>68.06005859375</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>82.18017578125</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>105.759765625</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>65.14990234375</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>65.14990234375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
         <v>0</v>
       </c>
     </row>
@@ -904,7 +881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:A22"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:1">
@@ -1005,11 +982,6 @@
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1019,7 +991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1037,7 +1009,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1045,7 +1017,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1053,7 +1025,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1061,7 +1033,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1069,7 +1041,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1077,7 +1049,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1085,7 +1057,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1093,7 +1065,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1101,7 +1073,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1109,7 +1081,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1117,7 +1089,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1125,7 +1097,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1133,7 +1105,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1141,7 +1113,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1149,7 +1121,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1157,7 +1129,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1165,7 +1137,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1173,17 +1145,9 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -1194,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1220,7 +1184,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1228,7 +1192,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1260,7 +1224,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1268,7 +1232,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1276,7 +1240,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1284,7 +1248,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1292,15 +1256,15 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>56.050048828125</v>
+        <v>55.659912109375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1308,39 +1272,39 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>55.659912109375</v>
+        <v>54.89990234375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>54.89990234375</v>
+        <v>54.050048828125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>54.050048828125</v>
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B18">
-        <v>53.659912109375</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1348,17 +1312,9 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>47.860107421875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -1369,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1395,7 +1351,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1403,7 +1359,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1411,7 +1367,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1419,7 +1375,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1435,7 +1391,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1451,7 +1407,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1459,7 +1415,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1467,7 +1423,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1475,7 +1431,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1483,7 +1439,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1491,7 +1447,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1499,41 +1455,33 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B17">
-        <v>198.440185546875</v>
+        <v>198.369873046875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>198.369873046875</v>
+        <v>186.80029296875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B19">
-        <v>186.80029296875</v>
+        <v>185.770263671875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20">
-        <v>185.770263671875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21">
         <v>139.630126953125</v>
       </c>
     </row>
@@ -1544,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1554,162 +1502,154 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>121.759765625</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>86.43017578125</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B4">
-        <v>81.64990234375</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>81.43017578125</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>77.22998046875</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>76.06005859375</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>72.240234375</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B9">
-        <v>65.14990234375</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>62.75</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>61.35009765625</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B12">
-        <v>61.1298828125</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B13">
-        <v>59.409912109375</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>56.360107421875</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>55</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16">
-        <v>49.449951171875</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B17">
-        <v>49.429931640625</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>45.550048828125</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B19">
-        <v>42.56005859375</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B20">
-        <v>42.56005859375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21">
-        <v>30.800048828125</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1737,7 +1677,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1745,7 +1685,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1753,7 +1693,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1761,7 +1701,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1769,7 +1709,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1777,7 +1717,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1785,7 +1725,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1793,7 +1733,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1801,7 +1741,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1809,7 +1749,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1817,7 +1757,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1825,7 +1765,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1833,7 +1773,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1841,7 +1781,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1849,7 +1789,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1857,7 +1797,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1865,7 +1805,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1873,17 +1813,9 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -1894,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1912,7 +1844,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1920,7 +1852,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1928,7 +1860,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1936,7 +1868,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1944,7 +1876,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1952,7 +1884,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1960,7 +1892,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1968,7 +1900,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1976,7 +1908,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1984,7 +1916,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1992,7 +1924,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2000,7 +1932,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2008,7 +1940,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2016,7 +1948,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2024,7 +1956,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2032,7 +1964,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2040,7 +1972,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2048,17 +1980,9 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -2069,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2087,7 +2011,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2095,7 +2019,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2103,7 +2027,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2111,7 +2035,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2119,7 +2043,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2127,7 +2051,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2135,7 +2059,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2143,7 +2067,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2151,7 +2075,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2159,7 +2083,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2167,7 +2091,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2175,7 +2099,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2183,7 +2107,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2191,7 +2115,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2199,7 +2123,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2207,7 +2131,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2215,7 +2139,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2223,17 +2147,9 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
         <v>0</v>
       </c>
     </row>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="26">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Rodada 5</t>
+  </si>
+  <si>
+    <t>Rodada 6</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -454,10 +457,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,10 +476,13 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -491,12 +497,15 @@
         <v>49.429931640625</v>
       </c>
       <c r="F2">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>87.919921875</v>
+      </c>
+      <c r="G2">
+        <v>87.919921875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -511,12 +520,15 @@
         <v>77.22998046875</v>
       </c>
       <c r="F3">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>78.47021484375</v>
+      </c>
+      <c r="G3">
+        <v>78.47021484375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -531,12 +543,15 @@
         <v>55</v>
       </c>
       <c r="F4">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>63.8701171875</v>
+      </c>
+      <c r="G4">
+        <v>63.8701171875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -551,12 +566,15 @@
         <v>61.35009765625</v>
       </c>
       <c r="F5">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>82.31982421875</v>
+      </c>
+      <c r="G5">
+        <v>82.31982421875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -571,12 +589,15 @@
         <v>121.759765625</v>
       </c>
       <c r="F6">
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>93.06982421875</v>
+      </c>
+      <c r="G6">
+        <v>93.06982421875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -591,12 +612,15 @@
         <v>86.43017578125</v>
       </c>
       <c r="F7">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>86.419921875</v>
+      </c>
+      <c r="G7">
+        <v>86.419921875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -611,12 +635,15 @@
         <v>30.800048828125</v>
       </c>
       <c r="F8">
-        <v>39.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>52.5400390625</v>
+      </c>
+      <c r="G8">
+        <v>52.5400390625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>61.56005859375</v>
@@ -631,12 +658,15 @@
         <v>76.06005859375</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>41.169921875</v>
+      </c>
+      <c r="G9">
+        <v>41.169921875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>54.050048828125</v>
@@ -651,12 +681,15 @@
         <v>49.449951171875</v>
       </c>
       <c r="F10">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>87.72021484375</v>
+      </c>
+      <c r="G10">
+        <v>87.72021484375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>47.860107421875</v>
@@ -671,12 +704,15 @@
         <v>81.64990234375</v>
       </c>
       <c r="F11">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>84.81982421875</v>
+      </c>
+      <c r="G11">
+        <v>84.81982421875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>55.659912109375</v>
@@ -691,12 +727,15 @@
         <v>62.75</v>
       </c>
       <c r="F12">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>77.22021484375</v>
+      </c>
+      <c r="G12">
+        <v>77.22021484375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>62.56005859375</v>
@@ -711,12 +750,15 @@
         <v>81.43017578125</v>
       </c>
       <c r="F13">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>85.669921875</v>
+      </c>
+      <c r="G13">
+        <v>85.669921875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -731,12 +773,15 @@
         <v>59.409912109375</v>
       </c>
       <c r="F14">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>84.6201171875</v>
+      </c>
+      <c r="G14">
+        <v>84.6201171875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -751,12 +796,15 @@
         <v>72.240234375</v>
       </c>
       <c r="F15">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>69.77001953125</v>
+      </c>
+      <c r="G15">
+        <v>69.77001953125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>60.60009765625</v>
@@ -771,12 +819,15 @@
         <v>42.56005859375</v>
       </c>
       <c r="F16">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>49.77001953125</v>
+      </c>
+      <c r="G16">
+        <v>49.77001953125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>61.159912109375</v>
@@ -791,12 +842,15 @@
         <v>42.56005859375</v>
       </c>
       <c r="F17">
-        <v>17.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>70.85986328125</v>
+      </c>
+      <c r="G17">
+        <v>70.85986328125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>67.16015625</v>
@@ -811,12 +865,15 @@
         <v>61.1298828125</v>
       </c>
       <c r="F18">
-        <v>25.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>72.759765625</v>
+      </c>
+      <c r="G18">
+        <v>72.759765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>54.89990234375</v>
@@ -831,12 +888,15 @@
         <v>45.550048828125</v>
       </c>
       <c r="F19">
-        <v>17.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>77.6201171875</v>
+      </c>
+      <c r="G19">
+        <v>77.6201171875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>68.06005859375</v>
@@ -851,12 +911,15 @@
         <v>65.14990234375</v>
       </c>
       <c r="F20">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>93.02001953125</v>
+      </c>
+      <c r="G20">
+        <v>93.02001953125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -871,6 +934,9 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>0</v>
       </c>
     </row>
@@ -886,102 +952,102 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1001,7 +1067,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1009,7 +1075,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1017,7 +1083,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1025,7 +1091,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1033,7 +1099,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1041,7 +1107,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1049,7 +1115,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1057,7 +1123,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1065,7 +1131,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1073,7 +1139,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1081,7 +1147,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1089,7 +1155,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1097,7 +1163,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1105,7 +1171,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1113,7 +1179,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1121,7 +1187,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1129,7 +1195,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1137,7 +1203,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1145,7 +1211,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1168,7 +1234,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1176,7 +1242,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1184,7 +1250,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1192,7 +1258,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1200,7 +1266,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1208,7 +1274,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1216,7 +1282,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1224,7 +1290,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1232,7 +1298,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1240,7 +1306,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1248,7 +1314,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1256,7 +1322,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1264,7 +1330,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1272,7 +1338,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>54.89990234375</v>
@@ -1280,7 +1346,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>54.050048828125</v>
@@ -1288,7 +1354,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>53.659912109375</v>
@@ -1296,7 +1362,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>47.860107421875</v>
@@ -1304,7 +1370,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1312,7 +1378,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1335,7 +1401,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1343,7 +1409,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1351,7 +1417,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1359,7 +1425,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1367,7 +1433,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1375,7 +1441,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1383,7 +1449,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1391,7 +1457,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1399,7 +1465,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1407,7 +1473,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1415,7 +1481,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1423,7 +1489,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1431,7 +1497,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1439,7 +1505,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1447,7 +1513,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1455,7 +1521,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17">
         <v>198.369873046875</v>
@@ -1463,7 +1529,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>186.80029296875</v>
@@ -1471,7 +1537,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>185.770263671875</v>
@@ -1479,7 +1545,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <v>139.630126953125</v>
@@ -1502,154 +1568,154 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>39.15</v>
+        <v>186.1396484375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>27.6</v>
+        <v>186.0400390625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>25.9</v>
+        <v>175.83984375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>25.7</v>
+        <v>175.4404296875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>22.7</v>
+        <v>172.83984375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>22.7</v>
+        <v>171.33984375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>22.3</v>
+        <v>169.6396484375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>22</v>
+        <v>169.240234375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>17.9</v>
+        <v>164.6396484375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>17.9</v>
+        <v>156.9404296875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>17.6</v>
+        <v>155.240234375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>15.2</v>
+        <v>154.4404296875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>13.8</v>
+        <v>145.51953125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>11.7</v>
+        <v>141.7197265625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>10.7</v>
+        <v>139.5400390625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B17">
-        <v>9.75</v>
+        <v>127.740234375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B18">
-        <v>7.4</v>
+        <v>105.080078125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>6.7</v>
+        <v>99.5400390625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
-        <v>2.2</v>
+        <v>82.33984375</v>
       </c>
     </row>
   </sheetData>
@@ -1669,7 +1735,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1677,7 +1743,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1685,7 +1751,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1693,7 +1759,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1701,7 +1767,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1709,7 +1775,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1717,7 +1783,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1725,7 +1791,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1733,7 +1799,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1741,7 +1807,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1749,7 +1815,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1757,7 +1823,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1765,7 +1831,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1773,7 +1839,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1781,7 +1847,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1789,7 +1855,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1797,7 +1863,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1805,7 +1871,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1813,7 +1879,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1836,7 +1902,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1844,7 +1910,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1852,7 +1918,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1860,7 +1926,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1868,7 +1934,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1876,7 +1942,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1884,7 +1950,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1892,7 +1958,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1900,7 +1966,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1908,7 +1974,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1916,7 +1982,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1924,7 +1990,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1932,7 +1998,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1940,7 +2006,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1948,7 +2014,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1956,7 +2022,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1964,7 +2030,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1972,7 +2038,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1980,7 +2046,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2003,7 +2069,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2011,7 +2077,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2019,7 +2085,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2027,7 +2093,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2035,7 +2101,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2043,7 +2109,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2051,7 +2117,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2059,7 +2125,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2067,7 +2133,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2075,7 +2141,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2083,7 +2149,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2091,7 +2157,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2099,7 +2165,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2107,7 +2173,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2115,7 +2181,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2123,7 +2189,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2131,7 +2197,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2139,7 +2205,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2147,7 +2213,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="27">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>GaúchoDaFronteira F.C</t>
+  </si>
+  <si>
+    <t>GE Xavanchesteer</t>
   </si>
   <si>
     <t>GrioTeam</t>
@@ -457,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -646,22 +649,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>61.56005859375</v>
+        <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>83.47998046875</v>
+        <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>90.4599609375</v>
+        <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>76.06005859375</v>
+        <v>56.360107421875</v>
       </c>
       <c r="F9">
-        <v>41.169921875</v>
+        <v>88.240234375</v>
       </c>
       <c r="G9">
-        <v>41.169921875</v>
+        <v>88.240234375</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -669,22 +672,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>54.050048828125</v>
+        <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>85.7001953125</v>
+        <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>65.66015625</v>
+        <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>49.449951171875</v>
+        <v>76.06005859375</v>
       </c>
       <c r="F10">
-        <v>87.72021484375</v>
+        <v>41.169921875</v>
       </c>
       <c r="G10">
-        <v>87.72021484375</v>
+        <v>41.169921875</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -692,22 +695,22 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>47.860107421875</v>
+        <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>72.18017578125</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>97.39990234375</v>
+        <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>81.64990234375</v>
+        <v>49.449951171875</v>
       </c>
       <c r="F11">
-        <v>84.81982421875</v>
+        <v>87.72021484375</v>
       </c>
       <c r="G11">
-        <v>84.81982421875</v>
+        <v>87.72021484375</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -715,22 +718,22 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>55.659912109375</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>73.60009765625</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>100.06005859375</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>62.75</v>
+        <v>81.64990234375</v>
       </c>
       <c r="F12">
-        <v>77.22021484375</v>
+        <v>84.81982421875</v>
       </c>
       <c r="G12">
-        <v>77.22021484375</v>
+        <v>84.81982421875</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -738,22 +741,22 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>62.56005859375</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>96.47998046875</v>
+        <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>87.4599609375</v>
+        <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>81.43017578125</v>
+        <v>62.75</v>
       </c>
       <c r="F13">
-        <v>85.669921875</v>
+        <v>77.22021484375</v>
       </c>
       <c r="G13">
-        <v>85.669921875</v>
+        <v>77.22021484375</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -761,22 +764,22 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>55.659912109375</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>55.780029296875</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>88.93994140625</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>59.409912109375</v>
+        <v>81.43017578125</v>
       </c>
       <c r="F14">
-        <v>84.6201171875</v>
+        <v>85.669921875</v>
       </c>
       <c r="G14">
-        <v>84.6201171875</v>
+        <v>85.669921875</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -784,22 +787,22 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>95.41015625</v>
+        <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>57.0400390625</v>
+        <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>72.240234375</v>
+        <v>59.409912109375</v>
       </c>
       <c r="F15">
-        <v>69.77001953125</v>
+        <v>84.6201171875</v>
       </c>
       <c r="G15">
-        <v>69.77001953125</v>
+        <v>84.6201171875</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -807,22 +810,22 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>60.60009765625</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>75.8798828125</v>
+        <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>87.39013671875</v>
+        <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>42.56005859375</v>
+        <v>72.240234375</v>
       </c>
       <c r="F16">
-        <v>49.77001953125</v>
+        <v>69.77001953125</v>
       </c>
       <c r="G16">
-        <v>49.77001953125</v>
+        <v>69.77001953125</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -830,22 +833,22 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>61.159912109375</v>
+        <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>71.18017578125</v>
+        <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>73.06005859375</v>
+        <v>87.39013671875</v>
       </c>
       <c r="E17">
         <v>42.56005859375</v>
       </c>
       <c r="F17">
-        <v>70.85986328125</v>
+        <v>49.77001953125</v>
       </c>
       <c r="G17">
-        <v>70.85986328125</v>
+        <v>49.77001953125</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -853,22 +856,22 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>67.16015625</v>
+        <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>86.4501953125</v>
+        <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>64.35986328125</v>
+        <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>61.1298828125</v>
+        <v>42.56005859375</v>
       </c>
       <c r="F18">
-        <v>72.759765625</v>
+        <v>70.85986328125</v>
       </c>
       <c r="G18">
-        <v>72.759765625</v>
+        <v>70.85986328125</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -876,22 +879,22 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>54.89990234375</v>
+        <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>77.60009765625</v>
+        <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>78.259765625</v>
+        <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>45.550048828125</v>
+        <v>61.1298828125</v>
       </c>
       <c r="F19">
-        <v>77.6201171875</v>
+        <v>72.759765625</v>
       </c>
       <c r="G19">
-        <v>77.6201171875</v>
+        <v>72.759765625</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -899,22 +902,22 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>68.06005859375</v>
+        <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>82.18017578125</v>
+        <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>105.759765625</v>
+        <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>65.14990234375</v>
+        <v>45.550048828125</v>
       </c>
       <c r="F20">
-        <v>93.02001953125</v>
+        <v>77.6201171875</v>
       </c>
       <c r="G20">
-        <v>93.02001953125</v>
+        <v>77.6201171875</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -922,21 +925,44 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>65.14990234375</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>93.02001953125</v>
       </c>
       <c r="G21">
+        <v>93.02001953125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>0</v>
       </c>
     </row>
@@ -947,7 +973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:A21"/>
+  <dimension ref="A2:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:1">
@@ -1048,6 +1074,11 @@
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1075,7 +1106,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1083,7 +1114,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1091,7 +1122,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1099,7 +1130,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1107,7 +1138,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1115,7 +1146,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1123,7 +1154,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1131,7 +1162,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1139,7 +1170,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1147,7 +1178,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1155,7 +1186,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1163,7 +1194,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1171,7 +1202,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1179,7 +1210,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1187,7 +1218,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1195,7 +1226,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1203,7 +1234,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1211,9 +1242,17 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -1224,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1250,7 +1289,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1258,7 +1297,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1290,7 +1329,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1298,7 +1337,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1306,7 +1345,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1314,7 +1353,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1322,15 +1361,15 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13">
-        <v>55.659912109375</v>
+        <v>56.050048828125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1338,39 +1377,39 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>54.89990234375</v>
+        <v>55.659912109375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B16">
-        <v>54.050048828125</v>
+        <v>54.89990234375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>53.659912109375</v>
+        <v>54.050048828125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B18">
-        <v>47.860107421875</v>
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1378,9 +1417,17 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20">
+        <v>47.860107421875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -1391,7 +1438,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1417,7 +1464,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1425,7 +1472,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1433,7 +1480,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1441,7 +1488,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1457,7 +1504,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1473,7 +1520,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1481,7 +1528,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1489,7 +1536,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1497,7 +1544,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1505,7 +1552,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1513,7 +1560,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1521,33 +1568,41 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B17">
-        <v>198.369873046875</v>
+        <v>198.440185546875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B18">
-        <v>186.80029296875</v>
+        <v>198.369873046875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>185.770263671875</v>
+        <v>186.80029296875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20">
+        <v>185.770263671875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>139.630126953125</v>
       </c>
     </row>
@@ -1558,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1576,7 +1631,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>186.0400390625</v>
@@ -1584,137 +1639,145 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>175.83984375</v>
+        <v>176.48046875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>175.4404296875</v>
+        <v>175.83984375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>172.83984375</v>
+        <v>175.4404296875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B7">
-        <v>171.33984375</v>
+        <v>172.83984375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>169.6396484375</v>
+        <v>171.33984375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>169.240234375</v>
+        <v>169.6396484375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>164.6396484375</v>
+        <v>169.240234375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>156.9404296875</v>
+        <v>164.6396484375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B12">
-        <v>155.240234375</v>
+        <v>156.9404296875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>154.4404296875</v>
+        <v>155.240234375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>145.51953125</v>
+        <v>154.4404296875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>141.7197265625</v>
+        <v>145.51953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16">
-        <v>139.5400390625</v>
+        <v>141.7197265625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B17">
-        <v>127.740234375</v>
+        <v>139.5400390625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B18">
-        <v>105.080078125</v>
+        <v>127.740234375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B19">
-        <v>99.5400390625</v>
+        <v>105.080078125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B20">
+        <v>99.5400390625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21">
         <v>82.33984375</v>
       </c>
     </row>
@@ -1725,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1743,7 +1806,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1751,7 +1814,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1759,7 +1822,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1767,7 +1830,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1775,7 +1838,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1783,7 +1846,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1791,7 +1854,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1799,7 +1862,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1807,7 +1870,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1815,7 +1878,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1823,7 +1886,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1831,7 +1894,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1839,7 +1902,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1847,7 +1910,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1855,7 +1918,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1863,7 +1926,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1871,7 +1934,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1879,9 +1942,17 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -1892,7 +1963,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1910,7 +1981,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1918,7 +1989,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1926,7 +1997,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1934,7 +2005,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1942,7 +2013,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1950,7 +2021,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1958,7 +2029,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1966,7 +2037,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1974,7 +2045,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1982,7 +2053,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1990,7 +2061,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1998,7 +2069,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2006,7 +2077,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2014,7 +2085,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2022,7 +2093,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2030,7 +2101,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2038,7 +2109,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2046,9 +2117,17 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
         <v>0</v>
       </c>
     </row>
@@ -2059,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2077,7 +2156,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2085,7 +2164,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2093,7 +2172,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2101,7 +2180,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2109,7 +2188,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2117,7 +2196,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2125,7 +2204,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2133,7 +2212,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2141,7 +2220,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2149,7 +2228,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2157,7 +2236,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2165,7 +2244,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2173,7 +2252,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2181,7 +2260,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2189,7 +2268,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2197,7 +2276,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2205,7 +2284,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2213,9 +2292,17 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
         <v>0</v>
       </c>
     </row>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -503,7 +503,7 @@
         <v>87.919921875</v>
       </c>
       <c r="G2">
-        <v>87.919921875</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -526,7 +526,7 @@
         <v>78.47021484375</v>
       </c>
       <c r="G3">
-        <v>78.47021484375</v>
+        <v>63.71</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -549,7 +549,7 @@
         <v>63.8701171875</v>
       </c>
       <c r="G4">
-        <v>63.8701171875</v>
+        <v>64.81</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -572,7 +572,7 @@
         <v>82.31982421875</v>
       </c>
       <c r="G5">
-        <v>82.31982421875</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -595,7 +595,7 @@
         <v>93.06982421875</v>
       </c>
       <c r="G6">
-        <v>93.06982421875</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -618,7 +618,7 @@
         <v>86.419921875</v>
       </c>
       <c r="G7">
-        <v>86.419921875</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -641,7 +641,7 @@
         <v>52.5400390625</v>
       </c>
       <c r="G8">
-        <v>52.5400390625</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -664,7 +664,7 @@
         <v>88.240234375</v>
       </c>
       <c r="G9">
-        <v>88.240234375</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -687,7 +687,7 @@
         <v>41.169921875</v>
       </c>
       <c r="G10">
-        <v>41.169921875</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -710,7 +710,7 @@
         <v>87.72021484375</v>
       </c>
       <c r="G11">
-        <v>87.72021484375</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -733,7 +733,7 @@
         <v>84.81982421875</v>
       </c>
       <c r="G12">
-        <v>84.81982421875</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -756,7 +756,7 @@
         <v>77.22021484375</v>
       </c>
       <c r="G13">
-        <v>77.22021484375</v>
+        <v>88.20999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -779,7 +779,7 @@
         <v>85.669921875</v>
       </c>
       <c r="G14">
-        <v>85.669921875</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -802,7 +802,7 @@
         <v>84.6201171875</v>
       </c>
       <c r="G15">
-        <v>84.6201171875</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -825,7 +825,7 @@
         <v>69.77001953125</v>
       </c>
       <c r="G16">
-        <v>69.77001953125</v>
+        <v>47.99</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -848,7 +848,7 @@
         <v>49.77001953125</v>
       </c>
       <c r="G17">
-        <v>49.77001953125</v>
+        <v>55.38</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -871,7 +871,7 @@
         <v>70.85986328125</v>
       </c>
       <c r="G18">
-        <v>70.85986328125</v>
+        <v>67.59</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -894,7 +894,7 @@
         <v>72.759765625</v>
       </c>
       <c r="G19">
-        <v>72.759765625</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -917,7 +917,7 @@
         <v>77.6201171875</v>
       </c>
       <c r="G20">
-        <v>77.6201171875</v>
+        <v>79.01000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -940,7 +940,7 @@
         <v>93.02001953125</v>
       </c>
       <c r="G21">
-        <v>93.02001953125</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1623,106 +1623,106 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B2">
-        <v>186.1396484375</v>
+        <v>176.02001953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>186.0400390625</v>
+        <v>168.42982421875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>176.48046875</v>
+        <v>165.52021484375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B5">
-        <v>175.83984375</v>
+        <v>165.43021484375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>175.4404296875</v>
+        <v>160.4301171875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B7">
-        <v>172.83984375</v>
+        <v>156.6301171875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>171.33984375</v>
+        <v>152.91982421875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>169.6396484375</v>
+        <v>151.129921875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>169.240234375</v>
+        <v>150.230234375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B11">
-        <v>164.6396484375</v>
+        <v>146.82982421875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>156.9404296875</v>
+        <v>144.279921875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B13">
-        <v>155.240234375</v>
+        <v>142.18021484375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>154.4404296875</v>
+        <v>138.44986328125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1730,39 +1730,39 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>145.51953125</v>
+        <v>133.959765625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B16">
-        <v>141.7197265625</v>
+        <v>133.809921875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B17">
-        <v>139.5400390625</v>
+        <v>128.6801171875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>127.740234375</v>
+        <v>117.76001953125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19">
-        <v>105.080078125</v>
+        <v>112.179921875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1770,15 +1770,15 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>99.5400390625</v>
+        <v>105.15001953125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21">
-        <v>82.33984375</v>
+        <v>87.0900390625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="28">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Rodada 6</t>
+  </si>
+  <si>
+    <t>Rodada 7</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -460,10 +463,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,10 +485,13 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -503,12 +509,15 @@
         <v>87.919921875</v>
       </c>
       <c r="G2">
-        <v>63.21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>63.2099609375</v>
+      </c>
+      <c r="H2">
+        <v>63.2099609375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -526,12 +535,15 @@
         <v>78.47021484375</v>
       </c>
       <c r="G3">
-        <v>63.71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>63.7099609375</v>
+      </c>
+      <c r="H3">
+        <v>63.7099609375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -549,12 +561,15 @@
         <v>63.8701171875</v>
       </c>
       <c r="G4">
-        <v>64.81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>64.81005859375</v>
+      </c>
+      <c r="H4">
+        <v>64.81005859375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -572,12 +587,15 @@
         <v>82.31982421875</v>
       </c>
       <c r="G5">
-        <v>70.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>70.60009765625</v>
+      </c>
+      <c r="H5">
+        <v>70.60009765625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -595,12 +613,15 @@
         <v>93.06982421875</v>
       </c>
       <c r="G6">
-        <v>75.36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>75.35986328125</v>
+      </c>
+      <c r="H6">
+        <v>75.35986328125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -618,12 +639,15 @@
         <v>86.419921875</v>
       </c>
       <c r="G7">
-        <v>47.39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>47.389892578125</v>
+      </c>
+      <c r="H7">
+        <v>47.389892578125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -641,12 +665,15 @@
         <v>52.5400390625</v>
       </c>
       <c r="G8">
-        <v>34.55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>34.550048828125</v>
+      </c>
+      <c r="H8">
+        <v>34.550048828125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -664,12 +691,15 @@
         <v>88.240234375</v>
       </c>
       <c r="G9">
-        <v>61.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>61.989990234375</v>
+      </c>
+      <c r="H9">
+        <v>61.989990234375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -687,12 +717,15 @@
         <v>41.169921875</v>
       </c>
       <c r="G10">
-        <v>71.01000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>71.009765625</v>
+      </c>
+      <c r="H10">
+        <v>71.009765625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -710,12 +743,15 @@
         <v>87.72021484375</v>
       </c>
       <c r="G11">
-        <v>77.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>77.7998046875</v>
+      </c>
+      <c r="H11">
+        <v>77.7998046875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -733,12 +769,15 @@
         <v>84.81982421875</v>
       </c>
       <c r="G12">
-        <v>62.01</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>62.010009765625</v>
+      </c>
+      <c r="H12">
+        <v>62.010009765625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -756,12 +795,15 @@
         <v>77.22021484375</v>
       </c>
       <c r="G13">
-        <v>88.20999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>88.2099609375</v>
+      </c>
+      <c r="H13">
+        <v>88.2099609375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -779,12 +821,15 @@
         <v>85.669921875</v>
       </c>
       <c r="G14">
-        <v>58.61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>58.610107421875</v>
+      </c>
+      <c r="H14">
+        <v>58.610107421875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -802,12 +847,15 @@
         <v>84.6201171875</v>
       </c>
       <c r="G15">
-        <v>75.81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>75.81005859375</v>
+      </c>
+      <c r="H15">
+        <v>75.81005859375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -825,12 +873,15 @@
         <v>69.77001953125</v>
       </c>
       <c r="G16">
-        <v>47.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>47.989990234375</v>
+      </c>
+      <c r="H16">
+        <v>47.989990234375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -848,12 +899,15 @@
         <v>49.77001953125</v>
       </c>
       <c r="G17">
-        <v>55.38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>55.3798828125</v>
+      </c>
+      <c r="H17">
+        <v>55.3798828125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -871,12 +925,15 @@
         <v>70.85986328125</v>
       </c>
       <c r="G18">
-        <v>67.59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>67.58984375</v>
+      </c>
+      <c r="H18">
+        <v>67.58984375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -894,12 +951,15 @@
         <v>72.759765625</v>
       </c>
       <c r="G19">
-        <v>61.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>61.199951171875</v>
+      </c>
+      <c r="H19">
+        <v>61.199951171875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -917,12 +977,15 @@
         <v>77.6201171875</v>
       </c>
       <c r="G20">
-        <v>79.01000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>79.009765625</v>
+      </c>
+      <c r="H20">
+        <v>79.009765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -942,10 +1005,13 @@
       <c r="G21">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -963,6 +1029,9 @@
         <v>0</v>
       </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>0</v>
       </c>
     </row>
@@ -978,107 +1047,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1167,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1106,7 +1175,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1114,7 +1183,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1122,7 +1191,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1130,7 +1199,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1138,7 +1207,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1146,7 +1215,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1154,7 +1223,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1162,7 +1231,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1170,7 +1239,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1178,7 +1247,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1186,7 +1255,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1194,7 +1263,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1202,7 +1271,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1210,7 +1279,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1218,7 +1287,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1226,7 +1295,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1234,7 +1303,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1242,7 +1311,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1250,7 +1319,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1273,7 +1342,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1281,7 +1350,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1289,7 +1358,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1297,7 +1366,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1305,7 +1374,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1313,7 +1382,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1321,7 +1390,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1329,7 +1398,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1337,7 +1406,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1345,7 +1414,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1353,7 +1422,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1361,7 +1430,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1369,7 +1438,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1377,7 +1446,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1385,7 +1454,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1393,7 +1462,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1401,7 +1470,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1409,7 +1478,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1417,7 +1486,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1425,7 +1494,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1448,7 +1517,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1456,7 +1525,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1464,7 +1533,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1472,7 +1541,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1480,7 +1549,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1488,7 +1557,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1496,7 +1565,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1504,7 +1573,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1512,7 +1581,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1520,7 +1589,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1528,7 +1597,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1536,7 +1605,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1544,7 +1613,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1552,7 +1621,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1560,7 +1629,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1568,7 +1637,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -1576,7 +1645,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -1584,7 +1653,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -1592,7 +1661,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -1600,7 +1669,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -1623,162 +1692,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2">
-        <v>176.02001953125</v>
+        <v>259.02001953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>168.42982421875</v>
+        <v>253.64013671875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>165.52021484375</v>
+        <v>243.78955078125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>165.43021484375</v>
+        <v>243.31982421875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>160.4301171875</v>
+        <v>236.240234375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>156.6301171875</v>
+        <v>235.6396484375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>152.91982421875</v>
+        <v>223.52001953125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>151.129921875</v>
+        <v>214.33984375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
-        <v>150.230234375</v>
+        <v>212.22021484375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>146.82982421875</v>
+        <v>208.83984375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>144.279921875</v>
+        <v>206.03955078125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13">
-        <v>142.18021484375</v>
+        <v>205.89013671875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>138.44986328125</v>
+        <v>202.89013671875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
-        <v>133.959765625</v>
+        <v>195.15966796875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B16">
-        <v>133.809921875</v>
+        <v>193.490234375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>128.6801171875</v>
+        <v>183.189453125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B18">
-        <v>117.76001953125</v>
+        <v>181.19970703125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19">
-        <v>112.179921875</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
-        <v>105.15001953125</v>
+        <v>160.52978515625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>87.0900390625</v>
+        <v>121.64013671875</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1867,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1806,7 +1875,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1814,7 +1883,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1822,7 +1891,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1830,7 +1899,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1838,7 +1907,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1846,7 +1915,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1854,7 +1923,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1862,7 +1931,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1870,7 +1939,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1878,7 +1947,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1886,7 +1955,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1894,7 +1963,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1902,7 +1971,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1910,7 +1979,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1918,7 +1987,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1926,7 +1995,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1934,7 +2003,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1942,7 +2011,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1950,7 +2019,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1973,7 +2042,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1981,7 +2050,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1989,7 +2058,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1997,7 +2066,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2005,7 +2074,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2013,7 +2082,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2021,7 +2090,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2029,7 +2098,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2037,7 +2106,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2045,7 +2114,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2053,7 +2122,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2061,7 +2130,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2069,7 +2138,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2077,7 +2146,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2085,7 +2154,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2093,7 +2162,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2101,7 +2170,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2109,7 +2178,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2117,7 +2186,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2125,7 +2194,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2148,7 +2217,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2156,7 +2225,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2164,7 +2233,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2172,7 +2241,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2180,7 +2249,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2188,7 +2257,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2196,7 +2265,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2204,7 +2273,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2212,7 +2281,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2220,7 +2289,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2228,7 +2297,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2236,7 +2305,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2244,7 +2313,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2252,7 +2321,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2260,7 +2329,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2268,7 +2337,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2276,7 +2345,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2284,7 +2353,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2292,7 +2361,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2300,7 +2369,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -512,7 +512,7 @@
         <v>63.2099609375</v>
       </c>
       <c r="H2">
-        <v>63.2099609375</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -538,7 +538,7 @@
         <v>63.7099609375</v>
       </c>
       <c r="H3">
-        <v>63.7099609375</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -564,7 +564,7 @@
         <v>64.81005859375</v>
       </c>
       <c r="H4">
-        <v>64.81005859375</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -590,7 +590,7 @@
         <v>70.60009765625</v>
       </c>
       <c r="H5">
-        <v>70.60009765625</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -616,7 +616,7 @@
         <v>75.35986328125</v>
       </c>
       <c r="H6">
-        <v>75.35986328125</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -642,7 +642,7 @@
         <v>47.389892578125</v>
       </c>
       <c r="H7">
-        <v>47.389892578125</v>
+        <v>38.87</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -668,7 +668,7 @@
         <v>34.550048828125</v>
       </c>
       <c r="H8">
-        <v>34.550048828125</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -694,7 +694,7 @@
         <v>61.989990234375</v>
       </c>
       <c r="H9">
-        <v>61.989990234375</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -720,7 +720,7 @@
         <v>71.009765625</v>
       </c>
       <c r="H10">
-        <v>71.009765625</v>
+        <v>40.27</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -746,7 +746,7 @@
         <v>77.7998046875</v>
       </c>
       <c r="H11">
-        <v>77.7998046875</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -772,7 +772,7 @@
         <v>62.010009765625</v>
       </c>
       <c r="H12">
-        <v>62.010009765625</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -798,7 +798,7 @@
         <v>88.2099609375</v>
       </c>
       <c r="H13">
-        <v>88.2099609375</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -824,7 +824,7 @@
         <v>58.610107421875</v>
       </c>
       <c r="H14">
-        <v>58.610107421875</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -850,7 +850,7 @@
         <v>75.81005859375</v>
       </c>
       <c r="H15">
-        <v>75.81005859375</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -876,7 +876,7 @@
         <v>47.989990234375</v>
       </c>
       <c r="H16">
-        <v>47.989990234375</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -902,7 +902,7 @@
         <v>55.3798828125</v>
       </c>
       <c r="H17">
-        <v>55.3798828125</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -928,7 +928,7 @@
         <v>67.58984375</v>
       </c>
       <c r="H18">
-        <v>67.58984375</v>
+        <v>32.97</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -954,7 +954,7 @@
         <v>61.199951171875</v>
       </c>
       <c r="H19">
-        <v>61.199951171875</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -980,7 +980,7 @@
         <v>79.009765625</v>
       </c>
       <c r="H20">
-        <v>79.009765625</v>
+        <v>41.27</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1006,7 +1006,7 @@
         <v>83</v>
       </c>
       <c r="H21">
-        <v>83</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1695,23 +1695,23 @@
         <v>26</v>
       </c>
       <c r="B2">
-        <v>259.02001953125</v>
+        <v>219.19001953125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>253.64013671875</v>
+        <v>209.10017578125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>243.78955078125</v>
+        <v>201.0998828125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1719,15 +1719,15 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>243.31982421875</v>
+        <v>200.86001953125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>236.240234375</v>
+        <v>198.6796875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1735,47 +1735,47 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>235.6396484375</v>
+        <v>197.8998828125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>223.52001953125</v>
+        <v>193.63017578125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B9">
-        <v>214.33984375</v>
+        <v>189.650029296875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B10">
-        <v>212.22021484375</v>
+        <v>184.719921875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>208.83984375</v>
+        <v>179.130224609375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>206.03955078125</v>
+        <v>178.109716796875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1783,47 +1783,47 @@
         <v>8</v>
       </c>
       <c r="B13">
-        <v>205.89013671875</v>
+        <v>177.88017578125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>202.89013671875</v>
+        <v>177.599833984375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B15">
-        <v>195.15966796875</v>
+        <v>172.679814453125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B16">
-        <v>193.490234375</v>
+        <v>171.41970703125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B17">
-        <v>183.189453125</v>
+        <v>157.95017578125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>181.19970703125</v>
+        <v>152.4496875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1831,23 +1831,23 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>165.75</v>
+        <v>141.810009765625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B20">
-        <v>160.52978515625</v>
+        <v>136.590087890625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B21">
-        <v>121.64013671875</v>
+        <v>117.14990234375</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="29">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>Rodada 7</t>
+  </si>
+  <si>
+    <t>Rodada 8</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -463,10 +466,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,10 +491,13 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -512,12 +518,15 @@
         <v>63.2099609375</v>
       </c>
       <c r="H2">
-        <v>49.97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>70.81982421875</v>
+      </c>
+      <c r="I2">
+        <v>70.81982421875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -538,12 +547,15 @@
         <v>63.7099609375</v>
       </c>
       <c r="H3">
-        <v>35.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>99.85986328125</v>
+      </c>
+      <c r="I3">
+        <v>99.85986328125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -564,12 +576,15 @@
         <v>64.81005859375</v>
       </c>
       <c r="H4">
-        <v>29.27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>55.52001953125</v>
+      </c>
+      <c r="I4">
+        <v>55.52001953125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -590,12 +605,15 @@
         <v>70.60009765625</v>
       </c>
       <c r="H5">
-        <v>31.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>64.2099609375</v>
+      </c>
+      <c r="I5">
+        <v>64.2099609375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -616,12 +634,15 @@
         <v>75.35986328125</v>
       </c>
       <c r="H6">
-        <v>30.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>100.25</v>
+      </c>
+      <c r="I6">
+        <v>100.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -642,12 +663,15 @@
         <v>47.389892578125</v>
       </c>
       <c r="H7">
-        <v>38.87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>67.27001953125</v>
+      </c>
+      <c r="I7">
+        <v>67.27001953125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -668,12 +692,15 @@
         <v>34.550048828125</v>
       </c>
       <c r="H8">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>61.5</v>
+      </c>
+      <c r="I8">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -694,12 +721,15 @@
         <v>61.989990234375</v>
       </c>
       <c r="H9">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>48.469970703125</v>
+      </c>
+      <c r="I9">
+        <v>48.469970703125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -720,12 +750,15 @@
         <v>71.009765625</v>
       </c>
       <c r="H10">
-        <v>40.27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>65.47021484375</v>
+      </c>
+      <c r="I10">
+        <v>65.47021484375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -746,12 +779,15 @@
         <v>77.7998046875</v>
       </c>
       <c r="H11">
-        <v>35.34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>57.93994140625</v>
+      </c>
+      <c r="I11">
+        <v>57.93994140625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -772,12 +808,15 @@
         <v>62.010009765625</v>
       </c>
       <c r="H12">
-        <v>30.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>77.06982421875</v>
+      </c>
+      <c r="I12">
+        <v>77.06982421875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -798,12 +837,15 @@
         <v>88.2099609375</v>
       </c>
       <c r="H13">
-        <v>28.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>61.110107421875</v>
+      </c>
+      <c r="I13">
+        <v>61.110107421875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -824,12 +866,15 @@
         <v>58.610107421875</v>
       </c>
       <c r="H14">
-        <v>45.37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>81.56982421875</v>
+      </c>
+      <c r="I14">
+        <v>81.56982421875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -850,12 +895,15 @@
         <v>75.81005859375</v>
       </c>
       <c r="H15">
-        <v>48.67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>83.22021484375</v>
+      </c>
+      <c r="I15">
+        <v>83.22021484375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -876,12 +924,15 @@
         <v>47.989990234375</v>
       </c>
       <c r="H16">
-        <v>24.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>46.550048828125</v>
+      </c>
+      <c r="I16">
+        <v>46.550048828125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -902,12 +953,15 @@
         <v>55.3798828125</v>
       </c>
       <c r="H17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>61.8701171875</v>
+      </c>
+      <c r="I17">
+        <v>61.8701171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -928,12 +982,15 @@
         <v>67.58984375</v>
       </c>
       <c r="H18">
-        <v>32.97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>71.77001953125</v>
+      </c>
+      <c r="I18">
+        <v>71.77001953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -954,12 +1011,15 @@
         <v>61.199951171875</v>
       </c>
       <c r="H19">
-        <v>44.15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>69.60009765625</v>
+      </c>
+      <c r="I19">
+        <v>69.60009765625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -980,12 +1040,15 @@
         <v>79.009765625</v>
       </c>
       <c r="H20">
-        <v>41.27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>65.47021484375</v>
+      </c>
+      <c r="I20">
+        <v>65.47021484375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1006,12 +1069,15 @@
         <v>83</v>
       </c>
       <c r="H21">
-        <v>43.17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>76.97021484375</v>
+      </c>
+      <c r="I21">
+        <v>76.97021484375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1032,6 +1098,9 @@
         <v>0</v>
       </c>
       <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>0</v>
       </c>
     </row>
@@ -1047,107 +1116,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1167,7 +1236,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1175,7 +1244,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1183,7 +1252,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1191,7 +1260,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1199,7 +1268,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1207,7 +1276,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1215,7 +1284,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1223,7 +1292,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1231,7 +1300,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1239,7 +1308,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1247,7 +1316,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1255,7 +1324,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1263,7 +1332,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1271,7 +1340,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1279,7 +1348,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1287,7 +1356,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1295,7 +1364,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1303,7 +1372,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1311,7 +1380,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1319,7 +1388,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1342,7 +1411,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1350,7 +1419,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1358,7 +1427,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1366,7 +1435,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1374,7 +1443,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1382,7 +1451,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1390,7 +1459,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1398,7 +1467,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1406,7 +1475,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1414,7 +1483,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1422,7 +1491,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1430,7 +1499,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1438,7 +1507,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1446,7 +1515,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1454,7 +1523,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1462,7 +1531,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1470,7 +1539,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1478,7 +1547,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1486,7 +1555,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1494,7 +1563,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1517,7 +1586,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1525,7 +1594,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1533,7 +1602,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1541,7 +1610,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1549,7 +1618,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1557,7 +1626,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1565,7 +1634,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1573,7 +1642,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1581,7 +1650,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1589,7 +1658,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1597,7 +1666,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1605,7 +1674,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1613,7 +1682,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1621,7 +1690,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1629,7 +1698,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1637,7 +1706,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -1645,7 +1714,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -1653,7 +1722,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -1661,7 +1730,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -1669,7 +1738,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -1692,58 +1761,58 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>219.19001953125</v>
+        <v>368.9296875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>209.10017578125</v>
+        <v>341.89990234375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>201.0998828125</v>
+        <v>329.96044921875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>200.86001953125</v>
+        <v>326.87060546875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>198.6796875</v>
+        <v>307.419677734375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>197.8998828125</v>
+        <v>300.969482421875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>193.63017578125</v>
+        <v>292.76953125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1751,103 +1820,103 @@
         <v>19</v>
       </c>
       <c r="B9">
-        <v>189.650029296875</v>
+        <v>287.650390625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>184.719921875</v>
+        <v>287.5703125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B11">
-        <v>179.130224609375</v>
+        <v>281.98974609375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>178.109716796875</v>
+        <v>281.39990234375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>177.88017578125</v>
+        <v>281.33984375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>177.599833984375</v>
+        <v>273.159912109375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>172.679814453125</v>
+        <v>268.349853515625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>171.41970703125</v>
+        <v>247.170166015625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>157.95017578125</v>
+        <v>243.1201171875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>152.4496875</v>
+        <v>239.72021484375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>141.810009765625</v>
+        <v>228.89013671875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B20">
-        <v>136.590087890625</v>
+        <v>210.860107421875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B21">
-        <v>117.14990234375</v>
+        <v>210.090087890625</v>
       </c>
     </row>
   </sheetData>
@@ -1867,7 +1936,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1875,7 +1944,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1883,7 +1952,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1891,7 +1960,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1899,7 +1968,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1907,7 +1976,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1915,7 +1984,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1923,7 +1992,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1931,7 +2000,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1939,7 +2008,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1947,7 +2016,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1955,7 +2024,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1963,7 +2032,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1971,7 +2040,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1979,7 +2048,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1987,7 +2056,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1995,7 +2064,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2003,7 +2072,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2011,7 +2080,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2019,7 +2088,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2042,7 +2111,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2050,7 +2119,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2058,7 +2127,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2066,7 +2135,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2074,7 +2143,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2082,7 +2151,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2090,7 +2159,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2098,7 +2167,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2106,7 +2175,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2114,7 +2183,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2122,7 +2191,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2130,7 +2199,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2138,7 +2207,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2146,7 +2215,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2154,7 +2223,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2162,7 +2231,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2170,7 +2239,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2178,7 +2247,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2186,7 +2255,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2194,7 +2263,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2217,7 +2286,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2225,7 +2294,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2233,7 +2302,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2241,7 +2310,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2249,7 +2318,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2257,7 +2326,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2265,7 +2334,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2273,7 +2342,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2281,7 +2350,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2289,7 +2358,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2297,7 +2366,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2305,7 +2374,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2313,7 +2382,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2321,7 +2390,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2329,7 +2398,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2337,7 +2406,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2345,7 +2414,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2353,7 +2422,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2361,7 +2430,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2369,7 +2438,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="30">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>Rodada 8</t>
+  </si>
+  <si>
+    <t>Rodada 9</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -466,10 +469,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,10 +497,13 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -521,12 +527,15 @@
         <v>70.81982421875</v>
       </c>
       <c r="I2">
-        <v>70.81982421875</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>77.5498046875</v>
+      </c>
+      <c r="J2">
+        <v>77.5498046875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -550,12 +559,15 @@
         <v>99.85986328125</v>
       </c>
       <c r="I3">
-        <v>99.85986328125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>58.679931640625</v>
+      </c>
+      <c r="J3">
+        <v>58.679931640625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -579,12 +591,15 @@
         <v>55.52001953125</v>
       </c>
       <c r="I4">
-        <v>55.52001953125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>71.75</v>
+      </c>
+      <c r="J4">
+        <v>71.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -608,12 +623,15 @@
         <v>64.2099609375</v>
       </c>
       <c r="I5">
-        <v>64.2099609375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>83.0498046875</v>
+      </c>
+      <c r="J5">
+        <v>83.0498046875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -637,12 +655,15 @@
         <v>100.25</v>
       </c>
       <c r="I6">
-        <v>100.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>75.52001953125</v>
+      </c>
+      <c r="J6">
+        <v>75.52001953125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -666,12 +687,15 @@
         <v>67.27001953125</v>
       </c>
       <c r="I7">
-        <v>67.27001953125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>75.75</v>
+      </c>
+      <c r="J7">
+        <v>75.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -695,12 +719,15 @@
         <v>61.5</v>
       </c>
       <c r="I8">
-        <v>61.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>77</v>
+      </c>
+      <c r="J8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -724,12 +751,15 @@
         <v>48.469970703125</v>
       </c>
       <c r="I9">
-        <v>48.469970703125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>82.85009765625</v>
+      </c>
+      <c r="J9">
+        <v>82.85009765625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -753,12 +783,15 @@
         <v>65.47021484375</v>
       </c>
       <c r="I10">
-        <v>65.47021484375</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>34.110107421875</v>
+      </c>
+      <c r="J10">
+        <v>34.110107421875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -782,12 +815,15 @@
         <v>57.93994140625</v>
       </c>
       <c r="I11">
-        <v>57.93994140625</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>42.89990234375</v>
+      </c>
+      <c r="J11">
+        <v>42.89990234375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -811,12 +847,15 @@
         <v>77.06982421875</v>
       </c>
       <c r="I12">
-        <v>77.06982421875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>80.0498046875</v>
+      </c>
+      <c r="J12">
+        <v>80.0498046875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -840,12 +879,15 @@
         <v>61.110107421875</v>
       </c>
       <c r="I13">
-        <v>61.110107421875</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>82.81982421875</v>
+      </c>
+      <c r="J13">
+        <v>82.81982421875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -869,12 +911,15 @@
         <v>81.56982421875</v>
       </c>
       <c r="I14">
-        <v>81.56982421875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>73.35009765625</v>
+      </c>
+      <c r="J14">
+        <v>73.35009765625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -898,12 +943,15 @@
         <v>83.22021484375</v>
       </c>
       <c r="I15">
-        <v>83.22021484375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>85.64990234375</v>
+      </c>
+      <c r="J15">
+        <v>85.64990234375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -927,12 +975,15 @@
         <v>46.550048828125</v>
       </c>
       <c r="I16">
-        <v>46.550048828125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>59.909912109375</v>
+      </c>
+      <c r="J16">
+        <v>59.909912109375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -956,12 +1007,15 @@
         <v>61.8701171875</v>
       </c>
       <c r="I17">
-        <v>61.8701171875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>70.5400390625</v>
+      </c>
+      <c r="J17">
+        <v>70.5400390625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -985,12 +1039,15 @@
         <v>71.77001953125</v>
       </c>
       <c r="I18">
-        <v>71.77001953125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>68.25</v>
+      </c>
+      <c r="J18">
+        <v>68.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1014,12 +1071,15 @@
         <v>69.60009765625</v>
       </c>
       <c r="I19">
-        <v>69.60009765625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>67.14990234375</v>
+      </c>
+      <c r="J19">
+        <v>67.14990234375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1043,12 +1103,15 @@
         <v>65.47021484375</v>
       </c>
       <c r="I20">
-        <v>65.47021484375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>80.85009765625</v>
+      </c>
+      <c r="J20">
+        <v>80.85009765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1072,12 +1135,15 @@
         <v>76.97021484375</v>
       </c>
       <c r="I21">
-        <v>76.97021484375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>76.4501953125</v>
+      </c>
+      <c r="J21">
+        <v>76.4501953125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1101,6 +1167,9 @@
         <v>0</v>
       </c>
       <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <v>0</v>
       </c>
     </row>
@@ -1116,107 +1185,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1236,7 +1305,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1244,7 +1313,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1252,7 +1321,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1260,7 +1329,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1268,7 +1337,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1276,7 +1345,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1284,7 +1353,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1292,7 +1361,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1300,7 +1369,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1308,7 +1377,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1316,7 +1385,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1324,7 +1393,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1332,7 +1401,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1340,7 +1409,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1348,7 +1417,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1356,7 +1425,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1364,7 +1433,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1372,7 +1441,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1380,7 +1449,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1388,7 +1457,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1411,7 +1480,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1419,7 +1488,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1427,7 +1496,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1435,7 +1504,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1443,7 +1512,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1451,7 +1520,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1459,7 +1528,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1467,7 +1536,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1475,7 +1544,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1483,7 +1552,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1491,7 +1560,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1499,7 +1568,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1507,7 +1576,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1515,7 +1584,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1523,7 +1592,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1531,7 +1600,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1539,7 +1608,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1547,7 +1616,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1555,7 +1624,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1563,7 +1632,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1586,7 +1655,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1594,7 +1663,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1602,7 +1671,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1610,7 +1679,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1618,7 +1687,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1626,7 +1695,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1634,7 +1703,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1642,7 +1711,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1650,7 +1719,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1658,7 +1727,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1666,7 +1735,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1674,7 +1743,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1682,7 +1751,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1690,7 +1759,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1698,7 +1767,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1706,7 +1775,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -1714,7 +1783,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -1722,7 +1791,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -1730,7 +1799,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -1738,7 +1807,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -1761,162 +1830,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>368.9296875</v>
+        <v>344.19970703125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <v>341.89990234375</v>
+        <v>329.4404296875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>329.96044921875</v>
+        <v>329.30029296875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>326.87060546875</v>
+        <v>309.360107421875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>307.419677734375</v>
+        <v>303.949462890625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>300.969482421875</v>
+        <v>302.9501953125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>292.76953125</v>
+        <v>300.719970703125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>287.650390625</v>
+        <v>300.1796875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>287.5703125</v>
+        <v>299.49951171875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>281.98974609375</v>
+        <v>299.199951171875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>281.39990234375</v>
+        <v>281.55029296875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B13">
-        <v>281.33984375</v>
+        <v>278.4697265625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>273.159912109375</v>
+        <v>276.829833984375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>268.349853515625</v>
+        <v>270.709716796875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>247.170166015625</v>
+        <v>266.35986328125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>243.1201171875</v>
+        <v>255.9501953125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>239.72021484375</v>
+        <v>237.56005859375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B19">
-        <v>228.89013671875</v>
+        <v>225.590087890625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>210.860107421875</v>
+        <v>224.219970703125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B21">
-        <v>210.090087890625</v>
+        <v>211.760009765625</v>
       </c>
     </row>
   </sheetData>
@@ -1936,162 +2005,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>85.64990234375</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>83.0498046875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>82.85009765625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>82.81982421875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>80.85009765625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>80.0498046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>77.5498046875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>76.4501953125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>75.52001953125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>73.35009765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>70.5400390625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>67.14990234375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>59.909912109375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>58.679931640625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>42.89990234375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>34.110107421875</v>
       </c>
     </row>
   </sheetData>
@@ -2111,7 +2180,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2119,7 +2188,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2127,7 +2196,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2135,7 +2204,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2143,7 +2212,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2151,7 +2220,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2159,7 +2228,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2167,7 +2236,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2175,7 +2244,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2183,7 +2252,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2191,7 +2260,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2199,7 +2268,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2207,7 +2276,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2215,7 +2284,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2223,7 +2292,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2231,7 +2300,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2239,7 +2308,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2247,7 +2316,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2255,7 +2324,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2263,7 +2332,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2286,7 +2355,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2294,7 +2363,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2302,7 +2371,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2310,7 +2379,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2318,7 +2387,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2326,7 +2395,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2334,7 +2403,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2342,7 +2411,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2350,7 +2419,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2358,7 +2427,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2366,7 +2435,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2374,7 +2443,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2382,7 +2451,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2390,7 +2459,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2398,7 +2467,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2406,7 +2475,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2414,7 +2483,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2422,7 +2491,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2430,7 +2499,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2438,7 +2507,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -530,7 +530,7 @@
         <v>77.5498046875</v>
       </c>
       <c r="J2">
-        <v>77.5498046875</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -562,7 +562,7 @@
         <v>58.679931640625</v>
       </c>
       <c r="J3">
-        <v>58.679931640625</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -594,7 +594,7 @@
         <v>71.75</v>
       </c>
       <c r="J4">
-        <v>71.75</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -626,7 +626,7 @@
         <v>83.0498046875</v>
       </c>
       <c r="J5">
-        <v>83.0498046875</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -658,7 +658,7 @@
         <v>75.52001953125</v>
       </c>
       <c r="J6">
-        <v>75.52001953125</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -690,7 +690,7 @@
         <v>75.75</v>
       </c>
       <c r="J7">
-        <v>75.75</v>
+        <v>85.95999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -722,7 +722,7 @@
         <v>77</v>
       </c>
       <c r="J8">
-        <v>77</v>
+        <v>68.98</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -754,7 +754,7 @@
         <v>82.85009765625</v>
       </c>
       <c r="J9">
-        <v>82.85009765625</v>
+        <v>85.53</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -786,7 +786,7 @@
         <v>34.110107421875</v>
       </c>
       <c r="J10">
-        <v>34.110107421875</v>
+        <v>71.04000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -818,7 +818,7 @@
         <v>42.89990234375</v>
       </c>
       <c r="J11">
-        <v>42.89990234375</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -850,7 +850,7 @@
         <v>80.0498046875</v>
       </c>
       <c r="J12">
-        <v>80.0498046875</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -882,7 +882,7 @@
         <v>82.81982421875</v>
       </c>
       <c r="J13">
-        <v>82.81982421875</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -914,7 +914,7 @@
         <v>73.35009765625</v>
       </c>
       <c r="J14">
-        <v>73.35009765625</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -946,7 +946,7 @@
         <v>85.64990234375</v>
       </c>
       <c r="J15">
-        <v>85.64990234375</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -978,7 +978,7 @@
         <v>59.909912109375</v>
       </c>
       <c r="J16">
-        <v>59.909912109375</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1010,7 +1010,7 @@
         <v>70.5400390625</v>
       </c>
       <c r="J17">
-        <v>70.5400390625</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1042,7 +1042,7 @@
         <v>68.25</v>
       </c>
       <c r="J18">
-        <v>68.25</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1074,7 +1074,7 @@
         <v>67.14990234375</v>
       </c>
       <c r="J19">
-        <v>67.14990234375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1106,7 +1106,7 @@
         <v>80.85009765625</v>
       </c>
       <c r="J20">
-        <v>80.85009765625</v>
+        <v>94.58</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1138,7 +1138,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J21">
-        <v>76.4501953125</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2005,10 +2005,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>85.64990234375</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2016,151 +2016,151 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>83.0498046875</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>82.85009765625</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>82.81982421875</v>
+        <v>94.58</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>80.85009765625</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
-        <v>80.0498046875</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>77.5498046875</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>77</v>
+        <v>85.95999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>76.4501953125</v>
+        <v>85.53</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>75.75</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B12">
-        <v>75.52001953125</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B13">
-        <v>73.35009765625</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>71.75</v>
+        <v>71.04000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>70.5400390625</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>68.25</v>
+        <v>68.98</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <v>67.14990234375</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18">
-        <v>59.909912109375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>58.679931640625</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B20">
-        <v>42.89990234375</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B21">
-        <v>34.110107421875</v>
+        <v>39.7</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="31">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Rodada 9</t>
+  </si>
+  <si>
+    <t>Rodada 10</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -469,10 +472,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,10 +503,13 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -530,12 +536,15 @@
         <v>77.5498046875</v>
       </c>
       <c r="J2">
-        <v>73.98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>73.68017578125</v>
+      </c>
+      <c r="K2">
+        <v>73.68017578125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -562,12 +571,15 @@
         <v>58.679931640625</v>
       </c>
       <c r="J3">
-        <v>88.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>87.14013671875</v>
+      </c>
+      <c r="K3">
+        <v>87.14013671875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -594,12 +606,15 @@
         <v>71.75</v>
       </c>
       <c r="J4">
-        <v>49.76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>49.760009765625</v>
+      </c>
+      <c r="K4">
+        <v>49.760009765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -626,12 +641,15 @@
         <v>83.0498046875</v>
       </c>
       <c r="J5">
-        <v>97.95999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>97.9599609375</v>
+      </c>
+      <c r="K5">
+        <v>97.9599609375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -658,12 +676,15 @@
         <v>75.52001953125</v>
       </c>
       <c r="J6">
-        <v>72.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>70.10009765625</v>
+      </c>
+      <c r="K6">
+        <v>70.10009765625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -690,12 +711,15 @@
         <v>75.75</v>
       </c>
       <c r="J7">
-        <v>85.95999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>85.9599609375</v>
+      </c>
+      <c r="K7">
+        <v>85.9599609375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -722,12 +746,15 @@
         <v>77</v>
       </c>
       <c r="J8">
-        <v>68.98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>68.68017578125</v>
+      </c>
+      <c r="K8">
+        <v>68.68017578125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -754,12 +781,15 @@
         <v>82.85009765625</v>
       </c>
       <c r="J9">
-        <v>85.53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>85.52978515625</v>
+      </c>
+      <c r="K9">
+        <v>85.52978515625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -786,12 +816,15 @@
         <v>34.110107421875</v>
       </c>
       <c r="J10">
-        <v>71.04000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>70.740234375</v>
+      </c>
+      <c r="K10">
+        <v>70.740234375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -818,12 +851,15 @@
         <v>42.89990234375</v>
       </c>
       <c r="J11">
-        <v>97.68000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>97.68017578125</v>
+      </c>
+      <c r="K11">
+        <v>97.68017578125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -850,12 +886,15 @@
         <v>80.0498046875</v>
       </c>
       <c r="J12">
-        <v>61.01</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>59.010009765625</v>
+      </c>
+      <c r="K12">
+        <v>59.010009765625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -882,12 +921,15 @@
         <v>82.81982421875</v>
       </c>
       <c r="J13">
-        <v>87.73999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>85.93994140625</v>
+      </c>
+      <c r="K13">
+        <v>85.93994140625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -914,12 +956,15 @@
         <v>73.35009765625</v>
       </c>
       <c r="J14">
-        <v>104.68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>104.68017578125</v>
+      </c>
+      <c r="K14">
+        <v>104.68017578125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -946,12 +991,15 @@
         <v>85.64990234375</v>
       </c>
       <c r="J15">
-        <v>68.44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>66.93994140625</v>
+      </c>
+      <c r="K15">
+        <v>66.93994140625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -978,12 +1026,15 @@
         <v>59.909912109375</v>
       </c>
       <c r="J16">
-        <v>70.48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>70.47998046875</v>
+      </c>
+      <c r="K16">
+        <v>70.47998046875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1010,12 +1061,15 @@
         <v>70.5400390625</v>
       </c>
       <c r="J17">
-        <v>39.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>39.699951171875</v>
+      </c>
+      <c r="K17">
+        <v>39.699951171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1042,12 +1096,15 @@
         <v>68.25</v>
       </c>
       <c r="J18">
-        <v>80.34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>80.33984375</v>
+      </c>
+      <c r="K18">
+        <v>80.33984375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1074,12 +1131,15 @@
         <v>67.14990234375</v>
       </c>
       <c r="J19">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>62.89990234375</v>
+      </c>
+      <c r="K19">
+        <v>62.89990234375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1106,12 +1166,15 @@
         <v>80.85009765625</v>
       </c>
       <c r="J20">
-        <v>94.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>94.27978515625</v>
+      </c>
+      <c r="K20">
+        <v>94.27978515625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1138,12 +1201,15 @@
         <v>76.4501953125</v>
       </c>
       <c r="J21">
-        <v>86.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>85.85009765625</v>
+      </c>
+      <c r="K21">
+        <v>85.85009765625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1170,6 +1236,9 @@
         <v>0</v>
       </c>
       <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
         <v>0</v>
       </c>
     </row>
@@ -1185,107 +1254,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1374,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1313,7 +1382,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1321,7 +1390,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1329,7 +1398,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1337,7 +1406,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1345,7 +1414,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1353,7 +1422,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1361,7 +1430,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1369,7 +1438,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1377,7 +1446,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1385,7 +1454,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1393,7 +1462,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1401,7 +1470,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1409,7 +1478,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1417,7 +1486,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1425,7 +1494,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1433,7 +1502,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1441,7 +1510,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1449,7 +1518,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1457,7 +1526,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1480,7 +1549,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1488,7 +1557,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1496,7 +1565,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1504,7 +1573,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1512,7 +1581,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1520,7 +1589,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1528,7 +1597,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1536,7 +1605,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1544,7 +1613,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1552,7 +1621,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1560,7 +1629,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1568,7 +1637,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1576,7 +1645,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1584,7 +1653,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1592,7 +1661,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1600,7 +1669,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1608,7 +1677,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1616,7 +1685,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1624,7 +1693,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1632,7 +1701,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1655,7 +1724,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1663,7 +1732,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1671,7 +1740,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1679,7 +1748,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1687,7 +1756,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1695,7 +1764,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1703,7 +1772,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1711,7 +1780,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1719,7 +1788,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1727,7 +1796,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1735,7 +1804,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1743,7 +1812,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1751,7 +1820,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1759,7 +1828,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1767,7 +1836,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1775,7 +1844,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -1783,7 +1852,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -1791,7 +1860,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -1799,7 +1868,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -1807,7 +1876,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -1830,7 +1899,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -1838,7 +1907,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -1846,7 +1915,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -1854,7 +1923,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -1862,7 +1931,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -1870,7 +1939,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -1878,7 +1947,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -1886,7 +1955,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -1894,7 +1963,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -1902,7 +1971,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -1910,7 +1979,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -1918,7 +1987,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -1926,7 +1995,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -1934,7 +2003,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -1942,7 +2011,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -1950,7 +2019,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -1958,7 +2027,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -1966,7 +2035,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -1974,7 +2043,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -1982,7 +2051,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2005,162 +2074,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>104.68</v>
+        <v>209.3603515625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
-        <v>97.95999999999999</v>
+        <v>195.919921875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>97.68000000000001</v>
+        <v>195.3603515625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>94.58</v>
+        <v>188.5595703125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>88.64</v>
+        <v>174.2802734375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>87.73999999999999</v>
+        <v>171.919921875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B8">
-        <v>86.75</v>
+        <v>171.8798828125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9">
-        <v>85.95999999999999</v>
+        <v>171.7001953125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>85.53</v>
+        <v>171.0595703125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>80.34</v>
+        <v>160.6796875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>73.98</v>
+        <v>147.3603515625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>72.3</v>
+        <v>141.48046875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B14">
-        <v>71.04000000000001</v>
+        <v>140.9599609375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>70.48</v>
+        <v>140.2001953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
-        <v>68.98</v>
+        <v>137.3603515625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>68.44</v>
+        <v>133.8798828125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>62</v>
+        <v>125.7998046875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>61.01</v>
+        <v>118.02001953125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20">
-        <v>49.76</v>
+        <v>99.52001953125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21">
-        <v>39.7</v>
+        <v>79.39990234375</v>
       </c>
     </row>
   </sheetData>
@@ -2180,7 +2249,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2188,7 +2257,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2196,7 +2265,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2204,7 +2273,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2212,7 +2281,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2220,7 +2289,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2228,7 +2297,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2236,7 +2305,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2244,7 +2313,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2252,7 +2321,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2260,7 +2329,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2268,7 +2337,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2276,7 +2345,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2284,7 +2353,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2292,7 +2361,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2300,7 +2369,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2308,7 +2377,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2316,7 +2385,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2324,7 +2393,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2332,7 +2401,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2355,7 +2424,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2363,7 +2432,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2371,7 +2440,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2379,7 +2448,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2387,7 +2456,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2395,7 +2464,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2403,7 +2472,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2411,7 +2480,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2419,7 +2488,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2427,7 +2496,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2435,7 +2504,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2443,7 +2512,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2451,7 +2520,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2459,7 +2528,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2467,7 +2536,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2475,7 +2544,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2483,7 +2552,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2491,7 +2560,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2499,7 +2568,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2507,7 +2576,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -539,7 +539,7 @@
         <v>73.68017578125</v>
       </c>
       <c r="K2">
-        <v>73.68017578125</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -574,7 +574,7 @@
         <v>87.14013671875</v>
       </c>
       <c r="K3">
-        <v>87.14013671875</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -609,7 +609,7 @@
         <v>49.760009765625</v>
       </c>
       <c r="K4">
-        <v>49.760009765625</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -644,7 +644,7 @@
         <v>97.9599609375</v>
       </c>
       <c r="K5">
-        <v>97.9599609375</v>
+        <v>69.06999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -679,7 +679,7 @@
         <v>70.10009765625</v>
       </c>
       <c r="K6">
-        <v>70.10009765625</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -714,7 +714,7 @@
         <v>85.9599609375</v>
       </c>
       <c r="K7">
-        <v>85.9599609375</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -749,7 +749,7 @@
         <v>68.68017578125</v>
       </c>
       <c r="K8">
-        <v>68.68017578125</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -784,7 +784,7 @@
         <v>85.52978515625</v>
       </c>
       <c r="K9">
-        <v>85.52978515625</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -819,7 +819,7 @@
         <v>70.740234375</v>
       </c>
       <c r="K10">
-        <v>70.740234375</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -854,7 +854,7 @@
         <v>97.68017578125</v>
       </c>
       <c r="K11">
-        <v>97.68017578125</v>
+        <v>66.56999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -889,7 +889,7 @@
         <v>59.010009765625</v>
       </c>
       <c r="K12">
-        <v>59.010009765625</v>
+        <v>60.57</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -924,7 +924,7 @@
         <v>85.93994140625</v>
       </c>
       <c r="K13">
-        <v>85.93994140625</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -959,7 +959,7 @@
         <v>104.68017578125</v>
       </c>
       <c r="K14">
-        <v>104.68017578125</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -994,7 +994,7 @@
         <v>66.93994140625</v>
       </c>
       <c r="K15">
-        <v>66.93994140625</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1029,7 +1029,7 @@
         <v>70.47998046875</v>
       </c>
       <c r="K16">
-        <v>70.47998046875</v>
+        <v>67.78</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1064,7 +1064,7 @@
         <v>39.699951171875</v>
       </c>
       <c r="K17">
-        <v>39.699951171875</v>
+        <v>32.15</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1099,7 +1099,7 @@
         <v>80.33984375</v>
       </c>
       <c r="K18">
-        <v>80.33984375</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1134,7 +1134,7 @@
         <v>62.89990234375</v>
       </c>
       <c r="K19">
-        <v>62.89990234375</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1169,7 +1169,7 @@
         <v>94.27978515625</v>
       </c>
       <c r="K20">
-        <v>94.27978515625</v>
+        <v>71.17</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1204,7 +1204,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K21">
-        <v>85.85009765625</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2077,7 +2077,7 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>209.3603515625</v>
+        <v>171.97017578125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2085,143 +2085,143 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>195.919921875</v>
+        <v>167.0299609375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>195.3603515625</v>
+        <v>165.44978515625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>188.5595703125</v>
+        <v>164.25017578125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>174.2802734375</v>
+        <v>145.14009765625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B7">
-        <v>171.919921875</v>
+        <v>143.61013671875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>171.8798828125</v>
+        <v>141.10978515625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9">
-        <v>171.7001953125</v>
+        <v>140.78984375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>171.0595703125</v>
+        <v>138.25998046875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>160.6796875</v>
+        <v>129.52994140625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>147.3603515625</v>
+        <v>126.68994140625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>141.48046875</v>
+        <v>125.8299609375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>140.9599609375</v>
+        <v>125.220234375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>140.2001953125</v>
+        <v>119.580009765625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>137.3603515625</v>
+        <v>112.99009765625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B17">
-        <v>133.8798828125</v>
+        <v>106.94990234375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>125.7998046875</v>
+        <v>105.25017578125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B19">
-        <v>118.02001953125</v>
+        <v>89.340009765625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B20">
-        <v>99.52001953125</v>
+        <v>88.08017578125001</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2229,7 +2229,7 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>79.39990234375</v>
+        <v>71.84995117187501</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="32">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>Rodada 10</t>
+  </si>
+  <si>
+    <t>Rodada 11</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -472,10 +475,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,10 +509,13 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -539,12 +545,15 @@
         <v>73.68017578125</v>
       </c>
       <c r="K2">
-        <v>31.57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>30.3699951171875</v>
+      </c>
+      <c r="L2">
+        <v>30.3699951171875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -574,12 +583,15 @@
         <v>87.14013671875</v>
       </c>
       <c r="K3">
-        <v>56.47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>55.27001953125</v>
+      </c>
+      <c r="L3">
+        <v>55.27001953125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -609,12 +621,15 @@
         <v>49.760009765625</v>
       </c>
       <c r="K4">
-        <v>39.58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>38.780029296875</v>
+      </c>
+      <c r="L4">
+        <v>38.780029296875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -644,12 +659,15 @@
         <v>97.9599609375</v>
       </c>
       <c r="K5">
-        <v>69.06999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>68.669921875</v>
+      </c>
+      <c r="L5">
+        <v>68.669921875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -679,12 +697,15 @@
         <v>70.10009765625</v>
       </c>
       <c r="K6">
-        <v>42.89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>42.090087890625</v>
+      </c>
+      <c r="L6">
+        <v>42.090087890625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -714,12 +735,15 @@
         <v>85.9599609375</v>
       </c>
       <c r="K7">
-        <v>39.87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>39.469970703125</v>
+      </c>
+      <c r="L7">
+        <v>39.469970703125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -749,12 +773,15 @@
         <v>68.68017578125</v>
       </c>
       <c r="K8">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>19.4000244140625</v>
+      </c>
+      <c r="L8">
+        <v>19.4000244140625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -784,12 +811,15 @@
         <v>85.52978515625</v>
       </c>
       <c r="K9">
-        <v>55.58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>55.179931640625</v>
+      </c>
+      <c r="L9">
+        <v>55.179931640625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -819,12 +849,15 @@
         <v>70.740234375</v>
       </c>
       <c r="K10">
-        <v>54.48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>53.280029296875</v>
+      </c>
+      <c r="L10">
+        <v>53.280029296875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -854,12 +887,15 @@
         <v>97.68017578125</v>
       </c>
       <c r="K11">
-        <v>66.56999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>65.3701171875</v>
+      </c>
+      <c r="L11">
+        <v>65.3701171875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -889,12 +925,15 @@
         <v>59.010009765625</v>
       </c>
       <c r="K12">
-        <v>60.57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>60.169921875</v>
+      </c>
+      <c r="L12">
+        <v>60.169921875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -924,12 +963,15 @@
         <v>85.93994140625</v>
       </c>
       <c r="K13">
-        <v>43.59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>43.590087890625</v>
+      </c>
+      <c r="L13">
+        <v>43.590087890625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -959,12 +1001,15 @@
         <v>104.68017578125</v>
       </c>
       <c r="K14">
-        <v>67.29000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>66.89013671875</v>
+      </c>
+      <c r="L14">
+        <v>66.89013671875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -994,12 +1039,15 @@
         <v>66.93994140625</v>
       </c>
       <c r="K15">
-        <v>59.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>58.949951171875</v>
+      </c>
+      <c r="L15">
+        <v>58.949951171875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1029,12 +1077,15 @@
         <v>70.47998046875</v>
       </c>
       <c r="K16">
-        <v>67.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>66.580078125</v>
+      </c>
+      <c r="L16">
+        <v>66.580078125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1064,12 +1115,15 @@
         <v>39.699951171875</v>
       </c>
       <c r="K17">
-        <v>32.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>31.75</v>
+      </c>
+      <c r="L17">
+        <v>31.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1099,12 +1153,15 @@
         <v>80.33984375</v>
       </c>
       <c r="K18">
-        <v>60.45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>60.050048828125</v>
+      </c>
+      <c r="L18">
+        <v>60.050048828125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1134,12 +1191,15 @@
         <v>62.89990234375</v>
       </c>
       <c r="K19">
-        <v>44.05</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>43.25</v>
+      </c>
+      <c r="L19">
+        <v>43.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1169,12 +1229,15 @@
         <v>94.27978515625</v>
       </c>
       <c r="K20">
-        <v>71.17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>70.77001953125</v>
+      </c>
+      <c r="L20">
+        <v>70.77001953125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1204,12 +1267,15 @@
         <v>85.85009765625</v>
       </c>
       <c r="K21">
-        <v>59.29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>58.090087890625</v>
+      </c>
+      <c r="L21">
+        <v>58.090087890625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1239,6 +1305,9 @@
         <v>0</v>
       </c>
       <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
         <v>0</v>
       </c>
     </row>
@@ -1254,107 +1323,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1374,7 +1443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1382,7 +1451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1390,7 +1459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1398,7 +1467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1406,7 +1475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1414,7 +1483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1422,7 +1491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1430,7 +1499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1438,7 +1507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1446,7 +1515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1454,7 +1523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1462,7 +1531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1470,7 +1539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1478,7 +1547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1486,7 +1555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1494,7 +1563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1502,7 +1571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1510,7 +1579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1518,7 +1587,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1526,7 +1595,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1549,7 +1618,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1557,7 +1626,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1565,7 +1634,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1573,7 +1642,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1581,7 +1650,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1589,7 +1658,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1597,7 +1666,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1605,7 +1674,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1613,7 +1682,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1621,7 +1690,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1629,7 +1698,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1637,7 +1706,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1645,7 +1714,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1653,7 +1722,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1661,7 +1730,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1669,7 +1738,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1677,7 +1746,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1685,7 +1754,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1693,7 +1762,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1701,7 +1770,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1724,7 +1793,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1732,7 +1801,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1740,7 +1809,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1748,7 +1817,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1756,7 +1825,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1764,7 +1833,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1772,7 +1841,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1780,7 +1849,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1788,7 +1857,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1796,7 +1865,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1804,7 +1873,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1812,7 +1881,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1820,7 +1889,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1828,7 +1897,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1836,7 +1905,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1844,7 +1913,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -1852,7 +1921,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -1860,7 +1929,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -1868,7 +1937,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -1876,7 +1945,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -1899,7 +1968,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -1907,7 +1976,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -1915,7 +1984,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -1923,7 +1992,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -1931,7 +2000,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -1939,7 +2008,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -1947,7 +2016,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -1955,7 +2024,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -1963,7 +2032,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -1971,7 +2040,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -1979,7 +2048,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -1987,7 +2056,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -1995,7 +2064,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2003,7 +2072,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2011,7 +2080,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2019,7 +2088,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2027,7 +2096,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2035,7 +2104,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2043,7 +2112,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2051,7 +2120,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2074,162 +2143,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>171.97017578125</v>
+        <v>238.46044921875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>167.0299609375</v>
+        <v>235.81982421875</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B4">
-        <v>165.44978515625</v>
+        <v>235.2998046875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>164.25017578125</v>
+        <v>228.42041015625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>145.14009765625</v>
+        <v>203.64013671875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>143.61013671875</v>
+        <v>202.0302734375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>141.10978515625</v>
+        <v>200.43994140625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>140.78984375</v>
+        <v>197.68017578125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>138.25998046875</v>
+        <v>195.8896484375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B11">
-        <v>129.52994140625</v>
+        <v>184.83984375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>126.68994140625</v>
+        <v>179.349853515625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>125.8299609375</v>
+        <v>177.30029296875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>125.220234375</v>
+        <v>173.1201171875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>119.580009765625</v>
+        <v>164.89990234375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>112.99009765625</v>
+        <v>154.2802734375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17">
-        <v>106.94990234375</v>
+        <v>149.39990234375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18">
-        <v>105.25017578125</v>
+        <v>134.420166015625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19">
-        <v>89.340009765625</v>
+        <v>127.320068359375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20">
-        <v>88.08017578125001</v>
+        <v>107.480224609375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
-        <v>71.84995117187501</v>
+        <v>103.199951171875</v>
       </c>
     </row>
   </sheetData>
@@ -2249,7 +2318,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2257,7 +2326,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2265,7 +2334,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2273,7 +2342,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2281,7 +2350,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2289,7 +2358,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2297,7 +2366,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2305,7 +2374,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2313,7 +2382,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2321,7 +2390,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2329,7 +2398,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2337,7 +2406,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2345,7 +2414,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2353,7 +2422,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2361,7 +2430,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2369,7 +2438,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2377,7 +2446,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2385,7 +2454,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2393,7 +2462,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2401,7 +2470,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2424,7 +2493,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2432,7 +2501,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2440,7 +2509,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2448,7 +2517,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2456,7 +2525,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2464,7 +2533,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2472,7 +2541,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2480,7 +2549,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2488,7 +2557,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2496,7 +2565,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2504,7 +2573,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2512,7 +2581,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2520,7 +2589,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2528,7 +2597,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2536,7 +2605,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2544,7 +2613,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2552,7 +2621,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2560,7 +2629,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2568,7 +2637,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2576,7 +2645,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="33">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>Rodada 11</t>
+  </si>
+  <si>
+    <t>Rodada 12</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -475,10 +478,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,10 +515,13 @@
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -548,12 +554,15 @@
         <v>30.3699951171875</v>
       </c>
       <c r="L2">
-        <v>30.3699951171875</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>107.56005859375</v>
+      </c>
+      <c r="M2">
+        <v>107.56005859375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -586,12 +595,15 @@
         <v>55.27001953125</v>
       </c>
       <c r="L3">
-        <v>55.27001953125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>81.35986328125</v>
+      </c>
+      <c r="M3">
+        <v>81.35986328125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -624,12 +636,15 @@
         <v>38.780029296875</v>
       </c>
       <c r="L4">
-        <v>38.780029296875</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>88.06005859375</v>
+      </c>
+      <c r="M4">
+        <v>88.06005859375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -662,12 +677,15 @@
         <v>68.669921875</v>
       </c>
       <c r="L5">
-        <v>68.669921875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>92.16015625</v>
+      </c>
+      <c r="M5">
+        <v>92.16015625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -700,12 +718,15 @@
         <v>42.090087890625</v>
       </c>
       <c r="L6">
-        <v>42.090087890625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>70.9599609375</v>
+      </c>
+      <c r="M6">
+        <v>70.9599609375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -738,12 +759,15 @@
         <v>39.469970703125</v>
       </c>
       <c r="L7">
-        <v>39.469970703125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>85.16015625</v>
+      </c>
+      <c r="M7">
+        <v>85.16015625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -776,12 +800,15 @@
         <v>19.4000244140625</v>
       </c>
       <c r="L8">
-        <v>19.4000244140625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>95.259765625</v>
+      </c>
+      <c r="M8">
+        <v>95.259765625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -814,12 +841,15 @@
         <v>55.179931640625</v>
       </c>
       <c r="L9">
-        <v>55.179931640625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>93.68017578125</v>
+      </c>
+      <c r="M9">
+        <v>93.68017578125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -852,12 +882,15 @@
         <v>53.280029296875</v>
       </c>
       <c r="L10">
-        <v>53.280029296875</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>96.4599609375</v>
+      </c>
+      <c r="M10">
+        <v>96.4599609375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -890,12 +923,15 @@
         <v>65.3701171875</v>
       </c>
       <c r="L11">
-        <v>65.3701171875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>82.4599609375</v>
+      </c>
+      <c r="M11">
+        <v>82.4599609375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -928,12 +964,15 @@
         <v>60.169921875</v>
       </c>
       <c r="L12">
-        <v>60.169921875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>82.81005859375</v>
+      </c>
+      <c r="M12">
+        <v>82.81005859375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -966,12 +1005,15 @@
         <v>43.590087890625</v>
       </c>
       <c r="L13">
-        <v>43.590087890625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>86.9599609375</v>
+      </c>
+      <c r="M13">
+        <v>86.9599609375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1004,12 +1046,15 @@
         <v>66.89013671875</v>
       </c>
       <c r="L14">
-        <v>66.89013671875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>90.4599609375</v>
+      </c>
+      <c r="M14">
+        <v>90.4599609375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1042,12 +1087,15 @@
         <v>58.949951171875</v>
       </c>
       <c r="L15">
-        <v>58.949951171875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>92.66015625</v>
+      </c>
+      <c r="M15">
+        <v>92.66015625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1080,12 +1128,15 @@
         <v>66.580078125</v>
       </c>
       <c r="L16">
-        <v>66.580078125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>29.8499755859375</v>
+      </c>
+      <c r="M16">
+        <v>29.8499755859375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1118,12 +1169,15 @@
         <v>31.75</v>
       </c>
       <c r="L17">
-        <v>31.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>51.530029296875</v>
+      </c>
+      <c r="M17">
+        <v>51.530029296875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1156,12 +1210,15 @@
         <v>60.050048828125</v>
       </c>
       <c r="L18">
-        <v>60.050048828125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>89.66015625</v>
+      </c>
+      <c r="M18">
+        <v>89.66015625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1194,12 +1251,15 @@
         <v>43.25</v>
       </c>
       <c r="L19">
-        <v>43.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>81.8798828125</v>
+      </c>
+      <c r="M19">
+        <v>81.8798828125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1232,12 +1292,15 @@
         <v>70.77001953125</v>
       </c>
       <c r="L20">
-        <v>70.77001953125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>98.56005859375</v>
+      </c>
+      <c r="M20">
+        <v>98.56005859375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1270,12 +1333,15 @@
         <v>58.090087890625</v>
       </c>
       <c r="L21">
-        <v>58.090087890625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>88.759765625</v>
+      </c>
+      <c r="M21">
+        <v>88.759765625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1308,6 +1374,9 @@
         <v>0</v>
       </c>
       <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>0</v>
       </c>
     </row>
@@ -1323,107 +1392,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1443,7 +1512,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1451,7 +1520,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1459,7 +1528,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1467,7 +1536,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1475,7 +1544,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1483,7 +1552,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1491,7 +1560,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1499,7 +1568,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1507,7 +1576,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1515,7 +1584,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1523,7 +1592,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1531,7 +1600,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1539,7 +1608,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1547,7 +1616,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1555,7 +1624,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1563,7 +1632,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1571,7 +1640,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1579,7 +1648,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1587,7 +1656,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1595,7 +1664,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1618,7 +1687,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1626,7 +1695,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1634,7 +1703,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1642,7 +1711,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1650,7 +1719,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1658,7 +1727,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1666,7 +1735,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1674,7 +1743,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1682,7 +1751,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1690,7 +1759,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1698,7 +1767,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1706,7 +1775,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1714,7 +1783,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1722,7 +1791,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1730,7 +1799,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1738,7 +1807,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1746,7 +1815,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1754,7 +1823,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1762,7 +1831,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1770,7 +1839,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1793,7 +1862,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1801,7 +1870,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1809,7 +1878,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1817,7 +1886,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1825,7 +1894,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1833,7 +1902,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1841,7 +1910,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1849,7 +1918,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1857,7 +1926,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1865,7 +1934,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1873,7 +1942,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1881,7 +1950,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1889,7 +1958,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1897,7 +1966,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1905,7 +1974,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1913,7 +1982,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -1921,7 +1990,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -1929,7 +1998,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -1937,7 +2006,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -1945,7 +2014,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -1968,7 +2037,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -1976,7 +2045,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -1984,7 +2053,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -1992,7 +2061,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2000,7 +2069,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2008,7 +2077,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2016,7 +2085,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2024,7 +2093,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2032,7 +2101,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2040,7 +2109,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2048,7 +2117,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2056,7 +2125,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2064,7 +2133,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2072,7 +2141,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2080,7 +2149,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2088,7 +2157,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2096,7 +2165,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2104,7 +2173,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2112,7 +2181,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2120,7 +2189,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2143,58 +2212,58 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B2">
-        <v>238.46044921875</v>
+        <v>362.169921875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>235.81982421875</v>
+        <v>352.490234375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>235.2998046875</v>
+        <v>350.9501953125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>228.42041015625</v>
+        <v>328.070068359375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>203.64013671875</v>
+        <v>327.97021484375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7">
-        <v>202.0302734375</v>
+        <v>321.459716796875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>200.43994140625</v>
+        <v>319.710205078125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2202,103 +2271,103 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>197.68017578125</v>
+        <v>319.1702880859375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>195.8896484375</v>
+        <v>316.940185546875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>184.83984375</v>
+        <v>311.210205078125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>179.349853515625</v>
+        <v>305.1298828125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B13">
-        <v>177.30029296875</v>
+        <v>303.449951171875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>173.1201171875</v>
+        <v>295.750244140625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>164.89990234375</v>
+        <v>284.800048828125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>154.2802734375</v>
+        <v>278.5997314453125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17">
-        <v>149.39990234375</v>
+        <v>269.90966796875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18">
-        <v>134.420166015625</v>
+        <v>264.66015625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B19">
-        <v>127.320068359375</v>
+        <v>254.110107421875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B20">
-        <v>107.480224609375</v>
+        <v>196.760009765625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
-        <v>103.199951171875</v>
+        <v>174.510009765625</v>
       </c>
     </row>
   </sheetData>
@@ -2318,7 +2387,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2326,7 +2395,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2334,7 +2403,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2342,7 +2411,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2350,7 +2419,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2358,7 +2427,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2366,7 +2435,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2374,7 +2443,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2382,7 +2451,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2390,7 +2459,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2398,7 +2467,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2406,7 +2475,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2414,7 +2483,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2422,7 +2491,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2430,7 +2499,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2438,7 +2507,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2446,7 +2515,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2454,7 +2523,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2462,7 +2531,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2470,7 +2539,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2493,7 +2562,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2501,7 +2570,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2509,7 +2578,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2517,7 +2586,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2525,7 +2594,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2533,7 +2602,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2541,7 +2610,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2549,7 +2618,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2557,7 +2626,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2565,7 +2634,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2573,7 +2642,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2581,7 +2650,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2589,7 +2658,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2597,7 +2666,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2605,7 +2674,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2613,7 +2682,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2621,7 +2690,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2629,7 +2698,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2637,7 +2706,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2645,7 +2714,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -557,7 +557,7 @@
         <v>107.56005859375</v>
       </c>
       <c r="M2">
-        <v>107.56005859375</v>
+        <v>66.11</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -598,7 +598,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="M3">
-        <v>81.35986328125</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -639,7 +639,7 @@
         <v>88.06005859375</v>
       </c>
       <c r="M4">
-        <v>88.06005859375</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -680,7 +680,7 @@
         <v>92.16015625</v>
       </c>
       <c r="M5">
-        <v>92.16015625</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -721,7 +721,7 @@
         <v>70.9599609375</v>
       </c>
       <c r="M6">
-        <v>70.9599609375</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -762,7 +762,7 @@
         <v>85.16015625</v>
       </c>
       <c r="M7">
-        <v>85.16015625</v>
+        <v>81.45</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -803,7 +803,7 @@
         <v>95.259765625</v>
       </c>
       <c r="M8">
-        <v>95.259765625</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -844,7 +844,7 @@
         <v>93.68017578125</v>
       </c>
       <c r="M9">
-        <v>93.68017578125</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -885,7 +885,7 @@
         <v>96.4599609375</v>
       </c>
       <c r="M10">
-        <v>96.4599609375</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -926,7 +926,7 @@
         <v>82.4599609375</v>
       </c>
       <c r="M11">
-        <v>82.4599609375</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -967,7 +967,7 @@
         <v>82.81005859375</v>
       </c>
       <c r="M12">
-        <v>82.81005859375</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1008,7 +1008,7 @@
         <v>86.9599609375</v>
       </c>
       <c r="M13">
-        <v>86.9599609375</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1049,7 +1049,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="M14">
-        <v>90.4599609375</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1090,7 +1090,7 @@
         <v>92.66015625</v>
       </c>
       <c r="M15">
-        <v>92.66015625</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1131,7 +1131,7 @@
         <v>29.8499755859375</v>
       </c>
       <c r="M16">
-        <v>29.8499755859375</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1172,7 +1172,7 @@
         <v>51.530029296875</v>
       </c>
       <c r="M17">
-        <v>51.530029296875</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1213,7 +1213,7 @@
         <v>89.66015625</v>
       </c>
       <c r="M18">
-        <v>89.66015625</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1254,7 +1254,7 @@
         <v>81.8798828125</v>
       </c>
       <c r="M19">
-        <v>81.8798828125</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1295,7 +1295,7 @@
         <v>98.56005859375</v>
       </c>
       <c r="M20">
-        <v>98.56005859375</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1336,7 +1336,7 @@
         <v>88.759765625</v>
       </c>
       <c r="M21">
-        <v>88.759765625</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2215,7 +2215,7 @@
         <v>30</v>
       </c>
       <c r="B2">
-        <v>362.169921875</v>
+        <v>347.10986328125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2223,7 +2223,7 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>352.490234375</v>
+        <v>346.4302734375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2231,31 +2231,31 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>350.9501953125</v>
+        <v>325.1900390625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B5">
-        <v>328.070068359375</v>
+        <v>319.359951171875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6">
-        <v>327.97021484375</v>
+        <v>317.739990234375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>321.459716796875</v>
+        <v>315.41025390625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2263,55 +2263,55 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>319.710205078125</v>
+        <v>312.000048828125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B9">
-        <v>319.1702880859375</v>
+        <v>309.389892578125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>316.940185546875</v>
+        <v>295.350048828125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B11">
-        <v>311.210205078125</v>
+        <v>292.27001953125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>305.1298828125</v>
+        <v>292.040087890625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B13">
-        <v>303.449951171875</v>
+        <v>285.400224609375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14">
-        <v>295.750244140625</v>
+        <v>283.150146484375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2319,23 +2319,23 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>284.800048828125</v>
+        <v>279.339990234375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B16">
-        <v>278.5997314453125</v>
+        <v>277.7202294921875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B17">
-        <v>269.90966796875</v>
+        <v>255.4399658203125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2343,15 +2343,15 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <v>264.66015625</v>
+        <v>242.45009765625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>254.110107421875</v>
+        <v>229.59978515625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2359,7 +2359,7 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>196.760009765625</v>
+        <v>224.0100341796875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2367,7 +2367,7 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>174.510009765625</v>
+        <v>158.26998046875</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="34">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Rodada 12</t>
+  </si>
+  <si>
+    <t>Rodada 13</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -478,10 +481,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,10 +521,13 @@
       <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -557,12 +563,15 @@
         <v>107.56005859375</v>
       </c>
       <c r="M2">
-        <v>66.11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>66.10986328125</v>
+      </c>
+      <c r="N2">
+        <v>66.10986328125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -600,10 +609,13 @@
       <c r="M3">
         <v>68.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -639,12 +651,15 @@
         <v>88.06005859375</v>
       </c>
       <c r="M4">
-        <v>65.84999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>65.85009765625</v>
+      </c>
+      <c r="N4">
+        <v>65.85009765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -680,12 +695,15 @@
         <v>92.16015625</v>
       </c>
       <c r="M5">
-        <v>66.40000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>66.39990234375</v>
+      </c>
+      <c r="N5">
+        <v>66.39990234375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -723,10 +741,13 @@
       <c r="M6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -762,12 +783,15 @@
         <v>85.16015625</v>
       </c>
       <c r="M7">
-        <v>81.45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>81.4501953125</v>
+      </c>
+      <c r="N7">
+        <v>81.4501953125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -803,12 +827,15 @@
         <v>95.259765625</v>
       </c>
       <c r="M8">
-        <v>72.09999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>72.10009765625</v>
+      </c>
+      <c r="N8">
+        <v>72.10009765625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -846,10 +873,13 @@
       <c r="M9">
         <v>75</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -885,12 +915,15 @@
         <v>96.4599609375</v>
       </c>
       <c r="M10">
-        <v>64.92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>64.919921875</v>
+      </c>
+      <c r="N10">
+        <v>64.919921875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -926,12 +959,15 @@
         <v>82.4599609375</v>
       </c>
       <c r="M11">
-        <v>69.90000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>69.89990234375</v>
+      </c>
+      <c r="N11">
+        <v>69.89990234375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -967,12 +1003,15 @@
         <v>82.81005859375</v>
       </c>
       <c r="M12">
-        <v>77.34999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>77.35009765625</v>
+      </c>
+      <c r="N12">
+        <v>77.35009765625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1010,10 +1049,13 @@
       <c r="M13">
         <v>101.25</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13">
+        <v>101.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1049,12 +1091,15 @@
         <v>90.4599609375</v>
       </c>
       <c r="M14">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>84.39990234375</v>
+      </c>
+      <c r="N14">
+        <v>84.39990234375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1090,12 +1135,15 @@
         <v>92.66015625</v>
       </c>
       <c r="M15">
-        <v>76.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>76.7998046875</v>
+      </c>
+      <c r="N15">
+        <v>76.7998046875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1131,12 +1179,15 @@
         <v>29.8499755859375</v>
       </c>
       <c r="M16">
-        <v>57.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>57.10009765625</v>
+      </c>
+      <c r="N16">
+        <v>57.10009765625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1172,12 +1223,15 @@
         <v>51.530029296875</v>
       </c>
       <c r="M17">
-        <v>35.29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>35.2900390625</v>
+      </c>
+      <c r="N17">
+        <v>35.2900390625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1213,12 +1267,15 @@
         <v>89.66015625</v>
       </c>
       <c r="M18">
-        <v>81.95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>81.9501953125</v>
+      </c>
+      <c r="N18">
+        <v>81.9501953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1254,12 +1311,15 @@
         <v>81.8798828125</v>
       </c>
       <c r="M19">
-        <v>41.57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>41.570068359375</v>
+      </c>
+      <c r="N19">
+        <v>41.570068359375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1297,10 +1357,13 @@
       <c r="M20">
         <v>83.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1336,12 +1399,15 @@
         <v>88.759765625</v>
       </c>
       <c r="M21">
-        <v>86.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>86.66015625</v>
+      </c>
+      <c r="N21">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1377,6 +1443,9 @@
         <v>0</v>
       </c>
       <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
         <v>0</v>
       </c>
     </row>
@@ -1392,107 +1461,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1512,7 +1581,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1520,7 +1589,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1528,7 +1597,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1536,7 +1605,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1544,7 +1613,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1552,7 +1621,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1560,7 +1629,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1568,7 +1637,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1576,7 +1645,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1584,7 +1653,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1592,7 +1661,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1600,7 +1669,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1608,7 +1677,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1616,7 +1685,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1624,7 +1693,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1632,7 +1701,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1640,7 +1709,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1648,7 +1717,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1656,7 +1725,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1664,7 +1733,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1687,7 +1756,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1695,7 +1764,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1703,7 +1772,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1711,7 +1780,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1719,7 +1788,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1727,7 +1796,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1735,7 +1804,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1743,7 +1812,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1751,7 +1820,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1759,7 +1828,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1767,7 +1836,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1775,7 +1844,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1783,7 +1852,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1791,7 +1860,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1799,7 +1868,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1807,7 +1876,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1815,7 +1884,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1823,7 +1892,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1831,7 +1900,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1839,7 +1908,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1862,7 +1931,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1870,7 +1939,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1878,7 +1947,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1886,7 +1955,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1894,7 +1963,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1902,7 +1971,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1910,7 +1979,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1918,7 +1987,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1926,7 +1995,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -1934,7 +2003,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -1942,7 +2011,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -1950,7 +2019,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -1958,7 +2027,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -1966,7 +2035,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -1974,7 +2043,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -1982,7 +2051,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -1990,7 +2059,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -1998,7 +2067,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -2006,7 +2075,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -2014,7 +2083,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -2037,7 +2106,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -2045,7 +2114,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -2053,7 +2122,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -2061,7 +2130,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2069,7 +2138,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2077,7 +2146,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2085,7 +2154,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2093,7 +2162,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2101,7 +2170,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2109,7 +2178,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2117,7 +2186,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2125,7 +2194,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2133,7 +2202,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2141,7 +2210,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2149,7 +2218,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2157,7 +2226,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2165,7 +2234,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2173,7 +2242,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2181,7 +2250,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2189,7 +2258,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2212,162 +2281,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B2">
-        <v>347.10986328125</v>
+        <v>430.830078125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B3">
-        <v>346.4302734375</v>
+        <v>430.60986328125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>325.1900390625</v>
+        <v>418.989990234375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
-        <v>319.359951171875</v>
+        <v>406.020263671875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>317.739990234375</v>
+        <v>393.950439453125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>315.41025390625</v>
+        <v>391.58984375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>312.000048828125</v>
+        <v>385.31005859375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>309.389892578125</v>
+        <v>384.389892578125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>295.350048828125</v>
+        <v>383.150146484375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>292.27001953125</v>
+        <v>373.490478515625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>292.040087890625</v>
+        <v>372.149658203125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>285.400224609375</v>
+        <v>360.77001953125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B14">
-        <v>283.150146484375</v>
+        <v>356.690185546875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>279.339990234375</v>
+        <v>350.320068359375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>277.7202294921875</v>
+        <v>343.8299560546875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
-        <v>255.4399658203125</v>
+        <v>327.5401611328125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>242.45009765625</v>
+        <v>308.30029296875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19">
-        <v>229.59978515625</v>
+        <v>281.1102294921875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>224.0100341796875</v>
+        <v>271.169921875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
-        <v>158.26998046875</v>
+        <v>193.56005859375</v>
       </c>
     </row>
   </sheetData>
@@ -2387,7 +2456,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2395,7 +2464,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2403,7 +2472,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2411,7 +2480,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2419,7 +2488,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2427,7 +2496,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2435,7 +2504,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2443,7 +2512,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2451,7 +2520,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2459,7 +2528,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2467,7 +2536,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2475,7 +2544,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2483,7 +2552,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2491,7 +2560,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2499,7 +2568,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2507,7 +2576,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2515,7 +2584,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2523,7 +2592,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2531,7 +2600,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2539,7 +2608,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2562,7 +2631,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2570,7 +2639,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2578,7 +2647,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2586,7 +2655,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2594,7 +2663,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2602,7 +2671,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2610,7 +2679,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2618,7 +2687,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2626,7 +2695,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2634,7 +2703,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2642,7 +2711,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2650,7 +2719,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2658,7 +2727,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2666,7 +2735,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2674,7 +2743,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2682,7 +2751,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2690,7 +2759,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2698,7 +2767,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2706,7 +2775,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2714,7 +2783,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -566,7 +566,7 @@
         <v>66.10986328125</v>
       </c>
       <c r="N2">
-        <v>66.10986328125</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -610,7 +610,7 @@
         <v>68.5</v>
       </c>
       <c r="N3">
-        <v>68.5</v>
+        <v>88.47</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -654,7 +654,7 @@
         <v>65.85009765625</v>
       </c>
       <c r="N4">
-        <v>65.85009765625</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -698,7 +698,7 @@
         <v>66.39990234375</v>
       </c>
       <c r="N5">
-        <v>66.39990234375</v>
+        <v>102.42</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -742,7 +742,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -786,7 +786,7 @@
         <v>81.4501953125</v>
       </c>
       <c r="N7">
-        <v>81.4501953125</v>
+        <v>113.22</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -830,7 +830,7 @@
         <v>72.10009765625</v>
       </c>
       <c r="N8">
-        <v>72.10009765625</v>
+        <v>119.03</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -874,7 +874,7 @@
         <v>75</v>
       </c>
       <c r="N9">
-        <v>75</v>
+        <v>108.98</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -918,7 +918,7 @@
         <v>64.919921875</v>
       </c>
       <c r="N10">
-        <v>64.919921875</v>
+        <v>99.97</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -962,7 +962,7 @@
         <v>69.89990234375</v>
       </c>
       <c r="N11">
-        <v>69.89990234375</v>
+        <v>108.52</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1006,7 +1006,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="N12">
-        <v>77.35009765625</v>
+        <v>91.87</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1050,7 +1050,7 @@
         <v>101.25</v>
       </c>
       <c r="N13">
-        <v>101.25</v>
+        <v>90.02</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1094,7 +1094,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N14">
-        <v>84.39990234375</v>
+        <v>108.52</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1138,7 +1138,7 @@
         <v>76.7998046875</v>
       </c>
       <c r="N15">
-        <v>76.7998046875</v>
+        <v>85.94</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1182,7 +1182,7 @@
         <v>57.10009765625</v>
       </c>
       <c r="N16">
-        <v>57.10009765625</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1226,7 +1226,7 @@
         <v>35.2900390625</v>
       </c>
       <c r="N17">
-        <v>35.2900390625</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1270,7 +1270,7 @@
         <v>81.9501953125</v>
       </c>
       <c r="N18">
-        <v>81.9501953125</v>
+        <v>92.22</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1314,7 +1314,7 @@
         <v>41.570068359375</v>
       </c>
       <c r="N19">
-        <v>41.570068359375</v>
+        <v>96.77</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1358,7 +1358,7 @@
         <v>83.5</v>
       </c>
       <c r="N20">
-        <v>83.5</v>
+        <v>114.52</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1402,7 +1402,7 @@
         <v>86.66015625</v>
       </c>
       <c r="N21">
-        <v>86.66015625</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -2281,82 +2281,82 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>430.830078125</v>
+        <v>461.62986328125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>430.60986328125</v>
+        <v>454.95017578125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>418.989990234375</v>
+        <v>427.60994140625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B5">
-        <v>406.020263671875</v>
+        <v>423.93015625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>393.950439453125</v>
+        <v>418.369892578125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B7">
-        <v>391.58984375</v>
+        <v>416.980107421875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>385.31005859375</v>
+        <v>407.759990234375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>384.389892578125</v>
+        <v>405.260283203125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B10">
-        <v>383.150146484375</v>
+        <v>404.220244140625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>373.490478515625</v>
+        <v>385.370146484375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2364,7 +2364,7 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>372.149658203125</v>
+        <v>381.289853515625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2372,39 +2372,39 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>360.77001953125</v>
+        <v>380.74001953125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>356.690185546875</v>
+        <v>377.0400927734375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>350.320068359375</v>
+        <v>375.670146484375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>343.8299560546875</v>
+        <v>374.4700634765625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>327.5401611328125</v>
+        <v>371.210087890625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2412,23 +2412,23 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>308.30029296875</v>
+        <v>332.8201953125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>281.1102294921875</v>
+        <v>326.369853515625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B20">
-        <v>271.169921875</v>
+        <v>255.0601318359375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2436,7 +2436,7 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>193.56005859375</v>
+        <v>213.10001953125</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -566,7 +566,7 @@
         <v>66.10986328125</v>
       </c>
       <c r="N2">
-        <v>99.31999999999999</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -610,7 +610,7 @@
         <v>68.5</v>
       </c>
       <c r="N3">
-        <v>88.47</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -654,7 +654,7 @@
         <v>65.85009765625</v>
       </c>
       <c r="N4">
-        <v>90.37</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -698,7 +698,7 @@
         <v>66.39990234375</v>
       </c>
       <c r="N5">
-        <v>102.42</v>
+        <v>112.29</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -742,7 +742,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>92.52</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -786,7 +786,7 @@
         <v>81.4501953125</v>
       </c>
       <c r="N7">
-        <v>113.22</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -830,7 +830,7 @@
         <v>72.10009765625</v>
       </c>
       <c r="N8">
-        <v>119.03</v>
+        <v>118.53</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -874,7 +874,7 @@
         <v>75</v>
       </c>
       <c r="N9">
-        <v>108.98</v>
+        <v>108.48</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -918,7 +918,7 @@
         <v>64.919921875</v>
       </c>
       <c r="N10">
-        <v>99.97</v>
+        <v>118.24</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -962,7 +962,7 @@
         <v>69.89990234375</v>
       </c>
       <c r="N11">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1006,7 +1006,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="N12">
-        <v>91.87</v>
+        <v>115.44</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1050,7 +1050,7 @@
         <v>101.25</v>
       </c>
       <c r="N13">
-        <v>90.02</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1094,7 +1094,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N14">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1270,7 +1270,7 @@
         <v>81.9501953125</v>
       </c>
       <c r="N18">
-        <v>92.22</v>
+        <v>113.19</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1314,7 +1314,7 @@
         <v>41.570068359375</v>
       </c>
       <c r="N19">
-        <v>96.77</v>
+        <v>96.84</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1358,7 +1358,7 @@
         <v>83.5</v>
       </c>
       <c r="N20">
-        <v>114.52</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1402,7 +1402,7 @@
         <v>86.66015625</v>
       </c>
       <c r="N21">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -2284,7 +2284,7 @@
         <v>31</v>
       </c>
       <c r="B2">
-        <v>461.62986328125</v>
+        <v>461.19986328125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2292,7 +2292,7 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>454.95017578125</v>
+        <v>455.02017578125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2300,31 +2300,31 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>427.60994140625</v>
+        <v>437.47994140625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B5">
-        <v>423.93015625</v>
+        <v>425.750107421875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>418.369892578125</v>
+        <v>425.190244140625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>416.980107421875</v>
+        <v>424.00015625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2332,23 +2332,23 @@
         <v>24</v>
       </c>
       <c r="B8">
-        <v>407.759990234375</v>
+        <v>420.729990234375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>405.260283203125</v>
+        <v>417.869892578125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>404.220244140625</v>
+        <v>405.330283203125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2356,55 +2356,55 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>385.370146484375</v>
+        <v>403.640146484375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>381.289853515625</v>
+        <v>394.780087890625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13">
-        <v>380.74001953125</v>
+        <v>383.740146484375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>377.0400927734375</v>
+        <v>381.289853515625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>375.670146484375</v>
+        <v>380.31001953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>374.4700634765625</v>
+        <v>377.1100927734375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B17">
-        <v>371.210087890625</v>
+        <v>373.9700634765625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2412,7 +2412,7 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>332.8201953125</v>
+        <v>340.8901953125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2420,7 +2420,7 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>326.369853515625</v>
+        <v>326.439853515625</v>
       </c>
     </row>
     <row r="20" spans="1:2">

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="35">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>Rodada 13</t>
+  </si>
+  <si>
+    <t>Rodada 14</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -481,10 +484,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,10 +527,13 @@
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -566,12 +572,15 @@
         <v>66.10986328125</v>
       </c>
       <c r="N2">
-        <v>99.39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>99.39013671875</v>
+      </c>
+      <c r="O2">
+        <v>99.39013671875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -610,12 +619,15 @@
         <v>68.5</v>
       </c>
       <c r="N3">
-        <v>88.04000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>88.0400390625</v>
+      </c>
+      <c r="O3">
+        <v>88.0400390625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -654,12 +666,15 @@
         <v>65.85009765625</v>
       </c>
       <c r="N4">
-        <v>98.44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>98.43994140625</v>
+      </c>
+      <c r="O4">
+        <v>98.43994140625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -698,12 +713,15 @@
         <v>66.39990234375</v>
       </c>
       <c r="N5">
-        <v>112.29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>112.2900390625</v>
+      </c>
+      <c r="O5">
+        <v>112.2900390625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -742,12 +760,15 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100.59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>100.58984375</v>
+      </c>
+      <c r="O6">
+        <v>100.58984375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -786,12 +807,15 @@
         <v>81.4501953125</v>
       </c>
       <c r="N7">
-        <v>113.29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>113.2900390625</v>
+      </c>
+      <c r="O7">
+        <v>113.2900390625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -830,12 +854,15 @@
         <v>72.10009765625</v>
       </c>
       <c r="N8">
-        <v>118.53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>118.43994140625</v>
+      </c>
+      <c r="O8">
+        <v>118.43994140625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -874,12 +901,15 @@
         <v>75</v>
       </c>
       <c r="N9">
-        <v>108.48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>108.39013671875</v>
+      </c>
+      <c r="O9">
+        <v>108.39013671875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -918,12 +948,15 @@
         <v>64.919921875</v>
       </c>
       <c r="N10">
-        <v>118.24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>118.240234375</v>
+      </c>
+      <c r="O10">
+        <v>118.240234375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -962,12 +995,15 @@
         <v>69.89990234375</v>
       </c>
       <c r="N11">
-        <v>108.59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>108.58984375</v>
+      </c>
+      <c r="O11">
+        <v>108.58984375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -1006,12 +1042,15 @@
         <v>77.35009765625</v>
       </c>
       <c r="N12">
-        <v>115.44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>115.43994140625</v>
+      </c>
+      <c r="O12">
+        <v>115.43994140625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1050,12 +1089,15 @@
         <v>101.25</v>
       </c>
       <c r="N13">
-        <v>102.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>102.990234375</v>
+      </c>
+      <c r="O13">
+        <v>102.990234375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1094,12 +1136,15 @@
         <v>84.39990234375</v>
       </c>
       <c r="N14">
-        <v>108.59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>108.58984375</v>
+      </c>
+      <c r="O14">
+        <v>108.58984375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1138,12 +1183,15 @@
         <v>76.7998046875</v>
       </c>
       <c r="N15">
-        <v>85.94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>85.93994140625</v>
+      </c>
+      <c r="O15">
+        <v>85.93994140625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1182,12 +1230,15 @@
         <v>57.10009765625</v>
       </c>
       <c r="N16">
-        <v>31.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>31.050048828125</v>
+      </c>
+      <c r="O16">
+        <v>31.050048828125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1226,12 +1277,15 @@
         <v>35.2900390625</v>
       </c>
       <c r="N17">
-        <v>54.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>54.830078125</v>
+      </c>
+      <c r="O17">
+        <v>54.830078125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1270,12 +1324,15 @@
         <v>81.9501953125</v>
       </c>
       <c r="N18">
-        <v>113.19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>113.18994140625</v>
+      </c>
+      <c r="O18">
+        <v>113.18994140625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1314,12 +1371,15 @@
         <v>41.570068359375</v>
       </c>
       <c r="N19">
-        <v>96.84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>96.83984375</v>
+      </c>
+      <c r="O19">
+        <v>96.83984375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1358,12 +1418,15 @@
         <v>83.5</v>
       </c>
       <c r="N20">
-        <v>114.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>114.08984375</v>
+      </c>
+      <c r="O20">
+        <v>114.08984375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1402,12 +1465,15 @@
         <v>86.66015625</v>
       </c>
       <c r="N21">
-        <v>106.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>106.39013671875</v>
+      </c>
+      <c r="O21">
+        <v>106.39013671875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1446,6 +1512,9 @@
         <v>0</v>
       </c>
       <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>0</v>
       </c>
     </row>
@@ -1461,107 +1530,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1581,7 +1650,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1589,7 +1658,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1597,7 +1666,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1605,7 +1674,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1613,7 +1682,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1621,7 +1690,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1629,7 +1698,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1637,7 +1706,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1645,7 +1714,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1653,7 +1722,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1661,7 +1730,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1669,7 +1738,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1677,7 +1746,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1685,7 +1754,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1693,7 +1762,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1701,7 +1770,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1709,7 +1778,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1717,7 +1786,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1725,7 +1794,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1733,7 +1802,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1756,7 +1825,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1764,7 +1833,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1772,7 +1841,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1780,7 +1849,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1788,7 +1857,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1796,7 +1865,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1804,7 +1873,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1812,7 +1881,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1820,7 +1889,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1828,7 +1897,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1836,7 +1905,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1844,7 +1913,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1852,7 +1921,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1860,7 +1929,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1868,7 +1937,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1876,7 +1945,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1884,7 +1953,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1892,7 +1961,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1900,7 +1969,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1908,7 +1977,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1931,7 +2000,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -1939,7 +2008,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -1947,7 +2016,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -1955,7 +2024,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -1963,7 +2032,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -1971,7 +2040,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -1979,7 +2048,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -1987,7 +2056,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -1995,7 +2064,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -2003,7 +2072,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -2011,7 +2080,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -2019,7 +2088,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -2027,7 +2096,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -2035,7 +2104,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -2043,7 +2112,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -2051,7 +2120,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -2059,7 +2128,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -2067,7 +2136,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -2075,7 +2144,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -2083,7 +2152,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -2106,7 +2175,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -2114,7 +2183,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -2122,7 +2191,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -2130,7 +2199,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2138,7 +2207,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2146,7 +2215,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2154,7 +2223,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2162,7 +2231,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2170,7 +2239,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2178,7 +2247,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2186,7 +2255,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2194,7 +2263,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2202,7 +2271,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2210,7 +2279,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2218,7 +2287,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2226,7 +2295,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2234,7 +2303,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2242,7 +2311,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2250,7 +2319,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2258,7 +2327,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2281,162 +2350,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2">
-        <v>461.19986328125</v>
+        <v>461.19970703125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>455.02017578125</v>
+        <v>455.02001953125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4">
-        <v>437.47994140625</v>
+        <v>437.47998046875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
-        <v>425.750107421875</v>
+        <v>425.750244140625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6">
-        <v>425.190244140625</v>
+        <v>425.190185546875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>424.00015625</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8">
-        <v>420.729990234375</v>
+        <v>420.730224609375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>417.869892578125</v>
+        <v>417.780029296875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>405.330283203125</v>
+        <v>405.330322265625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>403.640146484375</v>
+        <v>403.640380859375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>394.780087890625</v>
+        <v>394.780029296875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>383.740146484375</v>
+        <v>383.739990234375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
-        <v>381.289853515625</v>
+        <v>381.289794921875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>380.31001953125</v>
+        <v>380.31005859375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>377.1100927734375</v>
+        <v>377.1102294921875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
-        <v>373.9700634765625</v>
+        <v>373.8800048828125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>340.8901953125</v>
+        <v>340.89013671875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19">
-        <v>326.439853515625</v>
+        <v>326.439697265625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20">
-        <v>255.0601318359375</v>
+        <v>255.0601806640625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
-        <v>213.10001953125</v>
+        <v>213.10009765625</v>
       </c>
     </row>
   </sheetData>
@@ -2456,58 +2525,58 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>118.43994140625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>118.240234375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>115.43994140625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>114.08984375</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>113.2900390625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>113.18994140625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>112.2900390625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2515,103 +2584,103 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>108.58984375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>108.58984375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>108.39013671875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>102.990234375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100.58984375</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>99.39013671875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>98.43994140625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>96.83984375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>88.0400390625</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>85.93994140625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>54.830078125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>31.050048828125</v>
       </c>
     </row>
   </sheetData>
@@ -2631,7 +2700,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2639,7 +2708,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2647,7 +2716,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2655,7 +2724,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2663,7 +2732,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2671,7 +2740,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2679,7 +2748,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2687,7 +2756,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2695,7 +2764,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2703,7 +2772,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2711,7 +2780,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2719,7 +2788,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2727,7 +2796,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2735,7 +2804,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2743,7 +2812,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2751,7 +2820,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2759,7 +2828,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2767,7 +2836,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2775,7 +2844,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2783,7 +2852,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="36">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>Rodada 14</t>
+  </si>
+  <si>
+    <t>Rodada 15</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -484,10 +487,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,10 +533,13 @@
       <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -575,12 +581,15 @@
         <v>99.39013671875</v>
       </c>
       <c r="O2">
-        <v>99.39013671875</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>57.8798828125</v>
+      </c>
+      <c r="P2">
+        <v>57.8798828125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -622,12 +631,15 @@
         <v>88.0400390625</v>
       </c>
       <c r="O3">
-        <v>88.0400390625</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>69.4501953125</v>
+      </c>
+      <c r="P3">
+        <v>69.4501953125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -669,12 +681,15 @@
         <v>98.43994140625</v>
       </c>
       <c r="O4">
-        <v>98.43994140625</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>78.4501953125</v>
+      </c>
+      <c r="P4">
+        <v>78.4501953125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -716,12 +731,15 @@
         <v>112.2900390625</v>
       </c>
       <c r="O5">
-        <v>112.2900390625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>55.139892578125</v>
+      </c>
+      <c r="P5">
+        <v>55.139892578125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -763,12 +781,15 @@
         <v>100.58984375</v>
       </c>
       <c r="O6">
-        <v>100.58984375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>53.25</v>
+      </c>
+      <c r="P6">
+        <v>53.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -810,12 +831,15 @@
         <v>113.2900390625</v>
       </c>
       <c r="O7">
-        <v>113.2900390625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>61.949951171875</v>
+      </c>
+      <c r="P7">
+        <v>61.949951171875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -857,12 +881,15 @@
         <v>118.43994140625</v>
       </c>
       <c r="O8">
-        <v>118.43994140625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>70.14013671875</v>
+      </c>
+      <c r="P8">
+        <v>70.14013671875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -904,12 +931,15 @@
         <v>108.39013671875</v>
       </c>
       <c r="O9">
-        <v>108.39013671875</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>67.83984375</v>
+      </c>
+      <c r="P9">
+        <v>67.83984375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -951,12 +981,15 @@
         <v>118.240234375</v>
       </c>
       <c r="O10">
-        <v>118.240234375</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>58.43994140625</v>
+      </c>
+      <c r="P10">
+        <v>58.43994140625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -998,12 +1031,15 @@
         <v>108.58984375</v>
       </c>
       <c r="O11">
-        <v>108.58984375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>71.25</v>
+      </c>
+      <c r="P11">
+        <v>71.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -1045,12 +1081,15 @@
         <v>115.43994140625</v>
       </c>
       <c r="O12">
-        <v>115.43994140625</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>57.72998046875</v>
+      </c>
+      <c r="P12">
+        <v>57.72998046875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1092,12 +1131,15 @@
         <v>102.990234375</v>
       </c>
       <c r="O13">
-        <v>102.990234375</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>66.080078125</v>
+      </c>
+      <c r="P13">
+        <v>66.080078125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1139,12 +1181,15 @@
         <v>108.58984375</v>
       </c>
       <c r="O14">
-        <v>108.58984375</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>49.280029296875</v>
+      </c>
+      <c r="P14">
+        <v>49.280029296875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1186,12 +1231,15 @@
         <v>85.93994140625</v>
       </c>
       <c r="O15">
-        <v>85.93994140625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>66.0498046875</v>
+      </c>
+      <c r="P15">
+        <v>66.0498046875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1233,12 +1281,15 @@
         <v>31.050048828125</v>
       </c>
       <c r="O16">
-        <v>31.050048828125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>31.6500244140625</v>
+      </c>
+      <c r="P16">
+        <v>31.6500244140625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1280,12 +1331,15 @@
         <v>54.830078125</v>
       </c>
       <c r="O17">
-        <v>54.830078125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>30.030029296875</v>
+      </c>
+      <c r="P17">
+        <v>30.030029296875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1327,12 +1381,15 @@
         <v>113.18994140625</v>
       </c>
       <c r="O18">
-        <v>113.18994140625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>50.75</v>
+      </c>
+      <c r="P18">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1374,12 +1431,15 @@
         <v>96.83984375</v>
       </c>
       <c r="O19">
-        <v>96.83984375</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>47.43994140625</v>
+      </c>
+      <c r="P19">
+        <v>47.43994140625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1421,12 +1481,15 @@
         <v>114.08984375</v>
       </c>
       <c r="O20">
-        <v>114.08984375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>57.14990234375</v>
+      </c>
+      <c r="P20">
+        <v>57.14990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1468,12 +1531,15 @@
         <v>106.39013671875</v>
       </c>
       <c r="O21">
-        <v>106.39013671875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>53.780029296875</v>
+      </c>
+      <c r="P21">
+        <v>53.780029296875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1515,6 +1581,9 @@
         <v>0</v>
       </c>
       <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
         <v>0</v>
       </c>
     </row>
@@ -1530,107 +1599,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1650,7 +1719,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1658,7 +1727,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1666,7 +1735,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1674,7 +1743,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1682,7 +1751,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1690,7 +1759,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1698,7 +1767,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1706,7 +1775,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1714,7 +1783,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1722,7 +1791,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1730,7 +1799,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1738,7 +1807,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1746,7 +1815,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1754,7 +1823,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1762,7 +1831,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1770,7 +1839,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1778,7 +1847,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1786,7 +1855,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1794,7 +1863,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1802,7 +1871,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1825,7 +1894,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1833,7 +1902,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1841,7 +1910,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1849,7 +1918,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1857,7 +1926,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1865,7 +1934,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1873,7 +1942,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1881,7 +1950,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1889,7 +1958,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1897,7 +1966,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1905,7 +1974,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1913,7 +1982,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1921,7 +1990,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1929,7 +1998,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1937,7 +2006,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -1945,7 +2014,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -1953,7 +2022,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -1961,7 +2030,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -1969,7 +2038,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -1977,7 +2046,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2000,7 +2069,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -2008,7 +2077,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -2016,7 +2085,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -2024,7 +2093,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -2032,7 +2101,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -2040,7 +2109,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -2048,7 +2117,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -2056,7 +2125,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -2064,7 +2133,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -2072,7 +2141,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -2080,7 +2149,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -2088,7 +2157,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -2096,7 +2165,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -2104,7 +2173,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -2112,7 +2181,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -2120,7 +2189,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -2128,7 +2197,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -2136,7 +2205,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -2144,7 +2213,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -2152,7 +2221,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -2175,7 +2244,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -2183,7 +2252,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -2191,7 +2260,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -2199,7 +2268,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2207,7 +2276,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2215,7 +2284,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2223,7 +2292,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2231,7 +2300,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2239,7 +2308,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2247,7 +2316,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2255,7 +2324,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2263,7 +2332,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2271,7 +2340,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2279,7 +2348,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2287,7 +2356,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2295,7 +2364,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2303,7 +2372,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2311,7 +2380,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2319,7 +2388,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2327,7 +2396,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2350,7 +2419,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>461.19970703125</v>
@@ -2358,7 +2427,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>455.02001953125</v>
@@ -2366,7 +2435,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>437.47998046875</v>
@@ -2374,7 +2443,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>425.750244140625</v>
@@ -2382,7 +2451,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>425.190185546875</v>
@@ -2390,7 +2459,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>424</v>
@@ -2398,7 +2467,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>420.730224609375</v>
@@ -2406,7 +2475,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>417.780029296875</v>
@@ -2414,7 +2483,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>405.330322265625</v>
@@ -2422,7 +2491,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>403.640380859375</v>
@@ -2430,7 +2499,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>394.780029296875</v>
@@ -2438,7 +2507,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>383.739990234375</v>
@@ -2446,7 +2515,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>381.289794921875</v>
@@ -2454,7 +2523,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>380.31005859375</v>
@@ -2462,7 +2531,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>377.1102294921875</v>
@@ -2470,7 +2539,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>373.8800048828125</v>
@@ -2478,7 +2547,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>340.89013671875</v>
@@ -2486,7 +2555,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>326.439697265625</v>
@@ -2494,7 +2563,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>255.0601806640625</v>
@@ -2502,7 +2571,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>213.10009765625</v>
@@ -2525,66 +2594,66 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>118.43994140625</v>
+        <v>156.900390625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>118.240234375</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4">
-        <v>115.43994140625</v>
+        <v>140.2802734375</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>114.08984375</v>
+        <v>138.900390625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>113.2900390625</v>
+        <v>135.6796875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>113.18994140625</v>
+        <v>132.16015625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>112.2900390625</v>
+        <v>132.099609375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>108.58984375</v>
+        <v>123.89990234375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2592,31 +2661,31 @@
         <v>23</v>
       </c>
       <c r="B10">
-        <v>108.58984375</v>
+        <v>116.8798828125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B11">
-        <v>108.39013671875</v>
+        <v>115.759765625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B12">
-        <v>106.39013671875</v>
+        <v>115.4599609375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B13">
-        <v>102.990234375</v>
+        <v>114.2998046875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2624,23 +2693,23 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>100.58984375</v>
+        <v>110.27978515625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B15">
-        <v>99.39013671875</v>
+        <v>107.56005859375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>98.43994140625</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2648,23 +2717,23 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>96.83984375</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>88.0400390625</v>
+        <v>98.56005859375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>85.93994140625</v>
+        <v>94.8798828125</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2672,15 +2741,15 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>54.830078125</v>
+        <v>63.300048828125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>31.050048828125</v>
+        <v>60.06005859375</v>
       </c>
     </row>
   </sheetData>
@@ -2700,7 +2769,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2708,7 +2777,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2716,7 +2785,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2724,7 +2793,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2732,7 +2801,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2740,7 +2809,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2748,7 +2817,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2756,7 +2825,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2764,7 +2833,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2772,7 +2841,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2780,7 +2849,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2788,7 +2857,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2796,7 +2865,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2804,7 +2873,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2812,7 +2881,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2820,7 +2889,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2828,7 +2897,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2836,7 +2905,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2844,7 +2913,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2852,7 +2921,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -584,7 +584,7 @@
         <v>57.8798828125</v>
       </c>
       <c r="P2">
-        <v>57.8798828125</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -634,7 +634,7 @@
         <v>69.4501953125</v>
       </c>
       <c r="P3">
-        <v>69.4501953125</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -684,7 +684,7 @@
         <v>78.4501953125</v>
       </c>
       <c r="P4">
-        <v>78.4501953125</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -734,7 +734,7 @@
         <v>55.139892578125</v>
       </c>
       <c r="P5">
-        <v>55.139892578125</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -784,7 +784,7 @@
         <v>53.25</v>
       </c>
       <c r="P6">
-        <v>53.25</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -834,7 +834,7 @@
         <v>61.949951171875</v>
       </c>
       <c r="P7">
-        <v>61.949951171875</v>
+        <v>60.17</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -884,7 +884,7 @@
         <v>70.14013671875</v>
       </c>
       <c r="P8">
-        <v>70.14013671875</v>
+        <v>81.98</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -934,7 +934,7 @@
         <v>67.83984375</v>
       </c>
       <c r="P9">
-        <v>67.83984375</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -984,7 +984,7 @@
         <v>58.43994140625</v>
       </c>
       <c r="P10">
-        <v>58.43994140625</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1034,7 +1034,7 @@
         <v>71.25</v>
       </c>
       <c r="P11">
-        <v>71.25</v>
+        <v>55.52</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1084,7 +1084,7 @@
         <v>57.72998046875</v>
       </c>
       <c r="P12">
-        <v>57.72998046875</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1134,7 +1134,7 @@
         <v>66.080078125</v>
       </c>
       <c r="P13">
-        <v>66.080078125</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1184,7 +1184,7 @@
         <v>49.280029296875</v>
       </c>
       <c r="P14">
-        <v>49.280029296875</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1234,7 +1234,7 @@
         <v>66.0498046875</v>
       </c>
       <c r="P15">
-        <v>66.0498046875</v>
+        <v>35.42</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1284,7 +1284,7 @@
         <v>31.6500244140625</v>
       </c>
       <c r="P16">
-        <v>31.6500244140625</v>
+        <v>31.34</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1334,7 +1334,7 @@
         <v>30.030029296875</v>
       </c>
       <c r="P17">
-        <v>30.030029296875</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1384,7 +1384,7 @@
         <v>50.75</v>
       </c>
       <c r="P18">
-        <v>50.75</v>
+        <v>45.92</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1434,7 +1434,7 @@
         <v>47.43994140625</v>
       </c>
       <c r="P19">
-        <v>47.43994140625</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1484,7 +1484,7 @@
         <v>57.14990234375</v>
       </c>
       <c r="P20">
-        <v>57.14990234375</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1534,7 +1534,7 @@
         <v>53.780029296875</v>
       </c>
       <c r="P21">
-        <v>53.780029296875</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2594,162 +2594,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>156.900390625</v>
+        <v>152.12013671875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>142.5</v>
+        <v>132.03984375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>140.2802734375</v>
+        <v>126.77</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5">
-        <v>138.900390625</v>
+        <v>123.6001953125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>135.6796875</v>
+        <v>122.119951171875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>132.16015625</v>
+        <v>120.4301953125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B8">
-        <v>132.099609375</v>
+        <v>117.530029296875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B9">
-        <v>123.89990234375</v>
+        <v>115.700078125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>116.8798828125</v>
+        <v>113.62998046875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>115.759765625</v>
+        <v>113.179892578125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>115.4599609375</v>
+        <v>111.07990234375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B13">
-        <v>114.2998046875</v>
+        <v>108.63994140625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B14">
-        <v>110.27978515625</v>
+        <v>103.860029296875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>107.56005859375</v>
+        <v>103.6598828125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <v>106.5</v>
+        <v>101.4698046875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>101.5</v>
+        <v>99.63994140625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>98.56005859375</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>94.8798828125</v>
+        <v>92.37</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>63.300048828125</v>
+        <v>72.13002929687499</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21">
-        <v>60.06005859375</v>
+        <v>62.9900244140625</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="37">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Rodada 15</t>
+  </si>
+  <si>
+    <t>Rodada 16</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -487,10 +490,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,10 +539,13 @@
       <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -584,12 +590,15 @@
         <v>57.8798828125</v>
       </c>
       <c r="P2">
-        <v>45.78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <v>45.780029296875</v>
+      </c>
+      <c r="Q2">
+        <v>45.780029296875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -634,12 +643,15 @@
         <v>69.4501953125</v>
       </c>
       <c r="P3">
-        <v>50.98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>50.97998046875</v>
+      </c>
+      <c r="Q3">
+        <v>50.97998046875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -684,12 +696,15 @@
         <v>78.4501953125</v>
       </c>
       <c r="P4">
-        <v>45.15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>45.14990234375</v>
+      </c>
+      <c r="Q4">
+        <v>45.14990234375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -734,12 +749,15 @@
         <v>55.139892578125</v>
       </c>
       <c r="P5">
-        <v>58.04</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>58.179931640625</v>
+      </c>
+      <c r="Q5">
+        <v>58.179931640625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -784,12 +802,15 @@
         <v>53.25</v>
       </c>
       <c r="P6">
-        <v>39.12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>39.1201171875</v>
+      </c>
+      <c r="Q6">
+        <v>39.1201171875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -834,12 +855,15 @@
         <v>61.949951171875</v>
       </c>
       <c r="P7">
-        <v>60.17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>60.169921875</v>
+      </c>
+      <c r="Q7">
+        <v>60.169921875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -884,12 +908,15 @@
         <v>70.14013671875</v>
       </c>
       <c r="P8">
-        <v>81.98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>81.97998046875</v>
+      </c>
+      <c r="Q8">
+        <v>81.97998046875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -934,12 +961,15 @@
         <v>67.83984375</v>
       </c>
       <c r="P9">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>64.2001953125</v>
+      </c>
+      <c r="Q9">
+        <v>64.2001953125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -984,12 +1014,15 @@
         <v>58.43994140625</v>
       </c>
       <c r="P10">
-        <v>50.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>50.199951171875</v>
+      </c>
+      <c r="Q10">
+        <v>50.199951171875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -1034,12 +1067,15 @@
         <v>71.25</v>
       </c>
       <c r="P11">
-        <v>55.52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>55.52001953125</v>
+      </c>
+      <c r="Q11">
+        <v>55.52001953125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -1084,12 +1120,15 @@
         <v>57.72998046875</v>
       </c>
       <c r="P12">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>55.89990234375</v>
+      </c>
+      <c r="Q12">
+        <v>55.89990234375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1134,12 +1173,15 @@
         <v>66.080078125</v>
       </c>
       <c r="P13">
-        <v>49.62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>49.6201171875</v>
+      </c>
+      <c r="Q13">
+        <v>49.6201171875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1184,12 +1226,15 @@
         <v>49.280029296875</v>
       </c>
       <c r="P14">
-        <v>54.58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>54.580078125</v>
+      </c>
+      <c r="Q14">
+        <v>54.580078125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1234,12 +1279,15 @@
         <v>66.0498046875</v>
       </c>
       <c r="P15">
-        <v>35.42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>35.419921875</v>
+      </c>
+      <c r="Q15">
+        <v>35.419921875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1284,12 +1332,15 @@
         <v>31.6500244140625</v>
       </c>
       <c r="P16">
-        <v>31.34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>32.93994140625</v>
+      </c>
+      <c r="Q16">
+        <v>32.93994140625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1334,12 +1385,15 @@
         <v>30.030029296875</v>
       </c>
       <c r="P17">
-        <v>42.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>42.10009765625</v>
+      </c>
+      <c r="Q17">
+        <v>42.10009765625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1384,12 +1438,15 @@
         <v>50.75</v>
       </c>
       <c r="P18">
-        <v>45.92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+        <v>45.919921875</v>
+      </c>
+      <c r="Q18">
+        <v>45.919921875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1434,12 +1491,15 @@
         <v>47.43994140625</v>
       </c>
       <c r="P19">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>52.199951171875</v>
+      </c>
+      <c r="Q19">
+        <v>52.199951171875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1484,12 +1544,15 @@
         <v>57.14990234375</v>
       </c>
       <c r="P20">
-        <v>53.93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>53.929931640625</v>
+      </c>
+      <c r="Q20">
+        <v>53.929931640625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1536,10 +1599,13 @@
       <c r="P21">
         <v>63.75</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>63.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1584,6 +1650,9 @@
         <v>0</v>
       </c>
       <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
         <v>0</v>
       </c>
     </row>
@@ -1599,107 +1668,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1788,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1727,7 +1796,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1735,7 +1804,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1743,7 +1812,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1751,7 +1820,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1759,7 +1828,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1767,7 +1836,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1775,7 +1844,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1783,7 +1852,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1791,7 +1860,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1799,7 +1868,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1807,7 +1876,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1815,7 +1884,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1823,7 +1892,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1831,7 +1900,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1839,7 +1908,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1847,7 +1916,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1855,7 +1924,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1863,7 +1932,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1871,7 +1940,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1894,7 +1963,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1902,7 +1971,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1910,7 +1979,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1918,7 +1987,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1926,7 +1995,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -1934,7 +2003,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -1942,7 +2011,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -1950,7 +2019,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -1958,7 +2027,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1966,7 +2035,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -1974,7 +2043,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -1982,7 +2051,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -1990,7 +2059,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -1998,7 +2067,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -2006,7 +2075,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -2014,7 +2083,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -2022,7 +2091,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -2030,7 +2099,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -2038,7 +2107,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -2046,7 +2115,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2069,7 +2138,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -2077,7 +2146,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -2085,7 +2154,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -2093,7 +2162,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -2101,7 +2170,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -2109,7 +2178,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -2117,7 +2186,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -2125,7 +2194,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -2133,7 +2202,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -2141,7 +2210,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -2149,7 +2218,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -2157,7 +2226,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -2165,7 +2234,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -2173,7 +2242,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -2181,7 +2250,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -2189,7 +2258,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -2197,7 +2266,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -2205,7 +2274,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -2213,7 +2282,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -2221,7 +2290,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -2244,7 +2313,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -2252,7 +2321,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -2260,7 +2329,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -2268,7 +2337,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2276,7 +2345,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2284,7 +2353,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2292,7 +2361,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2300,7 +2369,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2308,7 +2377,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2316,7 +2385,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2324,7 +2393,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2332,7 +2401,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2340,7 +2409,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2348,7 +2417,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2356,7 +2425,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2364,7 +2433,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2372,7 +2441,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2380,7 +2449,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2388,7 +2457,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2396,7 +2465,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2419,7 +2488,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>461.19970703125</v>
@@ -2427,7 +2496,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>455.02001953125</v>
@@ -2435,7 +2504,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>437.47998046875</v>
@@ -2443,7 +2512,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>425.750244140625</v>
@@ -2451,7 +2520,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>425.190185546875</v>
@@ -2459,7 +2528,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>424</v>
@@ -2467,7 +2536,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>420.730224609375</v>
@@ -2475,7 +2544,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>417.780029296875</v>
@@ -2483,7 +2552,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>405.330322265625</v>
@@ -2491,7 +2560,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>403.640380859375</v>
@@ -2499,7 +2568,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>394.780029296875</v>
@@ -2507,7 +2576,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>383.739990234375</v>
@@ -2515,7 +2584,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>381.289794921875</v>
@@ -2523,7 +2592,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>380.31005859375</v>
@@ -2531,7 +2600,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>377.1102294921875</v>
@@ -2539,7 +2608,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>373.8800048828125</v>
@@ -2547,7 +2616,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>340.89013671875</v>
@@ -2555,7 +2624,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>326.439697265625</v>
@@ -2563,7 +2632,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>255.0601806640625</v>
@@ -2571,7 +2640,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>213.10009765625</v>
@@ -2594,58 +2663,58 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>152.12013671875</v>
+        <v>234.10009765625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>132.03984375</v>
+        <v>196.240234375</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>126.77</v>
+        <v>182.2900390625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>123.6001953125</v>
+        <v>182.289794921875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>122.119951171875</v>
+        <v>181.280029296875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7">
-        <v>120.4301953125</v>
+        <v>171.499755859375</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>117.530029296875</v>
+        <v>171.41015625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2653,63 +2722,63 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>115.700078125</v>
+        <v>169.52978515625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>113.62998046875</v>
+        <v>168.75</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>113.179892578125</v>
+        <v>165.3203125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12">
-        <v>111.07990234375</v>
+        <v>165.009765625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>108.63994140625</v>
+        <v>158.83984375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14">
-        <v>103.860029296875</v>
+        <v>158.440185546875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B15">
-        <v>103.6598828125</v>
+        <v>151.83984375</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B16">
-        <v>101.4698046875</v>
+        <v>149.43994140625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2717,39 +2786,39 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>99.63994140625</v>
+        <v>142.58984375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>96.67</v>
+        <v>136.8896484375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>92.37</v>
+        <v>131.490234375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>72.13002929687499</v>
+        <v>114.230224609375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>62.9900244140625</v>
+        <v>97.5299072265625</v>
       </c>
     </row>
   </sheetData>
@@ -2769,7 +2838,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2777,7 +2846,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2785,7 +2854,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2793,7 +2862,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2801,7 +2870,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2809,7 +2878,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2817,7 +2886,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2825,7 +2894,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2833,7 +2902,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2841,7 +2910,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2849,7 +2918,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2857,7 +2926,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2865,7 +2934,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2873,7 +2942,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2881,7 +2950,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2889,7 +2958,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2897,7 +2966,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2905,7 +2974,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2913,7 +2982,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2921,7 +2990,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -593,7 +593,7 @@
         <v>45.780029296875</v>
       </c>
       <c r="Q2">
-        <v>45.780029296875</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -646,7 +646,7 @@
         <v>50.97998046875</v>
       </c>
       <c r="Q3">
-        <v>50.97998046875</v>
+        <v>57.83</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -699,7 +699,7 @@
         <v>45.14990234375</v>
       </c>
       <c r="Q4">
-        <v>45.14990234375</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -752,7 +752,7 @@
         <v>58.179931640625</v>
       </c>
       <c r="Q5">
-        <v>58.179931640625</v>
+        <v>96.79000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -805,7 +805,7 @@
         <v>39.1201171875</v>
       </c>
       <c r="Q6">
-        <v>39.1201171875</v>
+        <v>86.83</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -858,7 +858,7 @@
         <v>60.169921875</v>
       </c>
       <c r="Q7">
-        <v>60.169921875</v>
+        <v>72.28</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -911,7 +911,7 @@
         <v>81.97998046875</v>
       </c>
       <c r="Q8">
-        <v>81.97998046875</v>
+        <v>81.78</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -964,7 +964,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="Q9">
-        <v>64.2001953125</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1017,7 +1017,7 @@
         <v>50.199951171875</v>
       </c>
       <c r="Q10">
-        <v>50.199951171875</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1070,7 +1070,7 @@
         <v>55.52001953125</v>
       </c>
       <c r="Q11">
-        <v>55.52001953125</v>
+        <v>69.15000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1123,7 +1123,7 @@
         <v>55.89990234375</v>
       </c>
       <c r="Q12">
-        <v>55.89990234375</v>
+        <v>103.39</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1176,7 +1176,7 @@
         <v>49.6201171875</v>
       </c>
       <c r="Q13">
-        <v>49.6201171875</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1229,7 +1229,7 @@
         <v>54.580078125</v>
       </c>
       <c r="Q14">
-        <v>54.580078125</v>
+        <v>68.58</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1282,7 +1282,7 @@
         <v>35.419921875</v>
       </c>
       <c r="Q15">
-        <v>35.419921875</v>
+        <v>91.34999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1335,7 +1335,7 @@
         <v>32.93994140625</v>
       </c>
       <c r="Q16">
-        <v>32.93994140625</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1388,7 +1388,7 @@
         <v>42.10009765625</v>
       </c>
       <c r="Q17">
-        <v>42.10009765625</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1441,7 +1441,7 @@
         <v>45.919921875</v>
       </c>
       <c r="Q18">
-        <v>45.919921875</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1494,7 +1494,7 @@
         <v>52.199951171875</v>
       </c>
       <c r="Q19">
-        <v>52.199951171875</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1547,7 +1547,7 @@
         <v>53.929931640625</v>
       </c>
       <c r="Q20">
-        <v>53.929931640625</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1600,7 +1600,7 @@
         <v>63.75</v>
       </c>
       <c r="Q21">
-        <v>63.75</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2666,71 +2666,71 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>234.10009765625</v>
+        <v>233.9001171875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>196.240234375</v>
+        <v>229.10009765625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
-        <v>182.2900390625</v>
+        <v>217.0198828125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>182.289794921875</v>
+        <v>210.10982421875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6">
-        <v>181.280029296875</v>
+        <v>208.079892578125</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>171.499755859375</v>
+        <v>206.7400390625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B8">
-        <v>171.41015625</v>
+        <v>195.92001953125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>169.52978515625</v>
+        <v>194.399873046875</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B10">
-        <v>168.75</v>
+        <v>192.8197265625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2738,39 +2738,39 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>165.3203125</v>
+        <v>191.9801953125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12">
-        <v>165.009765625</v>
+        <v>190.610029296875</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>158.83984375</v>
+        <v>190.279833984375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B14">
-        <v>158.440185546875</v>
+        <v>183.189892578125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>151.83984375</v>
+        <v>179.2001171875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2778,47 +2778,47 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>149.43994140625</v>
+        <v>178.409912109375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B17">
-        <v>142.58984375</v>
+        <v>178.26017578125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18">
-        <v>136.8896484375</v>
+        <v>172.440107421875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>131.490234375</v>
+        <v>160.269921875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>114.230224609375</v>
+        <v>113.5299658203125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
-        <v>97.5299072265625</v>
+        <v>91.64012695312501</v>
       </c>
     </row>
   </sheetData>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="38">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>Rodada 16</t>
+  </si>
+  <si>
+    <t>Rodada 17</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -490,10 +493,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -542,10 +545,13 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -595,10 +601,13 @@
       <c r="Q2">
         <v>74.75</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2">
+        <v>74.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -646,12 +655,15 @@
         <v>50.97998046875</v>
       </c>
       <c r="Q3">
-        <v>57.83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>57.830078125</v>
+      </c>
+      <c r="R3">
+        <v>57.830078125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -701,10 +713,13 @@
       <c r="Q4">
         <v>105.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -752,12 +767,15 @@
         <v>58.179931640625</v>
       </c>
       <c r="Q5">
-        <v>96.79000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>96.7900390625</v>
+      </c>
+      <c r="R5">
+        <v>96.7900390625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -805,12 +823,15 @@
         <v>39.1201171875</v>
       </c>
       <c r="Q6">
-        <v>86.83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+        <v>86.830078125</v>
+      </c>
+      <c r="R6">
+        <v>86.830078125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -858,12 +879,15 @@
         <v>60.169921875</v>
       </c>
       <c r="Q7">
-        <v>72.28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+        <v>72.27978515625</v>
+      </c>
+      <c r="R7">
+        <v>72.27978515625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -911,12 +935,15 @@
         <v>81.97998046875</v>
       </c>
       <c r="Q8">
-        <v>81.78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
+        <v>81.77978515625</v>
+      </c>
+      <c r="R8">
+        <v>81.77978515625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -964,12 +991,15 @@
         <v>64.2001953125</v>
       </c>
       <c r="Q9">
-        <v>74.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
+        <v>74.7001953125</v>
+      </c>
+      <c r="R9">
+        <v>74.7001953125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1017,12 +1047,15 @@
         <v>50.199951171875</v>
       </c>
       <c r="Q10">
-        <v>74.55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
+        <v>74.5498046875</v>
+      </c>
+      <c r="R10">
+        <v>74.5498046875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -1070,12 +1103,15 @@
         <v>55.52001953125</v>
       </c>
       <c r="Q11">
-        <v>69.15000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+        <v>69.14990234375</v>
+      </c>
+      <c r="R11">
+        <v>69.14990234375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -1123,12 +1159,15 @@
         <v>55.89990234375</v>
       </c>
       <c r="Q12">
-        <v>103.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
+        <v>103.39013671875</v>
+      </c>
+      <c r="R12">
+        <v>103.39013671875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1176,12 +1215,15 @@
         <v>49.6201171875</v>
       </c>
       <c r="Q13">
-        <v>76.28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
+        <v>76.27978515625</v>
+      </c>
+      <c r="R13">
+        <v>76.27978515625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1229,12 +1271,15 @@
         <v>54.580078125</v>
       </c>
       <c r="Q14">
-        <v>68.58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
+        <v>68.580078125</v>
+      </c>
+      <c r="R14">
+        <v>68.580078125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1282,12 +1327,15 @@
         <v>35.419921875</v>
       </c>
       <c r="Q15">
-        <v>91.34999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>91.35009765625</v>
+      </c>
+      <c r="R15">
+        <v>91.35009765625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1335,12 +1383,15 @@
         <v>32.93994140625</v>
       </c>
       <c r="Q16">
-        <v>48.94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>48.93994140625</v>
+      </c>
+      <c r="R16">
+        <v>48.93994140625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1388,12 +1439,15 @@
         <v>42.10009765625</v>
       </c>
       <c r="Q17">
-        <v>19.51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+        <v>19.510009765625</v>
+      </c>
+      <c r="R17">
+        <v>19.510009765625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1441,12 +1495,15 @@
         <v>45.919921875</v>
       </c>
       <c r="Q18">
-        <v>63.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
+        <v>63.60009765625</v>
+      </c>
+      <c r="R18">
+        <v>63.60009765625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1494,12 +1551,15 @@
         <v>52.199951171875</v>
       </c>
       <c r="Q19">
-        <v>108.44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
+        <v>108.43994140625</v>
+      </c>
+      <c r="R19">
+        <v>108.43994140625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1547,12 +1607,15 @@
         <v>53.929931640625</v>
       </c>
       <c r="Q20">
-        <v>79.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
+        <v>79.2001953125</v>
+      </c>
+      <c r="R20">
+        <v>79.2001953125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1600,12 +1663,15 @@
         <v>63.75</v>
       </c>
       <c r="Q21">
-        <v>73.08</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
+        <v>73.080078125</v>
+      </c>
+      <c r="R21">
+        <v>73.080078125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1653,6 +1719,9 @@
         <v>0</v>
       </c>
       <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
         <v>0</v>
       </c>
     </row>
@@ -1668,107 +1737,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1788,7 +1857,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1796,7 +1865,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1804,7 +1873,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1812,7 +1881,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1820,7 +1889,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1828,7 +1897,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1836,7 +1905,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1844,7 +1913,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1852,7 +1921,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1860,7 +1929,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1868,7 +1937,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1876,7 +1945,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1884,7 +1953,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1892,7 +1961,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1900,7 +1969,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1908,7 +1977,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1916,7 +1985,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1924,7 +1993,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1932,7 +2001,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1940,7 +2009,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1963,7 +2032,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -1971,7 +2040,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -1979,7 +2048,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -1987,7 +2056,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -1995,7 +2064,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -2003,7 +2072,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -2011,7 +2080,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -2019,7 +2088,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -2027,7 +2096,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -2035,7 +2104,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -2043,7 +2112,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -2051,7 +2120,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -2059,7 +2128,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -2067,7 +2136,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -2075,7 +2144,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -2083,7 +2152,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -2091,7 +2160,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -2099,7 +2168,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -2107,7 +2176,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -2115,7 +2184,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2138,7 +2207,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -2146,7 +2215,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -2154,7 +2223,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -2162,7 +2231,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -2170,7 +2239,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -2178,7 +2247,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -2186,7 +2255,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -2194,7 +2263,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -2202,7 +2271,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -2210,7 +2279,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -2218,7 +2287,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -2226,7 +2295,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -2234,7 +2303,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -2242,7 +2311,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -2250,7 +2319,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -2258,7 +2327,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -2266,7 +2335,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -2274,7 +2343,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -2282,7 +2351,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -2290,7 +2359,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -2313,7 +2382,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -2321,7 +2390,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -2329,7 +2398,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -2337,7 +2406,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2345,7 +2414,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2353,7 +2422,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2361,7 +2430,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2369,7 +2438,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2377,7 +2446,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2385,7 +2454,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2393,7 +2462,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2401,7 +2470,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2409,7 +2478,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2417,7 +2486,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2425,7 +2494,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2433,7 +2502,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2441,7 +2510,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2449,7 +2518,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2457,7 +2526,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2465,7 +2534,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2488,7 +2557,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>461.19970703125</v>
@@ -2496,7 +2565,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>455.02001953125</v>
@@ -2504,7 +2573,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>437.47998046875</v>
@@ -2512,7 +2581,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>425.750244140625</v>
@@ -2520,7 +2589,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>425.190185546875</v>
@@ -2528,7 +2597,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>424</v>
@@ -2536,7 +2605,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>420.730224609375</v>
@@ -2544,7 +2613,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>417.780029296875</v>
@@ -2552,7 +2621,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>405.330322265625</v>
@@ -2560,7 +2629,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>403.640380859375</v>
@@ -2568,7 +2637,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>394.780029296875</v>
@@ -2576,7 +2645,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>383.739990234375</v>
@@ -2584,7 +2653,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>381.289794921875</v>
@@ -2592,7 +2661,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>380.31005859375</v>
@@ -2600,7 +2669,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>377.1102294921875</v>
@@ -2608,7 +2677,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>373.8800048828125</v>
@@ -2616,7 +2685,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>340.89013671875</v>
@@ -2624,7 +2693,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>326.439697265625</v>
@@ -2632,7 +2701,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>255.0601806640625</v>
@@ -2640,7 +2709,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>213.10009765625</v>
@@ -2663,162 +2732,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B2">
-        <v>233.9001171875</v>
+        <v>334.60009765625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B3">
-        <v>229.10009765625</v>
+        <v>320.41015625</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B4">
-        <v>217.0198828125</v>
+        <v>316.519775390625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B5">
-        <v>210.10982421875</v>
+        <v>315.6796875</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>208.079892578125</v>
+        <v>306.89990234375</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>206.7400390625</v>
+        <v>284.169921875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>195.92001953125</v>
+        <v>281.4404296875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B9">
-        <v>194.399873046875</v>
+        <v>269.480224609375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10">
-        <v>192.8197265625</v>
+        <v>268.259765625</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>191.9801953125</v>
+        <v>266.679443359375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>190.610029296875</v>
+        <v>266.0302734375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B13">
-        <v>190.279833984375</v>
+        <v>265.06982421875</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B14">
-        <v>183.189892578125</v>
+        <v>263.690185546875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B15">
-        <v>179.2001171875</v>
+        <v>257.739501953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16">
-        <v>178.409912109375</v>
+        <v>253.159912109375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B17">
-        <v>178.26017578125</v>
+        <v>241.020263671875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B18">
-        <v>172.440107421875</v>
+        <v>236.09033203125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>160.269921875</v>
+        <v>223.8701171875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>113.5299658203125</v>
+        <v>162.4698486328125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
-        <v>91.64012695312501</v>
+        <v>111.150146484375</v>
       </c>
     </row>
   </sheetData>
@@ -2838,7 +2907,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2846,7 +2915,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2854,7 +2923,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2862,7 +2931,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2870,7 +2939,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2878,7 +2947,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2886,7 +2955,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2894,7 +2963,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2902,7 +2971,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2910,7 +2979,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2918,7 +2987,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2926,7 +2995,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2934,7 +3003,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2942,7 +3011,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2950,7 +3019,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2958,7 +3027,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2966,7 +3035,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2974,7 +3043,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2982,7 +3051,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2990,7 +3059,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="39">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Rodada 17</t>
+  </si>
+  <si>
+    <t>Rodada 18</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -493,10 +496,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,10 +551,13 @@
       <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -602,12 +608,15 @@
         <v>74.75</v>
       </c>
       <c r="R2">
-        <v>74.75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+        <v>68.02001953125</v>
+      </c>
+      <c r="S2">
+        <v>68.02001953125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -658,12 +667,15 @@
         <v>57.830078125</v>
       </c>
       <c r="R3">
-        <v>57.830078125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>76.8701171875</v>
+      </c>
+      <c r="S3">
+        <v>76.8701171875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -714,12 +726,15 @@
         <v>105.5</v>
       </c>
       <c r="R4">
-        <v>105.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>85.919921875</v>
+      </c>
+      <c r="S4">
+        <v>85.919921875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -770,12 +785,15 @@
         <v>96.7900390625</v>
       </c>
       <c r="R5">
-        <v>96.7900390625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>61.419921875</v>
+      </c>
+      <c r="S5">
+        <v>61.419921875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -826,12 +844,15 @@
         <v>86.830078125</v>
       </c>
       <c r="R6">
-        <v>86.830078125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>61.77001953125</v>
+      </c>
+      <c r="S6">
+        <v>61.77001953125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -882,12 +903,15 @@
         <v>72.27978515625</v>
       </c>
       <c r="R7">
-        <v>72.27978515625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>65.31982421875</v>
+      </c>
+      <c r="S7">
+        <v>65.31982421875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -938,12 +962,15 @@
         <v>81.77978515625</v>
       </c>
       <c r="R8">
-        <v>81.77978515625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>76.31982421875</v>
+      </c>
+      <c r="S8">
+        <v>76.31982421875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -994,12 +1021,15 @@
         <v>74.7001953125</v>
       </c>
       <c r="R9">
-        <v>74.7001953125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>69.6201171875</v>
+      </c>
+      <c r="S9">
+        <v>69.6201171875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1050,12 +1080,15 @@
         <v>74.5498046875</v>
       </c>
       <c r="R10">
-        <v>74.5498046875</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>82.919921875</v>
+      </c>
+      <c r="S10">
+        <v>82.919921875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -1106,12 +1139,15 @@
         <v>69.14990234375</v>
       </c>
       <c r="R11">
-        <v>69.14990234375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>76.6201171875</v>
+      </c>
+      <c r="S11">
+        <v>76.6201171875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -1162,12 +1198,15 @@
         <v>103.39013671875</v>
       </c>
       <c r="R12">
-        <v>103.39013671875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>60.1201171875</v>
+      </c>
+      <c r="S12">
+        <v>60.1201171875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1218,12 +1257,15 @@
         <v>76.27978515625</v>
       </c>
       <c r="R13">
-        <v>76.27978515625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>58.820068359375</v>
+      </c>
+      <c r="S13">
+        <v>58.820068359375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1274,12 +1316,15 @@
         <v>68.580078125</v>
       </c>
       <c r="R14">
-        <v>68.580078125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>70.81982421875</v>
+      </c>
+      <c r="S14">
+        <v>70.81982421875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1330,12 +1375,15 @@
         <v>91.35009765625</v>
       </c>
       <c r="R15">
-        <v>91.35009765625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>63.60009765625</v>
+      </c>
+      <c r="S15">
+        <v>63.60009765625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1386,12 +1434,15 @@
         <v>48.93994140625</v>
       </c>
       <c r="R16">
-        <v>48.93994140625</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+        <v>75.419921875</v>
+      </c>
+      <c r="S16">
+        <v>75.419921875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1442,12 +1493,15 @@
         <v>19.510009765625</v>
       </c>
       <c r="R17">
-        <v>19.510009765625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>52.949951171875</v>
+      </c>
+      <c r="S17">
+        <v>52.949951171875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1498,12 +1552,15 @@
         <v>63.60009765625</v>
       </c>
       <c r="R18">
-        <v>63.60009765625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+        <v>81.9501953125</v>
+      </c>
+      <c r="S18">
+        <v>81.9501953125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1554,12 +1611,15 @@
         <v>108.43994140625</v>
       </c>
       <c r="R19">
-        <v>108.43994140625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>68.22021484375</v>
+      </c>
+      <c r="S19">
+        <v>68.22021484375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1610,12 +1670,15 @@
         <v>79.2001953125</v>
       </c>
       <c r="R20">
-        <v>79.2001953125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+        <v>66.31982421875</v>
+      </c>
+      <c r="S20">
+        <v>66.31982421875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1666,12 +1729,15 @@
         <v>73.080078125</v>
       </c>
       <c r="R21">
-        <v>73.080078125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>65.6201171875</v>
+      </c>
+      <c r="S21">
+        <v>65.6201171875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1722,6 +1788,9 @@
         <v>0</v>
       </c>
       <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
         <v>0</v>
       </c>
     </row>
@@ -1737,107 +1806,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1857,7 +1926,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1865,7 +1934,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1873,7 +1942,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1881,7 +1950,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1889,7 +1958,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1897,7 +1966,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1905,7 +1974,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1913,7 +1982,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1921,7 +1990,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1929,7 +1998,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1937,7 +2006,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1945,7 +2014,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1953,7 +2022,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1961,7 +2030,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1969,7 +2038,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1977,7 +2046,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1985,7 +2054,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1993,7 +2062,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2001,7 +2070,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2009,7 +2078,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2032,7 +2101,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -2040,7 +2109,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -2048,7 +2117,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -2056,7 +2125,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -2064,7 +2133,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -2072,7 +2141,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -2080,7 +2149,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -2088,7 +2157,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -2096,7 +2165,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -2104,7 +2173,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -2112,7 +2181,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -2120,7 +2189,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -2128,7 +2197,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -2136,7 +2205,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -2144,7 +2213,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -2152,7 +2221,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -2160,7 +2229,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -2168,7 +2237,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -2176,7 +2245,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -2184,7 +2253,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2207,7 +2276,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -2215,7 +2284,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -2223,7 +2292,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -2231,7 +2300,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -2239,7 +2308,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -2247,7 +2316,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -2255,7 +2324,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -2263,7 +2332,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -2271,7 +2340,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -2279,7 +2348,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -2287,7 +2356,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -2295,7 +2364,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -2303,7 +2372,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -2311,7 +2380,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -2319,7 +2388,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -2327,7 +2396,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -2335,7 +2404,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -2343,7 +2412,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -2351,7 +2420,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -2359,7 +2428,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -2382,7 +2451,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -2390,7 +2459,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -2398,7 +2467,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -2406,7 +2475,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2414,7 +2483,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2422,7 +2491,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2430,7 +2499,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2438,7 +2507,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2446,7 +2515,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2454,7 +2523,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2462,7 +2531,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2470,7 +2539,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2478,7 +2547,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2486,7 +2555,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2494,7 +2563,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2502,7 +2571,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2510,7 +2579,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2518,7 +2587,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2526,7 +2595,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2534,7 +2603,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2557,7 +2626,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>461.19970703125</v>
@@ -2565,7 +2634,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>455.02001953125</v>
@@ -2573,7 +2642,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>437.47998046875</v>
@@ -2581,7 +2650,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>425.750244140625</v>
@@ -2589,7 +2658,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>425.190185546875</v>
@@ -2597,7 +2666,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>424</v>
@@ -2605,7 +2674,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>420.730224609375</v>
@@ -2613,7 +2682,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>417.780029296875</v>
@@ -2621,7 +2690,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>405.330322265625</v>
@@ -2629,7 +2698,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>403.640380859375</v>
@@ -2637,7 +2706,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>394.780029296875</v>
@@ -2645,7 +2714,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>383.739990234375</v>
@@ -2653,7 +2722,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>381.289794921875</v>
@@ -2661,7 +2730,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>380.31005859375</v>
@@ -2669,7 +2738,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>377.1102294921875</v>
@@ -2677,7 +2746,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>373.8800048828125</v>
@@ -2685,7 +2754,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>340.89013671875</v>
@@ -2693,7 +2762,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>326.439697265625</v>
@@ -2701,7 +2770,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>255.0601806640625</v>
@@ -2709,7 +2778,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>213.10009765625</v>
@@ -2732,162 +2801,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>334.60009765625</v>
+        <v>400.93994140625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>320.41015625</v>
+        <v>386.53955078125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>316.519775390625</v>
+        <v>349.16015625</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>315.6796875</v>
+        <v>349.029541015625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>306.89990234375</v>
+        <v>345.98046875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B7">
-        <v>284.169921875</v>
+        <v>344.520263671875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8">
-        <v>281.4404296875</v>
+        <v>337.26025390625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>269.480224609375</v>
+        <v>332.94970703125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>268.259765625</v>
+        <v>332.00048828125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
-        <v>266.679443359375</v>
+        <v>325.039306640625</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B12">
-        <v>266.0302734375</v>
+        <v>324.17041015625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B13">
-        <v>265.06982421875</v>
+        <v>322.919677734375</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>263.690185546875</v>
+        <v>321.850341796875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>257.739501953125</v>
+        <v>320.02001953125</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>253.159912109375</v>
+        <v>314.449951171875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17">
-        <v>241.020263671875</v>
+        <v>314.079833984375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>236.09033203125</v>
+        <v>309.6201171875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>223.8701171875</v>
+        <v>302.740234375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20">
-        <v>162.4698486328125</v>
+        <v>264.3697509765625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21">
-        <v>111.150146484375</v>
+        <v>197.5400390625</v>
       </c>
     </row>
   </sheetData>
@@ -2907,7 +2976,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2915,7 +2984,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2923,7 +2992,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2931,7 +3000,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2939,7 +3008,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2947,7 +3016,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -2955,7 +3024,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2963,7 +3032,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2971,7 +3040,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2979,7 +3048,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2987,7 +3056,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2995,7 +3064,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3003,7 +3072,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3011,7 +3080,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -3019,7 +3088,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3027,7 +3096,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3035,7 +3104,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3043,7 +3112,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3051,7 +3120,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3059,7 +3128,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21">
         <v>0</v>

--- a/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
+++ b/liga_classica/datasets_liga_classica/Pontuacoes_Liga_Classica_Aluna_Completa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Rodada 18</t>
+  </si>
+  <si>
+    <t>Rodada 19</t>
   </si>
   <si>
     <t>Arran Katoko FC</t>
@@ -496,10 +499,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,10 +557,13 @@
       <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>64.5</v>
@@ -611,12 +617,15 @@
         <v>68.02001953125</v>
       </c>
       <c r="S2">
-        <v>68.02001953125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>112.25</v>
+      </c>
+      <c r="T2">
+        <v>112.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>63.56005859375</v>
@@ -670,12 +679,15 @@
         <v>76.8701171875</v>
       </c>
       <c r="S3">
-        <v>76.8701171875</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>103.0498046875</v>
+      </c>
+      <c r="T3">
+        <v>103.0498046875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>47.860107421875</v>
@@ -729,12 +741,15 @@
         <v>85.919921875</v>
       </c>
       <c r="S4">
-        <v>85.919921875</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+        <v>121.85009765625</v>
+      </c>
+      <c r="T4">
+        <v>121.85009765625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>66.3701171875</v>
@@ -788,12 +803,15 @@
         <v>61.419921875</v>
       </c>
       <c r="S5">
-        <v>61.419921875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+        <v>105.60009765625</v>
+      </c>
+      <c r="T5">
+        <v>105.60009765625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>83.2001953125</v>
@@ -847,12 +865,15 @@
         <v>61.77001953125</v>
       </c>
       <c r="S6">
-        <v>61.77001953125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
+        <v>95.39990234375</v>
+      </c>
+      <c r="T6">
+        <v>95.39990234375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>53.659912109375</v>
@@ -906,12 +927,15 @@
         <v>65.31982421875</v>
       </c>
       <c r="S7">
-        <v>65.31982421875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
+        <v>106.64990234375</v>
+      </c>
+      <c r="T7">
+        <v>106.64990234375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>71.9599609375</v>
@@ -965,12 +989,15 @@
         <v>76.31982421875</v>
       </c>
       <c r="S8">
-        <v>76.31982421875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+        <v>116.0498046875</v>
+      </c>
+      <c r="T8">
+        <v>116.0498046875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>56.050048828125</v>
@@ -1024,12 +1051,15 @@
         <v>69.6201171875</v>
       </c>
       <c r="S9">
-        <v>69.6201171875</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>104.2998046875</v>
+      </c>
+      <c r="T9">
+        <v>104.2998046875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -1083,12 +1113,15 @@
         <v>82.919921875</v>
       </c>
       <c r="S10">
-        <v>82.919921875</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
+        <v>135.0498046875</v>
+      </c>
+      <c r="T10">
+        <v>135.0498046875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>54.050048828125</v>
@@ -1142,12 +1175,15 @@
         <v>76.6201171875</v>
       </c>
       <c r="S11">
-        <v>76.6201171875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+        <v>125.85009765625</v>
+      </c>
+      <c r="T11">
+        <v>125.85009765625</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>47.860107421875</v>
@@ -1201,12 +1237,15 @@
         <v>60.1201171875</v>
       </c>
       <c r="S12">
-        <v>60.1201171875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+        <v>132.9501953125</v>
+      </c>
+      <c r="T12">
+        <v>132.9501953125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13">
         <v>55.659912109375</v>
@@ -1260,12 +1299,15 @@
         <v>58.820068359375</v>
       </c>
       <c r="S13">
-        <v>58.820068359375</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
+        <v>111.2001953125</v>
+      </c>
+      <c r="T13">
+        <v>111.2001953125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>62.56005859375</v>
@@ -1319,12 +1361,15 @@
         <v>70.81982421875</v>
       </c>
       <c r="S14">
-        <v>70.81982421875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
+        <v>106.10009765625</v>
+      </c>
+      <c r="T14">
+        <v>106.10009765625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -1378,12 +1423,15 @@
         <v>63.60009765625</v>
       </c>
       <c r="S15">
-        <v>63.60009765625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
+        <v>93.10009765625</v>
+      </c>
+      <c r="T15">
+        <v>93.10009765625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1437,12 +1485,15 @@
         <v>75.419921875</v>
       </c>
       <c r="S16">
-        <v>75.419921875</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
+        <v>64.5498046875</v>
+      </c>
+      <c r="T16">
+        <v>64.5498046875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
@@ -1496,12 +1547,15 @@
         <v>52.949951171875</v>
       </c>
       <c r="S17">
-        <v>52.949951171875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+        <v>55.570068359375</v>
+      </c>
+      <c r="T17">
+        <v>55.570068359375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
@@ -1555,12 +1609,15 @@
         <v>81.9501953125</v>
       </c>
       <c r="S18">
-        <v>81.9501953125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
+        <v>132.1201171875</v>
+      </c>
+      <c r="T18">
+        <v>132.1201171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
@@ -1614,12 +1671,15 @@
         <v>68.22021484375</v>
       </c>
       <c r="S19">
-        <v>68.22021484375</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
+        <v>99.2998046875</v>
+      </c>
+      <c r="T19">
+        <v>99.2998046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
@@ -1673,12 +1733,15 @@
         <v>66.31982421875</v>
       </c>
       <c r="S20">
-        <v>66.31982421875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
+        <v>110.0498046875</v>
+      </c>
+      <c r="T20">
+        <v>110.0498046875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
@@ -1732,12 +1795,15 @@
         <v>65.6201171875</v>
       </c>
       <c r="S21">
-        <v>65.6201171875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>111.64990234375</v>
+      </c>
+      <c r="T21">
+        <v>111.64990234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1791,6 +1857,9 @@
         <v>0</v>
       </c>
       <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
         <v>0</v>
       </c>
     </row>
@@ -1806,107 +1875,107 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1926,7 +1995,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1934,7 +2003,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1942,7 +2011,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1950,7 +2019,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1958,7 +2027,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1966,7 +2035,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1974,7 +2043,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1982,7 +2051,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1990,7 +2059,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1998,7 +2067,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2006,7 +2075,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2014,7 +2083,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2022,7 +2091,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2030,7 +2099,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2038,7 +2107,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2046,7 +2115,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2054,7 +2123,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2062,7 +2131,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2070,7 +2139,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2078,7 +2147,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2101,7 +2170,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>83.2001953125</v>
@@ -2109,7 +2178,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>71.9599609375</v>
@@ -2117,7 +2186,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>68.06005859375</v>
@@ -2125,7 +2194,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>67.16015625</v>
@@ -2133,7 +2202,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>66.3701171875</v>
@@ -2141,7 +2210,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>64.5</v>
@@ -2149,7 +2218,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>63.56005859375</v>
@@ -2157,7 +2226,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9">
         <v>62.56005859375</v>
@@ -2165,7 +2234,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>61.56005859375</v>
@@ -2173,7 +2242,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>61.159912109375</v>
@@ -2181,7 +2250,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <v>60.60009765625</v>
@@ -2189,7 +2258,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>56.050048828125</v>
@@ -2197,7 +2266,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14">
         <v>55.659912109375</v>
@@ -2205,7 +2274,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>55.659912109375</v>
@@ -2213,7 +2282,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16">
         <v>54.89990234375</v>
@@ -2221,7 +2290,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>54.050048828125</v>
@@ -2229,7 +2298,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>53.659912109375</v>
@@ -2237,7 +2306,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>47.860107421875</v>
@@ -2245,7 +2314,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <v>47.860107421875</v>
@@ -2253,7 +2322,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2276,7 +2345,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>329.4599609375</v>
@@ -2284,7 +2353,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>269.39013671875</v>
@@ -2292,7 +2361,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>265.3701171875</v>
@@ -2300,7 +2369,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>253.08984375</v>
@@ -2308,7 +2377,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>251.22998046875</v>
@@ -2316,7 +2385,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -2324,7 +2393,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>247.169921875</v>
@@ -2332,7 +2401,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>236.41015625</v>
@@ -2340,7 +2409,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>230.16015625</v>
@@ -2348,7 +2417,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>224.6904296875</v>
@@ -2356,7 +2425,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>211.93994140625</v>
@@ -2364,7 +2433,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>205.830078125</v>
@@ -2372,7 +2441,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14">
         <v>204.1298828125</v>
@@ -2380,7 +2449,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15">
         <v>201.409912109375</v>
@@ -2388,7 +2457,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>200.810302734375</v>
@@ -2396,7 +2465,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17">
         <v>198.440185546875</v>
@@ -2404,7 +2473,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>198.369873046875</v>
@@ -2412,7 +2481,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>186.80029296875</v>
@@ -2420,7 +2489,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>185.770263671875</v>
@@ -2428,7 +2497,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>139.630126953125</v>
@@ -2451,7 +2520,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>344.19970703125</v>
@@ -2459,7 +2528,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>329.4404296875</v>
@@ -2467,7 +2536,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>329.30029296875</v>
@@ -2475,7 +2544,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>309.360107421875</v>
@@ -2483,7 +2552,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>303.949462890625</v>
@@ -2491,7 +2560,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>302.9501953125</v>
@@ -2499,7 +2568,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>300.719970703125</v>
@@ -2507,7 +2576,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>300.1796875</v>
@@ -2515,7 +2584,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>299.49951171875</v>
@@ -2523,7 +2592,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <v>299.199951171875</v>
@@ -2531,7 +2600,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>281.55029296875</v>
@@ -2539,7 +2608,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>278.4697265625</v>
@@ -2547,7 +2616,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>276.829833984375</v>
@@ -2555,7 +2624,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>270.709716796875</v>
@@ -2563,7 +2632,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>266.35986328125</v>
@@ -2571,7 +2640,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>255.9501953125</v>
@@ -2579,7 +2648,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>237.56005859375</v>
@@ -2587,7 +2656,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19">
         <v>225.590087890625</v>
@@ -2595,7 +2664,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>224.219970703125</v>
@@ -2603,7 +2672,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>211.760009765625</v>
@@ -2626,7 +2695,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>461.19970703125</v>
@@ -2634,7 +2703,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>455.02001953125</v>
@@ -2642,7 +2711,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>437.47998046875</v>
@@ -2650,7 +2719,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>425.750244140625</v>
@@ -2658,7 +2727,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>425.190185546875</v>
@@ -2666,7 +2735,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>424</v>
@@ -2674,7 +2743,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>420.730224609375</v>
@@ -2682,7 +2751,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>417.780029296875</v>
@@ -2690,7 +2759,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>405.330322265625</v>
@@ -2698,7 +2767,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>403.640380859375</v>
@@ -2706,7 +2775,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>394.780029296875</v>
@@ -2714,7 +2783,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>383.739990234375</v>
@@ -2722,7 +2791,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14">
         <v>381.289794921875</v>
@@ -2730,7 +2799,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>380.31005859375</v>
@@ -2738,7 +2807,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>377.1102294921875</v>
@@ -2746,7 +2815,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>373.8800048828125</v>
@@ -2754,7 +2823,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>340.89013671875</v>
@@ -2762,7 +2831,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>326.439697265625</v>
@@ -2770,7 +2839,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>255.0601806640625</v>
@@ -2778,7 +2847,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>213.10009765625</v>
@@ -2801,162 +2870,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>400.93994140625</v>
+        <v>436.8701171875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>386.53955078125</v>
+        <v>426.26953125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4">
-        <v>349.16015625</v>
+        <v>410.09033203125</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>349.029541015625</v>
+        <v>401.159423828125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6">
-        <v>345.98046875</v>
+        <v>398.39013671875</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>344.520263671875</v>
+        <v>380.66015625</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>337.26025390625</v>
+        <v>377.1298828125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B9">
-        <v>332.94970703125</v>
+        <v>375.599853515625</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B10">
-        <v>332.00048828125</v>
+        <v>374.34033203125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B11">
-        <v>325.039306640625</v>
+        <v>367.880126953125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12">
-        <v>324.17041015625</v>
+        <v>366.649658203125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>322.919677734375</v>
+        <v>366.369384765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>321.850341796875</v>
+        <v>362.000244140625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>320.02001953125</v>
+        <v>358.679931640625</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>314.449951171875</v>
+        <v>358.18017578125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>314.079833984375</v>
+        <v>349.52001953125</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>309.6201171875</v>
+        <v>349.360107421875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>302.740234375</v>
+        <v>336.3701171875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20">
-        <v>264.3697509765625</v>
+        <v>253.4996337890625</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21">
-        <v>197.5400390625</v>
+        <v>200.16015625</v>
       </c>
     </row>
   </sheetData>
@@ -2976,66 +3045,66 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>135.0498046875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>132.9501953125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>132.1201171875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>125.85009765625</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>121.85009765625</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>116.0498046875</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>112.25</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>111.64990234375</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3043,95 +3112,95 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>111.2001953125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>110.0498046875</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>106.64990234375</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>106.10009765625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>105.60009765625</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>104.2998046875</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>103.0498046875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>99.2998046875</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>95.39990234375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>93.10009765625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>64.5498046875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>55.570068359375</v>
       </c>
     </row>
   </sheetData>
